--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי אפללו – שיר של אהבה</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%95%d7%91%d7%99-%d7%90%d7%a4%d7%9c%d7%9c%d7%95-%d7%a9%d7%99%d7%a8-%d7%a9%d7%9c-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר יושב היטב בתוך העולם הסגנוני של קובי אפללו – בלדה רכה, רגשית, עם דגש על אינטימיות, זיכרון וזוגיות מתמשכת. השיר עוסק בכמה נושאים מרכזיים: אהבה מתמשכת לאורך שנים, התמודדות עם קשיים (“כשהכאב נגע…”), זיכרון ככוח מחזק, יצירה משותפת של</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:56</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי אפללו – שיר של אהבה</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-29</v>
@@ -492,10 +492,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:56</v>
+        <v>2:50</v>
       </c>
       <c r="H3" t="str">
-        <v>Charlie Puth</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-29</v>
@@ -530,10 +530,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:50</v>
+        <v>3:42</v>
       </c>
       <c r="H4" t="str">
-        <v>Miley Cyrus</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-29</v>
@@ -568,10 +568,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:42</v>
+        <v>2:16</v>
       </c>
       <c r="H5" t="str">
-        <v>Conan Gray</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-29</v>
@@ -606,10 +606,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:16</v>
+        <v>3:08</v>
       </c>
       <c r="H6" t="str">
-        <v>Charlie Puth</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-29</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:08</v>
+        <v>3:38</v>
       </c>
       <c r="H7" t="str">
-        <v>Kylie Morgan</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-29</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:38</v>
+        <v>3:01</v>
       </c>
       <c r="H8" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-29</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:01</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>Angelina Mango</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-29</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Julio Iglesias</v>
+        <v>Loreen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-29</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Loreen</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-29</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:58</v>
+        <v>3:49</v>
       </c>
       <c r="H12" t="str">
-        <v>Jessie Ware</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>Holly Humberstone</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-29</v>
@@ -910,10 +910,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H14" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-29</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:50</v>
+        <v>6:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Ella Langley</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-29</v>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>6:43</v>
+        <v>4:52</v>
       </c>
       <c r="H16" t="str">
-        <v>David Gilmour</v>
+        <v>Eagles</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-29</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:52</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>Eagles</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:13</v>
+        <v>3:28</v>
       </c>
       <c r="H18" t="str">
-        <v>Moody Joody</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-29</v>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Jackson Dean</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-29</v>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:01</v>
+        <v>4:00</v>
       </c>
       <c r="H20" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-29</v>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:00</v>
+        <v>5:35</v>
       </c>
       <c r="H21" t="str">
-        <v>Madison Cunningham</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:35</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>mary in the junkyard</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:01</v>
+        <v>3:40</v>
       </c>
       <c r="H23" t="str">
-        <v>Adam Sanders</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-29</v>
@@ -1290,10 +1290,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:40</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>twocolors</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:25</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>twocolors</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:42</v>
+        <v>3:56</v>
       </c>
       <c r="H26" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Prince</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-29</v>
@@ -1404,10 +1404,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:56</v>
+        <v>5:12</v>
       </c>
       <c r="H27" t="str">
-        <v>Prince</v>
+        <v>RAYE</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B28" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-29</v>
@@ -1442,10 +1442,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:12</v>
+        <v>3:30</v>
       </c>
       <c r="H28" t="str">
-        <v>RAYE</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-29</v>
@@ -1480,10 +1480,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:30</v>
+        <v>3:18</v>
       </c>
       <c r="H29" t="str">
-        <v>The Warning</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-29</v>
@@ -1518,10 +1518,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:18</v>
+        <v>3:33</v>
       </c>
       <c r="H30" t="str">
-        <v>Pentatonix</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-29</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:33</v>
+        <v>5:53</v>
       </c>
       <c r="H31" t="str">
-        <v>Tenille Townes</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:53</v>
+        <v>2:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Jessie Ware</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B33" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-29</v>
@@ -1632,10 +1632,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Niall Horan</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-29</v>
@@ -1670,10 +1670,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:26</v>
+        <v>2:40</v>
       </c>
       <c r="H34" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B35" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-29</v>
@@ -1708,10 +1708,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:40</v>
+        <v>3:30</v>
       </c>
       <c r="H35" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-29</v>
@@ -1746,10 +1746,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:30</v>
+        <v>4:02</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-29</v>
@@ -1784,10 +1784,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:02</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>Foo Fighters</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-29</v>
@@ -1822,10 +1822,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:40</v>
+        <v>2:22</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-29</v>
@@ -1860,10 +1860,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:22</v>
+        <v>3:47</v>
       </c>
       <c r="H39" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-29</v>
@@ -1898,10 +1898,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:47</v>
+        <v>3:39</v>
       </c>
       <c r="H40" t="str">
-        <v>Ella Langley</v>
+        <v>Cannons</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-29</v>
@@ -1936,10 +1936,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:39</v>
+        <v>4:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Cannons</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:10</v>
+        <v>4:47</v>
       </c>
       <c r="H42" t="str">
-        <v>Luke Combs</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:47</v>
+        <v>2:14</v>
       </c>
       <c r="H43" t="str">
-        <v>Nessa Barrett</v>
+        <v>aron!</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H44" t="str">
-        <v>aron!</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-29</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:00</v>
+        <v>3:56</v>
       </c>
       <c r="H45" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>DMA'S</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-29</v>
@@ -2126,10 +2126,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:56</v>
+        <v>3:17</v>
       </c>
       <c r="H46" t="str">
-        <v>DMA'S</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-29</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Nick Carter</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-29</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:38</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Carly Pearce</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-29</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:11</v>
+        <v>2:57</v>
       </c>
       <c r="H51" t="str">
-        <v>OneRepublic</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-29</v>
@@ -2354,10 +2354,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:57</v>
+        <v>3:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:47</v>
+        <v>7:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>7:10</v>
+        <v>3:06</v>
       </c>
       <c r="H54" t="str">
-        <v>David Gilmour</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-29</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:06</v>
+        <v>3:05</v>
       </c>
       <c r="H55" t="str">
-        <v>Grace Enger</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-29</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H56" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-29</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:12</v>
+        <v>9:11</v>
       </c>
       <c r="H57" t="str">
-        <v>Freya Ridings</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-29</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H58" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-29</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:49</v>
+        <v>3:28</v>
       </c>
       <c r="H59" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-29</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H60" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-29</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>Martin Garrix</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-29</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:11</v>
+        <v>2:27</v>
       </c>
       <c r="H62" t="str">
-        <v>Baby Queen</v>
+        <v>HAUSER</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-29</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-29</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:34</v>
+        <v>2:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Holly Humberstone</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-29</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H65" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-29</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H66" t="str">
-        <v>Rick Astley</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-29</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:39</v>
+        <v>5:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Jessie J</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:08</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Jessie J</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H69" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:42</v>
+        <v>2:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:31</v>
+        <v>3:14</v>
       </c>
       <c r="H71" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H72" t="str">
-        <v>Luke Combs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H73" t="str">
-        <v>Allison Russell</v>
+        <v>We Three</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H74" t="str">
-        <v>We Three</v>
+        <v>paris jackson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H75" t="str">
-        <v>paris jackson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:46</v>
+        <v>3:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H78" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:38</v>
+        <v>4:29</v>
       </c>
       <c r="H79" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Kungs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:29</v>
+        <v>4:28</v>
       </c>
       <c r="H80" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:28</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H82" t="str">
-        <v>aron!</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H83" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H84" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-29</v>
@@ -3611,7 +3611,7 @@
         <v>4:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Owen Riegling</v>
+        <v>LANY</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>LANY</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H87" t="str">
-        <v>Maverick Sabre</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-29</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Amanda Jordan</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-29</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="H89" t="str">
-        <v>Beabadoobee</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-29</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Spacey Jane</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-29</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H91" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-29</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H92" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-29</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H93" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-29</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H94" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-29</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-29</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-29</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H97" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-29</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H98" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H99" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H100" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H101" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G102" t="str">
-        <v>5:01</v>
+        <v>3:18</v>
       </c>
       <c r="H102" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L102" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Days We Left Behind</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:18</v>
+        <v>2:47</v>
       </c>
       <c r="H103" t="str">
-        <v>Paul McCartney</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L103" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G104" t="str">
-        <v>2:47</v>
+        <v>6:17</v>
       </c>
       <c r="H104" t="str">
-        <v>Miley Cyrus</v>
+        <v>RAYE</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L104" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>MARATHON</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>6:17</v>
+        <v>2:49</v>
       </c>
       <c r="H105" t="str">
-        <v>RAYE</v>
+        <v>Becky G</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L105" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>MARATHON</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>MARATHON - Single</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:49</v>
+        <v>3:00</v>
       </c>
       <c r="H106" t="str">
-        <v>Becky G</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L106" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ALL THE TIME</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H107" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L107" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Sucker For Love</v>
+        <v>FATHER</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sexistential</v>
+        <v>BULLY</v>
       </c>
       <c r="G108" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>Robyn</v>
+        <v>Kanye West</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L108" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>FATHER</v>
+        <v>Lose Control</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>BULLY</v>
+        <v>ADL</v>
       </c>
       <c r="G109" t="str">
-        <v>2:49</v>
+        <v>2:39</v>
       </c>
       <c r="H109" t="str">
-        <v>Kanye West</v>
+        <v>Yeat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L109" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Lose Control</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>ADL</v>
+        <v>Zavier</v>
       </c>
       <c r="G110" t="str">
-        <v>2:39</v>
+        <v>3:44</v>
       </c>
       <c r="H110" t="str">
-        <v>Yeat</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L110" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Zavier</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>2:07</v>
       </c>
       <c r="H111" t="str">
-        <v>Fetty Wap</v>
+        <v>Central Cee</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L111" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WAGWAN</v>
+        <v>Sideways</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G112" t="str">
-        <v>2:07</v>
+        <v>3:12</v>
       </c>
       <c r="H112" t="str">
-        <v>Central Cee</v>
+        <v>ZAYN</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L112" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Sideways</v>
+        <v>Automatic</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>KONNAKOL</v>
+        <v>Superbloom</v>
       </c>
       <c r="G113" t="str">
-        <v>3:12</v>
+        <v>2:57</v>
       </c>
       <c r="H113" t="str">
-        <v>ZAYN</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L113" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Automatic</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Superbloom</v>
+        <v>Ricochet</v>
       </c>
       <c r="G114" t="str">
-        <v>2:57</v>
+        <v>3:34</v>
       </c>
       <c r="H114" t="str">
-        <v>Jessie Ware</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L114" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tractor Beam</v>
+        <v>prom queen</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ricochet</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:34</v>
+        <v>2:43</v>
       </c>
       <c r="H115" t="str">
-        <v>Snail Mail</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L115" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>prom queen</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>prom queen - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:43</v>
+        <v>3:26</v>
       </c>
       <c r="H116" t="str">
-        <v>Amelia Moore</v>
+        <v>J Balvin</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L116" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pal Agua</v>
+        <v>Phoenix</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:26</v>
+        <v>2:24</v>
       </c>
       <c r="H117" t="str">
-        <v>J Balvin</v>
+        <v>Marshmello</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L117" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Phoenix</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Phoenix - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:24</v>
+        <v>2:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Marshmello</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L118" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:56</v>
+        <v>3:36</v>
       </c>
       <c r="H119" t="str">
-        <v>Ne-Yo</v>
+        <v>Eli</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L119" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Feel Your Rain</v>
+        <v>Lonely</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G120" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H120" t="str">
-        <v>Eli</v>
+        <v>Fcukers</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L120" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Lonely</v>
+        <v>Back in Love</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Ö</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>3:14</v>
       </c>
       <c r="H121" t="str">
-        <v>Fcukers</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L121" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Back in Love</v>
+        <v>Sideways</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Back in Love - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G122" t="str">
-        <v>3:14</v>
+        <v>3:55</v>
       </c>
       <c r="H122" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L122" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sideways</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Honora</v>
       </c>
       <c r="G123" t="str">
-        <v>3:55</v>
+        <v>4:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Charlie Puth</v>
+        <v>Flea</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L123" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Honora</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:22</v>
+        <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>Flea</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L124" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:58</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L125" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G126" t="str">
-        <v>3:02</v>
+        <v>4:42</v>
       </c>
       <c r="H126" t="str">
-        <v>Honey Bxby</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L126" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>One Thing At A Time</v>
+        <v>wasteland</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Creature of Habit</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:42</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Courtney Barnett</v>
+        <v>Yuna</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L127" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>wasteland</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>wasteland - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G128" t="str">
-        <v>3:05</v>
+        <v>2:31</v>
       </c>
       <c r="H128" t="str">
-        <v>Yuna</v>
+        <v>Artemas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L128" t="str">
-        <v>wasteland - Yuna</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Por LA</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>getting up to no good</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G129" t="str">
-        <v>2:31</v>
+        <v>2:19</v>
       </c>
       <c r="H129" t="str">
-        <v>Artemas</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L129" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Por LA</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>TODO Ø NADA</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G130" t="str">
-        <v>2:19</v>
+        <v>4:14</v>
       </c>
       <c r="H130" t="str">
-        <v>Linea Personal</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L130" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>You Lead Me</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Broken View</v>
       </c>
       <c r="G131" t="str">
-        <v>4:14</v>
+        <v>4:18</v>
       </c>
       <c r="H131" t="str">
-        <v>Lauren Daigle</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L131" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Just A Kid</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Broken View</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:18</v>
+        <v>2:54</v>
       </c>
       <c r="H132" t="str">
-        <v>Sam Barber</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L132" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Country And She Knows It</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:54</v>
+        <v>2:35</v>
       </c>
       <c r="H133" t="str">
-        <v>Luke Bryan</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L133" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G134" t="str">
-        <v>2:35</v>
+        <v>3:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Thomas Rhett</v>
+        <v>ERNEST</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L134" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Deep Blue</v>
+        <v>Special</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Deep Blue</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>2:49</v>
       </c>
       <c r="H135" t="str">
-        <v>ERNEST</v>
+        <v>Elmiene</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L135" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Special</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>sounds for someone</v>
+        <v>CANDY</v>
       </c>
       <c r="G136" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H136" t="str">
-        <v>Elmiene</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L136" t="str">
-        <v>Special - Elmiene</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Heart Attack</v>
+        <v>STAY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>CANDY</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:52</v>
+        <v>3:06</v>
       </c>
       <c r="H137" t="str">
-        <v>Justine Skye</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L137" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>STAY</v>
+        <v>Unglued</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>STAY - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G138" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>Stray Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L138" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Unglued</v>
+        <v>Ritual</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Work of Heart</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:54</v>
+        <v>3:01</v>
       </c>
       <c r="H139" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L139" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Ritual</v>
+        <v>The Best</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Ritual - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:01</v>
+        <v>3:48</v>
       </c>
       <c r="H140" t="str">
-        <v>Icona Pop</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L140" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>The Best</v>
+        <v>Smile</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:48</v>
+        <v>3:50</v>
       </c>
       <c r="H141" t="str">
-        <v>Conan Gray</v>
+        <v>Two Shell</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L141" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Smile</v>
+        <v>Duro</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Smile - Single</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H142" t="str">
-        <v>Two Shell</v>
+        <v>Skrillex</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L142" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Duro</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Duro - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G143" t="str">
-        <v>3:05</v>
+        <v>2:58</v>
       </c>
       <c r="H143" t="str">
-        <v>Skrillex</v>
+        <v>Sublime</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L143" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Carousel</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G144" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H144" t="str">
-        <v>Sublime</v>
+        <v>Cannons</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L144" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Carousel</v>
+        <v>Mercy</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Everything Glows</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:36</v>
+        <v>3:49</v>
       </c>
       <c r="H145" t="str">
-        <v>Cannons</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L145" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Mercy</v>
+        <v>Palms</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Mercy - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:49</v>
+        <v>3:18</v>
       </c>
       <c r="H146" t="str">
-        <v>PRESIDENT</v>
+        <v>The Maine</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L146" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Palms</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Palms - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G147" t="str">
-        <v>3:18</v>
+        <v>5:28</v>
       </c>
       <c r="H147" t="str">
-        <v>The Maine</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L147" t="str">
-        <v>Palms - The Maine</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Ozzy's Song</v>
+        <v>Danger</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>5:28</v>
+        <v>2:19</v>
       </c>
       <c r="H148" t="str">
-        <v>Black Label Society</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L148" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Danger</v>
+        <v>Icarus</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Danger - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:19</v>
+        <v>4:25</v>
       </c>
       <c r="H149" t="str">
-        <v>Nia Archives</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L149" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Icarus</v>
+        <v>idk idk</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Icarus - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:25</v>
+        <v>2:26</v>
       </c>
       <c r="H150" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L150" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>idk idk</v>
+        <v>Tonight</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>idk idk - Single</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:26</v>
+        <v>2:25</v>
       </c>
       <c r="H151" t="str">
-        <v>Jim Legxacy</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L151" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tonight</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Tonight - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G152" t="str">
-        <v>2:25</v>
+        <v>3:44</v>
       </c>
       <c r="H152" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L152" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Switcheroo</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G153" t="str">
-        <v>3:44</v>
+        <v>2:45</v>
       </c>
       <c r="H153" t="str">
-        <v>Gelli Haha</v>
+        <v>BIA</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L153" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G154" t="str">
-        <v>2:45</v>
+        <v>3:33</v>
       </c>
       <c r="H154" t="str">
-        <v>BIA</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L154" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>this girl wants everything</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>3:44</v>
       </c>
       <c r="H155" t="str">
-        <v>Isaia Huron</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L155" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>2:41</v>
       </c>
       <c r="H156" t="str">
-        <v>Slayyyter</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L156" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Kingdom of Fear</v>
+        <v>R3verse</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Deep Water - EP</v>
+        <v>takeaways</v>
       </c>
       <c r="G157" t="str">
-        <v>2:41</v>
+        <v>3:31</v>
       </c>
       <c r="H157" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Medium Build</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L157" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>R3verse</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>takeaways</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G158" t="str">
-        <v>3:31</v>
+        <v>2:32</v>
       </c>
       <c r="H158" t="str">
-        <v>Medium Build</v>
+        <v>MIKE</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L158" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>heart of gold</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H159" t="str">
-        <v>MIKE</v>
+        <v>kai devega</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L159" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>heart of gold</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>heart of gold - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G160" t="str">
-        <v>2:51</v>
+        <v>4:21</v>
       </c>
       <c r="H160" t="str">
-        <v>kai devega</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L160" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Breaking Down</v>
+        <v>Dream House</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Skeletor</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:21</v>
+        <v>2:54</v>
       </c>
       <c r="H161" t="str">
-        <v>Chief Keef</v>
+        <v>Empress Of</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L161" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dream House</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Dream House - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:54</v>
+        <v>2:51</v>
       </c>
       <c r="H162" t="str">
-        <v>Empress Of</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L162" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Baby Blue</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H163" t="str">
-        <v>Cody Simpson</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L163" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G164" t="str">
-        <v>2:37</v>
+        <v>4:05</v>
       </c>
       <c r="H164" t="str">
-        <v>MEDUZA</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L164" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Forever Now</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>4:05</v>
+        <v>3:46</v>
       </c>
       <c r="H165" t="str">
-        <v>Switchfoot</v>
+        <v>Benny G</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L165" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:46</v>
+        <v>3:03</v>
       </c>
       <c r="H166" t="str">
-        <v>Benny G</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L166" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>3:03</v>
+        <v>4:19</v>
       </c>
       <c r="H167" t="str">
-        <v>Eric Bellinger</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L167" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:19</v>
+        <v>2:10</v>
       </c>
       <c r="H168" t="str">
-        <v>Anish Kumar</v>
+        <v>WesGhost</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L168" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>GASLIGHT</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:10</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>WesGhost</v>
+        <v>GERD</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L169" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Truth To Be Told</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H170" t="str">
-        <v>GERD</v>
+        <v>Prospa</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L170" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Free Your Mind</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H171" t="str">
-        <v>Prospa</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L171" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Down To The Bone</v>
+        <v>Breathe</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:51</v>
+        <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>Josh Baker</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L172" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Breathe</v>
+        <v>xs</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Breathe - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H173" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L173" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>xs</v>
+        <v>Sail</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>xs - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G174" t="str">
-        <v>3:19</v>
+        <v>4:54</v>
       </c>
       <c r="H174" t="str">
-        <v>Ashley Cooke</v>
+        <v>Future Islands</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L174" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Sail</v>
+        <v>Dreaming</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G175" t="str">
-        <v>4:54</v>
+        <v>3:33</v>
       </c>
       <c r="H175" t="str">
-        <v>Future Islands</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L175" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Dreaming</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Dear Nashville</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G176" t="str">
-        <v>3:33</v>
+        <v>2:39</v>
       </c>
       <c r="H176" t="str">
-        <v>Ashley Monroe</v>
+        <v>Armanii</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L176" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>NEW TINGZ</v>
+        <v>La Opinión</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G177" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>Armanii</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L177" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>La Opinión</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Mis Compas El Final</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:23</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>Joss Favela</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L178" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>qué ves en mí?</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:24</v>
+        <v>2:43</v>
       </c>
       <c r="H179" t="str">
-        <v>Paloma Morphy</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L179" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:43</v>
+        <v>2:16</v>
       </c>
       <c r="H180" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L180" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>TUTUTU</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>TUTUTU - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:16</v>
+        <v>2:56</v>
       </c>
       <c r="H181" t="str">
-        <v>ELENA ROSE</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L181" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>Me Neither</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G182" t="str">
-        <v>2:56</v>
+        <v>3:32</v>
       </c>
       <c r="H182" t="str">
-        <v>2'Live Bre</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L182" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Me Neither</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G183" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H183" t="str">
-        <v>Ty Myers</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L183" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Cole Palmer</v>
+        <v>Wonder</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Solid Ground</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>3:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Limoblaze</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L184" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Wonder</v>
+        <v>ICU</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Wonder - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:48</v>
+        <v>2:53</v>
       </c>
       <c r="H185" t="str">
-        <v>Meeks Carter</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L185" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>ICU</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>ICU - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G186" t="str">
-        <v>2:53</v>
+        <v>2:45</v>
       </c>
       <c r="H186" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Jozzy</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L186" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:45</v>
+        <v>3:21</v>
       </c>
       <c r="H187" t="str">
-        <v>Jozzy</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L187" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Waiting Room</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Waiting Room - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G188" t="str">
-        <v>3:21</v>
+        <v>4:02</v>
       </c>
       <c r="H188" t="str">
-        <v>Jenevieve</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L188" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Rise</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:02</v>
+        <v>3:51</v>
       </c>
       <c r="H189" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L189" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Roll On Thru</v>
+        <v>Delicately</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:51</v>
+        <v>3:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Hayden Everett</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L190" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Delicately</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Delicately - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Andrea Bejar</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L191" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>One Of Those Things</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G192" t="str">
-        <v>3:27</v>
+        <v>6:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Lucy Clearwater</v>
+        <v>José González</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L192" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>For Every Dusk</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G193" t="str">
-        <v>6:04</v>
+        <v>3:33</v>
       </c>
       <c r="H193" t="str">
-        <v>José González</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L193" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>I'll Wait</v>
+        <v>Daisy</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:33</v>
+        <v>3:02</v>
       </c>
       <c r="H194" t="str">
-        <v>Buzzy Lee</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L194" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Daisy</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Daisy - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G195" t="str">
-        <v>3:02</v>
+        <v>3:57</v>
       </c>
       <c r="H195" t="str">
-        <v>Lola Blue</v>
+        <v>james K</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L195" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Friend Remixes</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:57</v>
+        <v>2:45</v>
       </c>
       <c r="H196" t="str">
-        <v>james K</v>
+        <v>MAVICA</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L196" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Fort</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Perdidos - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:45</v>
+        <v>2:27</v>
       </c>
       <c r="H197" t="str">
-        <v>MAVICA</v>
+        <v>Lamb</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L197" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Fort</v>
+        <v>SAME LA</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-29</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Fort - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:27</v>
+        <v>3:44</v>
       </c>
       <c r="H198" t="str">
-        <v>Lamb</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L198" t="str">
-        <v>Fort - Lamb</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SAME LA</v>
+        <v>Working On It</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-29</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>SAME LA - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:44</v>
+        <v>3:06</v>
       </c>
       <c r="H199" t="str">
-        <v>Tiffany Day</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L199" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Working On It</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-29</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Working On It - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:06</v>
+        <v>4:03</v>
       </c>
       <c r="H200" t="str">
-        <v>Arthur Hill</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L200" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>spring cleaning</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-29</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H201" t="str">
-        <v>Ethan Regan</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L201" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Just Drivin'</v>
+        <v>Simple Things</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-29</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H202" t="str">
-        <v>Presley Haile</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L202" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Simple Things</v>
+        <v>Want It Back</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-29</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Simple Things - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:46</v>
+        <v>3:27</v>
       </c>
       <c r="H203" t="str">
-        <v>Evening Elephants</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L203" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Want It Back</v>
+        <v>Bite Down</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-29</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Want It Back - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:27</v>
+        <v>3:36</v>
       </c>
       <c r="H204" t="str">
-        <v>Giant Rooks</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L204" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Bite Down</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-29</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Bite Down - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G205" t="str">
-        <v>3:36</v>
+        <v>5:42</v>
       </c>
       <c r="H205" t="str">
-        <v>Anna Sofia</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L205" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Demons</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-29</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G206" t="str">
-        <v>5:42</v>
+        <v>2:42</v>
       </c>
       <c r="H206" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Anella</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L206" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Demons</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D207" t="str">
         <v>2026-03-29</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>2:42</v>
+        <v>3:35</v>
       </c>
       <c r="H207" t="str">
-        <v>Anella</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L207" t="str">
-        <v>Demons - Anella</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Es brennt...</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D208" t="str">
         <v>2026-03-29</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>3:35</v>
+        <v>3:49</v>
       </c>
       <c r="H208" t="str">
-        <v>Till Lindemann</v>
+        <v>Enslaved</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L208" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Fire Marengo</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D209" t="str">
         <v>2026-03-29</v>
@@ -8317,68 +8317,30 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G209" t="str">
-        <v>3:49</v>
+        <v>4:09</v>
       </c>
       <c r="H209" t="str">
-        <v>Enslaved</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L209" t="str">
-        <v>Fire Marengo - Enslaved</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Close to the Bone</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G210" t="str">
-        <v>4:09</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
-      </c>
-      <c r="L210" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L217"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410257&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>נתי שקד - גשם</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410256&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-29</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Miley Cyrus</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>נתי שקד - גשם</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>לידור עמירה - חלום</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410255&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-29</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>3:42</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Conan Gray</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>לידור עמירה - חלום</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410254&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-29</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>2:16</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>ישראל מועלמי - דור מלא נסיונות</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410253&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-29</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:08</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Kylie Morgan</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>ישראל מועלמי - דור מלא נסיונות</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>יונתן רזאל - היינו כחולמים</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410252&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-29</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>יונתן רזאל - היינו כחולמים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>בר סיידו - הימים שאחריך</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410251&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-29</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Angelina Mango</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>בר סיידו - הימים שאחריך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>נגה ארז Stuck In Heaven</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-29</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://yosmusic.com/%d7%a0%d7%92%d7%94-%d7%90%d7%a8%d7%96-stuck-in-heaven/</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-29</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>Stuck In Heaven של נגה ארז הוא דוגמה  לפער בין סאונד פופ קצבי, כמעט “כיפי”, לבין תוכן רגשי מורכב ואפילו מטריד. זה בדיוק אחד הסימנים המסחריים של נגה ארז: מוזיקה שמרקידה אותך, בזמן שהמילים עושות לך קצת אי־נוחות. מבחינה מוזיקלית,</v>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Julio Iglesias</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>נגה ארז Stuck In Heaven</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-29</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:59</v>
+        <v>3:56</v>
       </c>
       <c r="H10" t="str">
-        <v>Loreen</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-29</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:58</v>
+        <v>2:50</v>
       </c>
       <c r="H11" t="str">
-        <v>Jessie Ware</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-29</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H12" t="str">
-        <v>Holly Humberstone</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:22</v>
+        <v>2:16</v>
       </c>
       <c r="H13" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:50</v>
+        <v>3:08</v>
       </c>
       <c r="H14" t="str">
-        <v>Ella Langley</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>6:43</v>
+        <v>3:38</v>
       </c>
       <c r="H15" t="str">
-        <v>David Gilmour</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:52</v>
+        <v>3:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Eagles</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:13</v>
+        <v>3:59</v>
       </c>
       <c r="H17" t="str">
-        <v>Moody Joody</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:28</v>
+        <v>2:59</v>
       </c>
       <c r="H18" t="str">
-        <v>Jackson Dean</v>
+        <v>Loreen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:01</v>
+        <v>2:58</v>
       </c>
       <c r="H19" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H20" t="str">
-        <v>Madison Cunningham</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:35</v>
+        <v>3:22</v>
       </c>
       <c r="H21" t="str">
-        <v>mary in the junkyard</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:01</v>
+        <v>3:50</v>
       </c>
       <c r="H22" t="str">
-        <v>Adam Sanders</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:40</v>
+        <v>6:43</v>
       </c>
       <c r="H23" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:25</v>
+        <v>4:52</v>
       </c>
       <c r="H24" t="str">
-        <v>twocolors</v>
+        <v>Eagles</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:42</v>
+        <v>3:13</v>
       </c>
       <c r="H25" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:56</v>
+        <v>3:28</v>
       </c>
       <c r="H26" t="str">
-        <v>Prince</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:12</v>
+        <v>3:01</v>
       </c>
       <c r="H27" t="str">
-        <v>RAYE</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:30</v>
+        <v>4:00</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:18</v>
+        <v>5:35</v>
       </c>
       <c r="H29" t="str">
-        <v>Pentatonix</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-29</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:33</v>
+        <v>3:01</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-29</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:53</v>
+        <v>3:40</v>
       </c>
       <c r="H31" t="str">
-        <v>Jessie Ware</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:37</v>
+        <v>2:25</v>
       </c>
       <c r="H32" t="str">
-        <v>Niall Horan</v>
+        <v>twocolors</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-29</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:26</v>
+        <v>3:42</v>
       </c>
       <c r="H33" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-29</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:40</v>
+        <v>3:56</v>
       </c>
       <c r="H34" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Prince</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:30</v>
+        <v>5:12</v>
       </c>
       <c r="H35" t="str">
-        <v>Jackson Dean</v>
+        <v>RAYE</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:02</v>
+        <v>3:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Foo Fighters</v>
+        <v>The Warning</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B37" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-29</v>
@@ -1784,10 +1784,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:40</v>
+        <v>3:18</v>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B38" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-29</v>
@@ -1822,10 +1822,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:22</v>
+        <v>3:33</v>
       </c>
       <c r="H38" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-29</v>
@@ -1860,10 +1860,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:47</v>
+        <v>5:53</v>
       </c>
       <c r="H39" t="str">
-        <v>Ella Langley</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-29</v>
@@ -1898,10 +1898,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:39</v>
+        <v>2:37</v>
       </c>
       <c r="H40" t="str">
-        <v>Cannons</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-29</v>
@@ -1936,10 +1936,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:10</v>
+        <v>2:26</v>
       </c>
       <c r="H41" t="str">
-        <v>Luke Combs</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:47</v>
+        <v>2:40</v>
       </c>
       <c r="H42" t="str">
-        <v>Nessa Barrett</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:14</v>
+        <v>3:30</v>
       </c>
       <c r="H43" t="str">
-        <v>aron!</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:00</v>
+        <v>4:02</v>
       </c>
       <c r="H44" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-29</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:56</v>
+        <v>3:40</v>
       </c>
       <c r="H45" t="str">
-        <v>DMA'S</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-29</v>
@@ -2126,10 +2126,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:17</v>
+        <v>2:22</v>
       </c>
       <c r="H46" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:17</v>
+        <v>3:47</v>
       </c>
       <c r="H47" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:39</v>
       </c>
       <c r="H48" t="str">
-        <v>Nick Carter</v>
+        <v>Cannons</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:38</v>
+        <v>4:10</v>
       </c>
       <c r="H49" t="str">
-        <v>Carly Pearce</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>4:47</v>
       </c>
       <c r="H50" t="str">
-        <v>OneRepublic</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:57</v>
+        <v>2:14</v>
       </c>
       <c r="H51" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>aron!</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:47</v>
+        <v>4:00</v>
       </c>
       <c r="H52" t="str">
-        <v>Armin van Buuren</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>7:10</v>
+        <v>3:56</v>
       </c>
       <c r="H53" t="str">
-        <v>David Gilmour</v>
+        <v>DMA'S</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H54" t="str">
-        <v>Grace Enger</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:05</v>
+        <v>3:17</v>
       </c>
       <c r="H55" t="str">
-        <v>Tucker Wetmore</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-29</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:12</v>
+        <v>3:31</v>
       </c>
       <c r="H56" t="str">
-        <v>Freya Ridings</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-29</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>9:11</v>
+        <v>3:38</v>
       </c>
       <c r="H57" t="str">
-        <v>David Gilmour</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-29</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:49</v>
+        <v>4:11</v>
       </c>
       <c r="H58" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-29</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:28</v>
+        <v>2:57</v>
       </c>
       <c r="H59" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-29</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H60" t="str">
-        <v>Martin Garrix</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-29</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:11</v>
+        <v>7:10</v>
       </c>
       <c r="H61" t="str">
-        <v>Baby Queen</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-29</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:27</v>
+        <v>3:06</v>
       </c>
       <c r="H62" t="str">
-        <v>HAUSER</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-29</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:34</v>
+        <v>3:05</v>
       </c>
       <c r="H63" t="str">
-        <v>Holly Humberstone</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-29</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:50</v>
+        <v>3:12</v>
       </c>
       <c r="H64" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-29</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:51</v>
+        <v>9:11</v>
       </c>
       <c r="H65" t="str">
-        <v>Rick Astley</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-29</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:39</v>
+        <v>3:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-29</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:08</v>
+        <v>3:28</v>
       </c>
       <c r="H67" t="str">
-        <v>Jessie J</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>3:31</v>
       </c>
       <c r="H68" t="str">
-        <v>Bishop Briggs</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:42</v>
+        <v>3:11</v>
       </c>
       <c r="H69" t="str">
-        <v>Dean Lewis</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:31</v>
+        <v>2:27</v>
       </c>
       <c r="H70" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>HAUSER</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:14</v>
+        <v>3:34</v>
       </c>
       <c r="H71" t="str">
-        <v>Luke Combs</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:22</v>
+        <v>2:50</v>
       </c>
       <c r="H72" t="str">
-        <v>Allison Russell</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:43</v>
+        <v>3:51</v>
       </c>
       <c r="H73" t="str">
-        <v>We Three</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:54</v>
+        <v>2:39</v>
       </c>
       <c r="H74" t="str">
-        <v>paris jackson</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:46</v>
+        <v>5:08</v>
       </c>
       <c r="H75" t="str">
-        <v>Kane Brown</v>
+        <v>Jessie J</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:37</v>
+        <v>3:46</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:57</v>
+        <v>2:42</v>
       </c>
       <c r="H77" t="str">
-        <v>Malcolm Todd</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:38</v>
+        <v>2:31</v>
       </c>
       <c r="H78" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:29</v>
+        <v>3:14</v>
       </c>
       <c r="H79" t="str">
-        <v>Kungs</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:28</v>
+        <v>3:22</v>
       </c>
       <c r="H80" t="str">
-        <v>Sunday (1994)</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>3:43</v>
       </c>
       <c r="H81" t="str">
-        <v>aron!</v>
+        <v>We Three</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:51</v>
+        <v>2:54</v>
       </c>
       <c r="H82" t="str">
-        <v>Colinstoughmusic</v>
+        <v>paris jackson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Sunday (1994)</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:16</v>
+        <v>3:37</v>
       </c>
       <c r="H84" t="str">
-        <v>Owen Riegling</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:16</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>LANY</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:25</v>
+        <v>3:38</v>
       </c>
       <c r="H86" t="str">
-        <v>Maverick Sabre</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:50</v>
+        <v>4:29</v>
       </c>
       <c r="H87" t="str">
-        <v>Amanda Jordan</v>
+        <v>Kungs</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-29</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>4:28</v>
       </c>
       <c r="H88" t="str">
-        <v>Beabadoobee</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-29</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:58</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Spacey Jane</v>
+        <v>aron!</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-29</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:25</v>
+        <v>3:51</v>
       </c>
       <c r="H90" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-29</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:09</v>
+        <v>2:49</v>
       </c>
       <c r="H91" t="str">
-        <v>Mei Semones</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-29</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:08</v>
+        <v>4:16</v>
       </c>
       <c r="H92" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-29</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:57</v>
+        <v>4:16</v>
       </c>
       <c r="H93" t="str">
-        <v>Natalie Jane</v>
+        <v>LANY</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-29</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-29</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:12</v>
+        <v>2:50</v>
       </c>
       <c r="H95" t="str">
-        <v>David Gilmour</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-29</v>
@@ -4029,7 +4029,7 @@
         <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>Far Caspian</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-29</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:34</v>
+        <v>3:58</v>
       </c>
       <c r="H97" t="str">
-        <v>Celine Dion</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-29</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:48</v>
+        <v>3:25</v>
       </c>
       <c r="H98" t="str">
-        <v>Harry Styles</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-29</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:58</v>
+        <v>4:09</v>
       </c>
       <c r="H99" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-29</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:33</v>
+        <v>2:08</v>
       </c>
       <c r="H100" t="str">
-        <v>Ellise</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-29</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:01</v>
+        <v>2:57</v>
       </c>
       <c r="H101" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Days We Left Behind</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:18</v>
+        <v>3:13</v>
       </c>
       <c r="H102" t="str">
-        <v>Paul McCartney</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>2:47</v>
+        <v>4:12</v>
       </c>
       <c r="H103" t="str">
-        <v>Miley Cyrus</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>6:17</v>
+        <v>3:57</v>
       </c>
       <c r="H104" t="str">
-        <v>RAYE</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>MARATHON</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>MARATHON - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H105" t="str">
-        <v>Becky G</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ALL THE TIME</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:00</v>
+        <v>3:48</v>
       </c>
       <c r="H106" t="str">
-        <v>John Summit</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Sucker For Love</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Sexistential</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:34</v>
+        <v>4:58</v>
       </c>
       <c r="H107" t="str">
-        <v>Robyn</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>FATHER</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>BULLY</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>2:33</v>
       </c>
       <c r="H108" t="str">
-        <v>Kanye West</v>
+        <v>Ellise</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Lose Control</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>ADL</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>2:39</v>
+        <v>5:01</v>
       </c>
       <c r="H109" t="str">
-        <v>Yeat</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Zavier</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G110" t="str">
-        <v>3:44</v>
+        <v>3:18</v>
       </c>
       <c r="H110" t="str">
-        <v>Fetty Wap</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L110" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WAGWAN</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:07</v>
+        <v>2:47</v>
       </c>
       <c r="H111" t="str">
-        <v>Central Cee</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L111" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Sideways</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>KONNAKOL</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G112" t="str">
-        <v>3:12</v>
+        <v>6:17</v>
       </c>
       <c r="H112" t="str">
-        <v>ZAYN</v>
+        <v>RAYE</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L112" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Automatic</v>
+        <v>MARATHON</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Superbloom</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:57</v>
+        <v>2:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Jessie Ware</v>
+        <v>Becky G</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L113" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Tractor Beam</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Ricochet</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H114" t="str">
-        <v>Snail Mail</v>
+        <v>John Summit</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L114" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>prom queen</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>prom queen - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G115" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H115" t="str">
-        <v>Amelia Moore</v>
+        <v>Robyn</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L115" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Pal Agua</v>
+        <v>FATHER</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Pal Agua - Single</v>
+        <v>BULLY</v>
       </c>
       <c r="G116" t="str">
-        <v>3:26</v>
+        <v>2:49</v>
       </c>
       <c r="H116" t="str">
-        <v>J Balvin</v>
+        <v>Kanye West</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L116" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Phoenix</v>
+        <v>Lose Control</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Phoenix - Single</v>
+        <v>ADL</v>
       </c>
       <c r="G117" t="str">
-        <v>2:24</v>
+        <v>2:39</v>
       </c>
       <c r="H117" t="str">
-        <v>Marshmello</v>
+        <v>Yeat</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L117" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Zavier</v>
       </c>
       <c r="G118" t="str">
-        <v>2:56</v>
+        <v>3:44</v>
       </c>
       <c r="H118" t="str">
-        <v>Ne-Yo</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L118" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Feel Your Rain</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G119" t="str">
-        <v>3:36</v>
+        <v>2:07</v>
       </c>
       <c r="H119" t="str">
-        <v>Eli</v>
+        <v>Central Cee</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L119" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lonely</v>
+        <v>Sideways</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ö</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G120" t="str">
-        <v>2:58</v>
+        <v>3:12</v>
       </c>
       <c r="H120" t="str">
-        <v>Fcukers</v>
+        <v>ZAYN</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L120" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Back in Love</v>
+        <v>Automatic</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Back in Love - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G121" t="str">
-        <v>3:14</v>
+        <v>2:57</v>
       </c>
       <c r="H121" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L121" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Sideways</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Ricochet</v>
       </c>
       <c r="G122" t="str">
-        <v>3:55</v>
+        <v>3:34</v>
       </c>
       <c r="H122" t="str">
-        <v>Charlie Puth</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L122" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>prom queen</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Honora</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:22</v>
+        <v>2:43</v>
       </c>
       <c r="H123" t="str">
-        <v>Flea</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L123" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H124" t="str">
-        <v>Chelsea Cutler</v>
+        <v>J Balvin</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L124" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>Phoenix</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>2:24</v>
       </c>
       <c r="H125" t="str">
-        <v>Honey Bxby</v>
+        <v>Marshmello</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L125" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>One Thing At A Time</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Creature of Habit</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:42</v>
+        <v>2:56</v>
       </c>
       <c r="H126" t="str">
-        <v>Courtney Barnett</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L126" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>wasteland</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>wasteland - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>3:36</v>
       </c>
       <c r="H127" t="str">
-        <v>Yuna</v>
+        <v>Eli</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L127" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Lonely</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>getting up to no good</v>
+        <v>Ö</v>
       </c>
       <c r="G128" t="str">
-        <v>2:31</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Artemas</v>
+        <v>Fcukers</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L128" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Por LA</v>
+        <v>Back in Love</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>TODO Ø NADA</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:19</v>
+        <v>3:14</v>
       </c>
       <c r="H129" t="str">
-        <v>Linea Personal</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L129" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>You Lead Me</v>
+        <v>Sideways</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G130" t="str">
-        <v>4:14</v>
+        <v>3:55</v>
       </c>
       <c r="H130" t="str">
-        <v>Lauren Daigle</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L130" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Just A Kid</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Broken View</v>
+        <v>Honora</v>
       </c>
       <c r="G131" t="str">
-        <v>4:18</v>
+        <v>4:22</v>
       </c>
       <c r="H131" t="str">
-        <v>Sam Barber</v>
+        <v>Flea</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L131" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Country And She Knows It</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H132" t="str">
-        <v>Luke Bryan</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L132" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:35</v>
+        <v>3:02</v>
       </c>
       <c r="H133" t="str">
-        <v>Thomas Rhett</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L133" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Deep Blue</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Deep Blue</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G134" t="str">
-        <v>3:17</v>
+        <v>4:42</v>
       </c>
       <c r="H134" t="str">
-        <v>ERNEST</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L134" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Special</v>
+        <v>wasteland</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>sounds for someone</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:49</v>
+        <v>3:05</v>
       </c>
       <c r="H135" t="str">
-        <v>Elmiene</v>
+        <v>Yuna</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L135" t="str">
-        <v>Special - Elmiene</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Heart Attack</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>CANDY</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G136" t="str">
-        <v>2:52</v>
+        <v>2:31</v>
       </c>
       <c r="H136" t="str">
-        <v>Justine Skye</v>
+        <v>Artemas</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L136" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>STAY</v>
+        <v>Por LA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>STAY - Single</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G137" t="str">
-        <v>3:06</v>
+        <v>2:19</v>
       </c>
       <c r="H137" t="str">
-        <v>Stray Kids</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L137" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Unglued</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Work of Heart</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G138" t="str">
-        <v>3:54</v>
+        <v>4:14</v>
       </c>
       <c r="H138" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L138" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ritual</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Ritual - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G139" t="str">
-        <v>3:01</v>
+        <v>4:18</v>
       </c>
       <c r="H139" t="str">
-        <v>Icona Pop</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L139" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>The Best</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:48</v>
+        <v>2:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Conan Gray</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L140" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Smile</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Smile - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:50</v>
+        <v>2:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Two Shell</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L141" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Duro</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Duro - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G142" t="str">
-        <v>3:05</v>
+        <v>3:17</v>
       </c>
       <c r="H142" t="str">
-        <v>Skrillex</v>
+        <v>ERNEST</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L142" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Special</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G143" t="str">
-        <v>2:58</v>
+        <v>2:49</v>
       </c>
       <c r="H143" t="str">
-        <v>Sublime</v>
+        <v>Elmiene</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L143" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Carousel</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Everything Glows</v>
+        <v>CANDY</v>
       </c>
       <c r="G144" t="str">
-        <v>3:36</v>
+        <v>2:52</v>
       </c>
       <c r="H144" t="str">
-        <v>Cannons</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L144" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Mercy</v>
+        <v>STAY</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Mercy - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H145" t="str">
-        <v>PRESIDENT</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L145" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Palms</v>
+        <v>Unglued</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Palms - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G146" t="str">
-        <v>3:18</v>
+        <v>3:54</v>
       </c>
       <c r="H146" t="str">
-        <v>The Maine</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L146" t="str">
-        <v>Palms - The Maine</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Ozzy's Song</v>
+        <v>Ritual</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>5:28</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Black Label Society</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L147" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Danger</v>
+        <v>The Best</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Danger - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G148" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H148" t="str">
-        <v>Nia Archives</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L148" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Icarus</v>
+        <v>Smile</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Icarus - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:25</v>
+        <v>3:50</v>
       </c>
       <c r="H149" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Two Shell</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L149" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>idk idk</v>
+        <v>Duro</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>idk idk - Single</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:26</v>
+        <v>3:05</v>
       </c>
       <c r="H150" t="str">
-        <v>Jim Legxacy</v>
+        <v>Skrillex</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L150" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Tonight</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Tonight - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G151" t="str">
-        <v>2:25</v>
+        <v>2:58</v>
       </c>
       <c r="H151" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Sublime</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L151" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Carousel</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Switcheroo</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G152" t="str">
-        <v>3:44</v>
+        <v>3:36</v>
       </c>
       <c r="H152" t="str">
-        <v>Gelli Haha</v>
+        <v>Cannons</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L152" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>Mercy</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:45</v>
+        <v>3:49</v>
       </c>
       <c r="H153" t="str">
-        <v>BIA</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L153" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>this girl wants everything</v>
+        <v>Palms</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:33</v>
+        <v>3:18</v>
       </c>
       <c r="H154" t="str">
-        <v>Isaia Huron</v>
+        <v>The Maine</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L154" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:44</v>
+        <v>5:28</v>
       </c>
       <c r="H155" t="str">
-        <v>Slayyyter</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L155" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Danger</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Deep Water - EP</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:41</v>
+        <v>2:19</v>
       </c>
       <c r="H156" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L156" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>R3verse</v>
+        <v>Icarus</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>takeaways</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:31</v>
+        <v>4:25</v>
       </c>
       <c r="H157" t="str">
-        <v>Medium Build</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L157" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>idk idk</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:32</v>
+        <v>2:26</v>
       </c>
       <c r="H158" t="str">
-        <v>MIKE</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L158" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>heart of gold</v>
+        <v>Tonight</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>heart of gold - Single</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:51</v>
+        <v>2:25</v>
       </c>
       <c r="H159" t="str">
-        <v>kai devega</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L159" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Breaking Down</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Skeletor</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G160" t="str">
-        <v>4:21</v>
+        <v>3:44</v>
       </c>
       <c r="H160" t="str">
-        <v>Chief Keef</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L160" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Dream House</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Dream House - Single</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G161" t="str">
-        <v>2:54</v>
+        <v>2:45</v>
       </c>
       <c r="H161" t="str">
-        <v>Empress Of</v>
+        <v>BIA</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L161" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Baby Blue</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G162" t="str">
-        <v>2:51</v>
+        <v>3:33</v>
       </c>
       <c r="H162" t="str">
-        <v>Cody Simpson</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L162" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G163" t="str">
-        <v>2:37</v>
+        <v>3:44</v>
       </c>
       <c r="H163" t="str">
-        <v>MEDUZA</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L163" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Forever Now</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>4:05</v>
+        <v>2:41</v>
       </c>
       <c r="H164" t="str">
-        <v>Switchfoot</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L164" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>R3verse</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>takeaways</v>
       </c>
       <c r="G165" t="str">
-        <v>3:46</v>
+        <v>3:31</v>
       </c>
       <c r="H165" t="str">
-        <v>Benny G</v>
+        <v>Medium Build</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L165" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G166" t="str">
-        <v>3:03</v>
+        <v>2:32</v>
       </c>
       <c r="H166" t="str">
-        <v>Eric Bellinger</v>
+        <v>MIKE</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L166" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>heart of gold</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:19</v>
+        <v>2:51</v>
       </c>
       <c r="H167" t="str">
-        <v>Anish Kumar</v>
+        <v>kai devega</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L167" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>GASLIGHT</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G168" t="str">
-        <v>2:10</v>
+        <v>4:21</v>
       </c>
       <c r="H168" t="str">
-        <v>WesGhost</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L168" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Truth To Be Told</v>
+        <v>Dream House</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:17</v>
+        <v>2:54</v>
       </c>
       <c r="H169" t="str">
-        <v>GERD</v>
+        <v>Empress Of</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L169" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Free Your Mind</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H170" t="str">
-        <v>Prospa</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L170" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Down To The Bone</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H171" t="str">
-        <v>Josh Baker</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L171" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Breathe</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Breathe - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H172" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L172" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>xs</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>xs - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:19</v>
+        <v>3:46</v>
       </c>
       <c r="H173" t="str">
-        <v>Ashley Cooke</v>
+        <v>Benny G</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L173" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Sail</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:54</v>
+        <v>3:03</v>
       </c>
       <c r="H174" t="str">
-        <v>Future Islands</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L174" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Dreaming</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Dear Nashville</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>3:33</v>
+        <v>4:19</v>
       </c>
       <c r="H175" t="str">
-        <v>Ashley Monroe</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L175" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>NEW TINGZ</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:39</v>
+        <v>2:10</v>
       </c>
       <c r="H176" t="str">
-        <v>Armanii</v>
+        <v>WesGhost</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L176" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>La Opinión</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Mis Compas El Final</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>3:17</v>
       </c>
       <c r="H177" t="str">
-        <v>Joss Favela</v>
+        <v>GERD</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L177" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>qué ves en mí?</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H178" t="str">
-        <v>Paloma Morphy</v>
+        <v>Prospa</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L178" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:43</v>
+        <v>2:51</v>
       </c>
       <c r="H179" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L179" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>TUTUTU</v>
+        <v>Breathe</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:16</v>
+        <v>2:48</v>
       </c>
       <c r="H180" t="str">
-        <v>ELENA ROSE</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L180" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>xs</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:56</v>
+        <v>3:19</v>
       </c>
       <c r="H181" t="str">
-        <v>2'Live Bre</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L181" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Me Neither</v>
+        <v>Sail</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Heavy On The Soul</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G182" t="str">
-        <v>3:32</v>
+        <v>4:54</v>
       </c>
       <c r="H182" t="str">
-        <v>Ty Myers</v>
+        <v>Future Islands</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L182" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cole Palmer</v>
+        <v>Dreaming</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Solid Ground</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G183" t="str">
-        <v>2:48</v>
+        <v>3:33</v>
       </c>
       <c r="H183" t="str">
-        <v>Limoblaze</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L183" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Wonder</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Wonder - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G184" t="str">
-        <v>3:48</v>
+        <v>2:39</v>
       </c>
       <c r="H184" t="str">
-        <v>Meeks Carter</v>
+        <v>Armanii</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L184" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>ICU</v>
+        <v>La Opinión</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>ICU - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G185" t="str">
-        <v>2:53</v>
+        <v>3:23</v>
       </c>
       <c r="H185" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L185" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:45</v>
+        <v>3:24</v>
       </c>
       <c r="H186" t="str">
-        <v>Jozzy</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L186" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Waiting Room</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Waiting Room - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:21</v>
+        <v>2:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Jenevieve</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L187" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Rise</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:02</v>
+        <v>2:16</v>
       </c>
       <c r="H188" t="str">
-        <v>Melissa Etheridge</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L188" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Roll On Thru</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:51</v>
+        <v>2:56</v>
       </c>
       <c r="H189" t="str">
-        <v>Hayden Everett</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L189" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Delicately</v>
+        <v>Me Neither</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Delicately - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G190" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H190" t="str">
-        <v>Andrea Bejar</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L190" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>One Of Those Things</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G191" t="str">
-        <v>3:27</v>
+        <v>2:48</v>
       </c>
       <c r="H191" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L191" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>For Every Dusk</v>
+        <v>Wonder</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>6:04</v>
+        <v>3:48</v>
       </c>
       <c r="H192" t="str">
-        <v>José González</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L192" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I'll Wait</v>
+        <v>ICU</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H193" t="str">
-        <v>Buzzy Lee</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L193" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Daisy</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Daisy - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G194" t="str">
-        <v>3:02</v>
+        <v>2:45</v>
       </c>
       <c r="H194" t="str">
-        <v>Lola Blue</v>
+        <v>Jozzy</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L194" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Friend Remixes</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:57</v>
+        <v>3:21</v>
       </c>
       <c r="H195" t="str">
-        <v>james K</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L195" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Perdidos - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G196" t="str">
-        <v>2:45</v>
+        <v>4:02</v>
       </c>
       <c r="H196" t="str">
-        <v>MAVICA</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L196" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Fort</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Fort - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:27</v>
+        <v>3:51</v>
       </c>
       <c r="H197" t="str">
-        <v>Lamb</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L197" t="str">
-        <v>Fort - Lamb</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SAME LA</v>
+        <v>Delicately</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-29</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>SAME LA - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:44</v>
+        <v>3:20</v>
       </c>
       <c r="H198" t="str">
-        <v>Tiffany Day</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L198" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Working On It</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-29</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Working On It - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H199" t="str">
-        <v>Arthur Hill</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L199" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>spring cleaning</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-29</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G200" t="str">
-        <v>4:03</v>
+        <v>6:04</v>
       </c>
       <c r="H200" t="str">
-        <v>Ethan Regan</v>
+        <v>José González</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L200" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Just Drivin'</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-29</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G201" t="str">
-        <v>3:26</v>
+        <v>3:33</v>
       </c>
       <c r="H201" t="str">
-        <v>Presley Haile</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L201" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Simple Things</v>
+        <v>Daisy</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-29</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Simple Things - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:46</v>
+        <v>3:02</v>
       </c>
       <c r="H202" t="str">
-        <v>Evening Elephants</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L202" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Want It Back</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-29</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Want It Back - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G203" t="str">
-        <v>3:27</v>
+        <v>3:57</v>
       </c>
       <c r="H203" t="str">
-        <v>Giant Rooks</v>
+        <v>james K</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L203" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Bite Down</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-29</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Bite Down - Single</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:36</v>
+        <v>2:45</v>
       </c>
       <c r="H204" t="str">
-        <v>Anna Sofia</v>
+        <v>MAVICA</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L204" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Fort</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-29</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>5:42</v>
+        <v>2:27</v>
       </c>
       <c r="H205" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Lamb</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L205" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Demons</v>
+        <v>SAME LA</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-29</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>2:42</v>
+        <v>3:44</v>
       </c>
       <c r="H206" t="str">
-        <v>Anella</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L206" t="str">
-        <v>Demons - Anella</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Es brennt...</v>
+        <v>Working On It</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D207" t="str">
         <v>2026-03-29</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:35</v>
+        <v>3:06</v>
       </c>
       <c r="H207" t="str">
-        <v>Till Lindemann</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L207" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Fire Marengo</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D208" t="str">
         <v>2026-03-29</v>
@@ -8279,68 +8279,372 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>3:49</v>
+        <v>4:03</v>
       </c>
       <c r="H208" t="str">
-        <v>Enslaved</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L208" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
+        <v>Just Drivin'</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Just Drivin' - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>3:26</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Presley Haile</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Just Drivin' - Presley Haile</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Simple Things</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Simple Things - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>3:46</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Evening Elephants</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Simple Things - Evening Elephants</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Want It Back</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Want It Back - Single</v>
+      </c>
+      <c r="G211" t="str">
+        <v>3:27</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Giant Rooks</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Want It Back - Giant Rooks</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Bite Down</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Bite Down - Single</v>
+      </c>
+      <c r="G212" t="str">
+        <v>3:36</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Anna Sofia</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Bite Down - Anna Sofia</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Ulvgjeld &amp; Blodsodel</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Grand Serpent Rising</v>
+      </c>
+      <c r="G213" t="str">
+        <v>5:42</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Dimmu Borgir</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Demons</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>Ask Me How I’ve Been</v>
+      </c>
+      <c r="G214" t="str">
+        <v>2:42</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Anella</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Demons - Anella</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Es brennt...</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>Es brennt... - Single</v>
+      </c>
+      <c r="G215" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Till Lindemann</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Es brennt... - Till Lindemann</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Fire Marengo</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+      </c>
+      <c r="G216" t="str">
+        <v>3:49</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Enslaved</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Fire Marengo - Enslaved</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
         <v>Close to the Bone</v>
       </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
-      <c r="D209" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
+      <c r="D217" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G209" t="str">
+      <c r="G217" t="str">
         <v>4:09</v>
       </c>
-      <c r="H209" t="str">
+      <c r="H217" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K209" t="str">
+      <c r="K217" t="str">
         <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
-      <c r="L209" t="str">
+      <c r="L217" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L217"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L217"/>
+  <dimension ref="A1:L213"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
+        <v>שיר אמלי - אזמהניה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410257&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410260&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
+        <v>שיר אמלי - אזמהניה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתי שקד - גשם</v>
+        <v>רשל רובין - יש לי כוח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410256&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410259&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-29</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתי שקד - גשם</v>
+        <v>רשל רובין - יש לי כוח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>לידור עמירה - חלום</v>
+        <v>עברי לידר - ביונסה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410255&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410258&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-29</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>לידור עמירה - חלום</v>
+        <v>עברי לידר - ביונסה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
+        <v>ספיר סבן שלומי שבת – בליבי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410254&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>https://yosmusic.com/%d7%a1%d7%a4%d7%99%d7%a8-%d7%a1%d7%91%d7%9f-%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%91%d7%9c%d7%99%d7%91%d7%99/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-29</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>השיר “בליבי” בדואט של ספיר סבן ושלומי שבת הוא מפגש בין נוסטלגיה טלוויזיונית, זהות מוזיקלית ים־תיכונית, ורב־לשוניות רגשית. עצם החיבור ביניהם – עשור אחרי The Voice ישראל – מוסיף רובד מטא־רגשי: לא רק כשיר על געגוע, אלא גם – סגירת</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
+        <v>ספיר סבן שלומי שבת – בליבי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ישראל מועלמי - דור מלא נסיונות</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410253&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-29</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>3:56</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ישראל מועלמי - דור מלא נסיונות</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יונתן רזאל - היינו כחולמים</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410252&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-29</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יונתן רזאל - היינו כחולמים</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בר סיידו - הימים שאחריך</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410251&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-29</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>3:42</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Conan Gray</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>בר סיידו - הימים שאחריך</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נגה ארז Stuck In Heaven</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%92%d7%94-%d7%90%d7%a8%d7%96-stuck-in-heaven/</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-29</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Stuck In Heaven של נגה ארז הוא דוגמה  לפער בין סאונד פופ קצבי, כמעט “כיפי”, לבין תוכן רגשי מורכב ואפילו מטריד. זה בדיוק אחד הסימנים המסחריים של נגה ארז: מוזיקה שמרקידה אותך, בזמן שהמילים עושות לך קצת אי־נוחות. מבחינה מוזיקלית,</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>2:16</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נגה ארז Stuck In Heaven</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-29</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:56</v>
+        <v>3:08</v>
       </c>
       <c r="H10" t="str">
-        <v>Charlie Puth</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-29</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:50</v>
+        <v>3:38</v>
       </c>
       <c r="H11" t="str">
-        <v>Miley Cyrus</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-29</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:42</v>
+        <v>3:01</v>
       </c>
       <c r="H12" t="str">
-        <v>Conan Gray</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-29</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:16</v>
+        <v>3:59</v>
       </c>
       <c r="H13" t="str">
-        <v>Charlie Puth</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:08</v>
+        <v>2:59</v>
       </c>
       <c r="H14" t="str">
-        <v>Kylie Morgan</v>
+        <v>Loreen</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H15" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>3:49</v>
       </c>
       <c r="H16" t="str">
-        <v>Angelina Mango</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:59</v>
+        <v>3:22</v>
       </c>
       <c r="H17" t="str">
-        <v>Julio Iglesias</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:59</v>
+        <v>3:50</v>
       </c>
       <c r="H18" t="str">
-        <v>Loreen</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:58</v>
+        <v>6:43</v>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:49</v>
+        <v>4:52</v>
       </c>
       <c r="H20" t="str">
-        <v>Holly Humberstone</v>
+        <v>Eagles</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:22</v>
+        <v>3:13</v>
       </c>
       <c r="H21" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:50</v>
+        <v>3:28</v>
       </c>
       <c r="H22" t="str">
-        <v>Ella Langley</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>6:43</v>
+        <v>3:01</v>
       </c>
       <c r="H23" t="str">
-        <v>David Gilmour</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:52</v>
+        <v>4:00</v>
       </c>
       <c r="H24" t="str">
-        <v>Eagles</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:13</v>
+        <v>5:35</v>
       </c>
       <c r="H25" t="str">
-        <v>Moody Joody</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H26" t="str">
-        <v>Jackson Dean</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:01</v>
+        <v>3:40</v>
       </c>
       <c r="H27" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:00</v>
+        <v>2:25</v>
       </c>
       <c r="H28" t="str">
-        <v>Madison Cunningham</v>
+        <v>twocolors</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:35</v>
+        <v>3:42</v>
       </c>
       <c r="H29" t="str">
-        <v>mary in the junkyard</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-29</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:01</v>
+        <v>3:56</v>
       </c>
       <c r="H30" t="str">
-        <v>Adam Sanders</v>
+        <v>Prince</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-29</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:40</v>
+        <v>5:12</v>
       </c>
       <c r="H31" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>RAYE</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H32" t="str">
-        <v>twocolors</v>
+        <v>The Warning</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-29</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:42</v>
+        <v>3:18</v>
       </c>
       <c r="H33" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-29</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:56</v>
+        <v>3:33</v>
       </c>
       <c r="H34" t="str">
-        <v>Prince</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:12</v>
+        <v>5:53</v>
       </c>
       <c r="H35" t="str">
-        <v>RAYE</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:30</v>
+        <v>2:37</v>
       </c>
       <c r="H36" t="str">
-        <v>The Warning</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B37" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-29</v>
@@ -1784,10 +1784,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:18</v>
+        <v>2:26</v>
       </c>
       <c r="H37" t="str">
-        <v>Pentatonix</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B38" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-29</v>
@@ -1822,10 +1822,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:33</v>
+        <v>2:40</v>
       </c>
       <c r="H38" t="str">
-        <v>Tenille Townes</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-29</v>
@@ -1860,10 +1860,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>5:53</v>
+        <v>3:30</v>
       </c>
       <c r="H39" t="str">
-        <v>Jessie Ware</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-29</v>
@@ -1898,10 +1898,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:37</v>
+        <v>4:02</v>
       </c>
       <c r="H40" t="str">
-        <v>Niall Horan</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-29</v>
@@ -1936,10 +1936,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:26</v>
+        <v>3:40</v>
       </c>
       <c r="H41" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:40</v>
+        <v>2:22</v>
       </c>
       <c r="H42" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:30</v>
+        <v>3:47</v>
       </c>
       <c r="H43" t="str">
-        <v>Jackson Dean</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:02</v>
+        <v>3:39</v>
       </c>
       <c r="H44" t="str">
-        <v>Foo Fighters</v>
+        <v>Cannons</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-29</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:40</v>
+        <v>4:10</v>
       </c>
       <c r="H45" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-29</v>
@@ -2126,10 +2126,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:22</v>
+        <v>4:47</v>
       </c>
       <c r="H46" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B47" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-29</v>
@@ -2164,10 +2164,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:47</v>
+        <v>2:14</v>
       </c>
       <c r="H47" t="str">
-        <v>Ella Langley</v>
+        <v>aron!</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B48" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-29</v>
@@ -2202,10 +2202,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:39</v>
+        <v>4:00</v>
       </c>
       <c r="H48" t="str">
-        <v>Cannons</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-29</v>
@@ -2240,10 +2240,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:10</v>
+        <v>3:56</v>
       </c>
       <c r="H49" t="str">
-        <v>Luke Combs</v>
+        <v>DMA'S</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:47</v>
+        <v>3:17</v>
       </c>
       <c r="H50" t="str">
-        <v>Nessa Barrett</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H51" t="str">
-        <v>aron!</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:00</v>
+        <v>3:31</v>
       </c>
       <c r="H52" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:56</v>
+        <v>3:38</v>
       </c>
       <c r="H53" t="str">
-        <v>DMA'S</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:17</v>
+        <v>4:11</v>
       </c>
       <c r="H54" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:17</v>
+        <v>2:57</v>
       </c>
       <c r="H55" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-29</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Nick Carter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-29</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:38</v>
+        <v>7:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Carly Pearce</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-29</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:11</v>
+        <v>3:06</v>
       </c>
       <c r="H58" t="str">
-        <v>OneRepublic</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-29</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:57</v>
+        <v>3:05</v>
       </c>
       <c r="H59" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-29</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:47</v>
+        <v>3:12</v>
       </c>
       <c r="H60" t="str">
-        <v>Armin van Buuren</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-29</v>
@@ -2693,10 +2693,10 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>7:10</v>
+        <v>9:11</v>
       </c>
       <c r="H61" t="str">
         <v>David Gilmour</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-29</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:06</v>
+        <v>3:49</v>
       </c>
       <c r="H62" t="str">
-        <v>Grace Enger</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-29</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:05</v>
+        <v>3:28</v>
       </c>
       <c r="H63" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-29</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:12</v>
+        <v>3:31</v>
       </c>
       <c r="H64" t="str">
-        <v>Freya Ridings</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-29</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>9:11</v>
+        <v>3:11</v>
       </c>
       <c r="H65" t="str">
-        <v>David Gilmour</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-29</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:49</v>
+        <v>2:27</v>
       </c>
       <c r="H66" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>HAUSER</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-29</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:28</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:31</v>
+        <v>2:50</v>
       </c>
       <c r="H68" t="str">
-        <v>Martin Garrix</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H69" t="str">
-        <v>Baby Queen</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:27</v>
+        <v>2:39</v>
       </c>
       <c r="H70" t="str">
-        <v>HAUSER</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:34</v>
+        <v>5:08</v>
       </c>
       <c r="H71" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jessie J</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:50</v>
+        <v>3:46</v>
       </c>
       <c r="H72" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:51</v>
+        <v>2:42</v>
       </c>
       <c r="H73" t="str">
-        <v>Rick Astley</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:39</v>
+        <v>2:31</v>
       </c>
       <c r="H74" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>5:08</v>
+        <v>3:14</v>
       </c>
       <c r="H75" t="str">
-        <v>Jessie J</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:46</v>
+        <v>3:22</v>
       </c>
       <c r="H76" t="str">
-        <v>Bishop Briggs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:42</v>
+        <v>3:43</v>
       </c>
       <c r="H77" t="str">
-        <v>Dean Lewis</v>
+        <v>We Three</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H78" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>paris jackson</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:14</v>
+        <v>2:46</v>
       </c>
       <c r="H79" t="str">
-        <v>Luke Combs</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H80" t="str">
-        <v>Allison Russell</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:43</v>
+        <v>2:57</v>
       </c>
       <c r="H81" t="str">
-        <v>We Three</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:54</v>
+        <v>3:38</v>
       </c>
       <c r="H82" t="str">
-        <v>paris jackson</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>4:29</v>
       </c>
       <c r="H83" t="str">
-        <v>Kane Brown</v>
+        <v>Kungs</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H84" t="str">
-        <v>Lainey Wilson</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H85" t="str">
-        <v>Malcolm Todd</v>
+        <v>aron!</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:38</v>
+        <v>3:51</v>
       </c>
       <c r="H86" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:29</v>
+        <v>2:49</v>
       </c>
       <c r="H87" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-29</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:28</v>
+        <v>4:16</v>
       </c>
       <c r="H88" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-29</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>4:16</v>
       </c>
       <c r="H89" t="str">
-        <v>aron!</v>
+        <v>LANY</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-29</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:51</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-29</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:49</v>
+        <v>2:50</v>
       </c>
       <c r="H91" t="str">
-        <v>Sunday (1994)</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-29</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:16</v>
+        <v>3:57</v>
       </c>
       <c r="H92" t="str">
-        <v>Owen Riegling</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-29</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:16</v>
+        <v>3:58</v>
       </c>
       <c r="H93" t="str">
-        <v>LANY</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-29</v>
@@ -3953,7 +3953,7 @@
         <v>3:25</v>
       </c>
       <c r="H94" t="str">
-        <v>Maverick Sabre</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-29</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:50</v>
+        <v>4:09</v>
       </c>
       <c r="H95" t="str">
-        <v>Amanda Jordan</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-29</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:57</v>
+        <v>2:08</v>
       </c>
       <c r="H96" t="str">
-        <v>Beabadoobee</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-29</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:58</v>
+        <v>2:57</v>
       </c>
       <c r="H97" t="str">
-        <v>Spacey Jane</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-29</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:25</v>
+        <v>3:13</v>
       </c>
       <c r="H98" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-29</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:09</v>
+        <v>4:12</v>
       </c>
       <c r="H99" t="str">
-        <v>Mei Semones</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-29</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:08</v>
+        <v>3:57</v>
       </c>
       <c r="H100" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-29</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:57</v>
+        <v>3:34</v>
       </c>
       <c r="H101" t="str">
-        <v>Natalie Jane</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-29</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H102" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-29</v>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:12</v>
+        <v>4:58</v>
       </c>
       <c r="H103" t="str">
-        <v>David Gilmour</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-29</v>
@@ -4327,13 +4327,13 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:57</v>
+        <v>2:33</v>
       </c>
       <c r="H104" t="str">
-        <v>Far Caspian</v>
+        <v>Ellise</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,18 +4345,18 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-29</v>
@@ -4365,13 +4365,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:34</v>
+        <v>5:01</v>
       </c>
       <c r="H105" t="str">
-        <v>Celine Dion</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,18 +4383,18 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B106" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>3 weeks ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G106" t="str">
-        <v>3:48</v>
+        <v>3:18</v>
       </c>
       <c r="H106" t="str">
-        <v>Harry Styles</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L106" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B107" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>3 weeks ago</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>4:58</v>
+        <v>2:47</v>
       </c>
       <c r="H107" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L107" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B108" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>3 weeks ago</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G108" t="str">
-        <v>2:33</v>
+        <v>6:17</v>
       </c>
       <c r="H108" t="str">
-        <v>Ellise</v>
+        <v>RAYE</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L108" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>MARATHON</v>
       </c>
       <c r="B109" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>3 weeks ago</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>5:01</v>
+        <v>2:49</v>
       </c>
       <c r="H109" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Becky G</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L109" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Days We Left Behind</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:18</v>
+        <v>3:00</v>
       </c>
       <c r="H110" t="str">
-        <v>Paul McCartney</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L110" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G111" t="str">
-        <v>2:47</v>
+        <v>3:34</v>
       </c>
       <c r="H111" t="str">
-        <v>Miley Cyrus</v>
+        <v>Robyn</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L111" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>FATHER</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>BULLY</v>
       </c>
       <c r="G112" t="str">
-        <v>6:17</v>
+        <v>2:49</v>
       </c>
       <c r="H112" t="str">
-        <v>RAYE</v>
+        <v>Kanye West</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L112" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>MARATHON</v>
+        <v>Lose Control</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>MARATHON - Single</v>
+        <v>ADL</v>
       </c>
       <c r="G113" t="str">
-        <v>2:49</v>
+        <v>2:39</v>
       </c>
       <c r="H113" t="str">
-        <v>Becky G</v>
+        <v>Yeat</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L113" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ALL THE TIME</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Zavier</v>
       </c>
       <c r="G114" t="str">
-        <v>3:00</v>
+        <v>3:44</v>
       </c>
       <c r="H114" t="str">
-        <v>John Summit</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L114" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Sucker For Love</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Sexistential</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G115" t="str">
-        <v>3:34</v>
+        <v>2:07</v>
       </c>
       <c r="H115" t="str">
-        <v>Robyn</v>
+        <v>Central Cee</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L115" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>FATHER</v>
+        <v>Sideways</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>BULLY</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G116" t="str">
-        <v>2:49</v>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>Kanye West</v>
+        <v>ZAYN</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L116" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Lose Control</v>
+        <v>Automatic</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ADL</v>
+        <v>Superbloom</v>
       </c>
       <c r="G117" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H117" t="str">
-        <v>Yeat</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L117" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Zavier</v>
+        <v>Ricochet</v>
       </c>
       <c r="G118" t="str">
-        <v>3:44</v>
+        <v>3:34</v>
       </c>
       <c r="H118" t="str">
-        <v>Fetty Wap</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L118" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WAGWAN</v>
+        <v>prom queen</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:07</v>
+        <v>2:43</v>
       </c>
       <c r="H119" t="str">
-        <v>Central Cee</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L119" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Sideways</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>KONNAKOL</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:12</v>
+        <v>3:26</v>
       </c>
       <c r="H120" t="str">
-        <v>ZAYN</v>
+        <v>J Balvin</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L120" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Automatic</v>
+        <v>Phoenix</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Superbloom</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:57</v>
+        <v>2:24</v>
       </c>
       <c r="H121" t="str">
-        <v>Jessie Ware</v>
+        <v>Marshmello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L121" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tractor Beam</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Ricochet</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:34</v>
+        <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Snail Mail</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L122" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>prom queen</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>prom queen - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:43</v>
+        <v>3:36</v>
       </c>
       <c r="H123" t="str">
-        <v>Amelia Moore</v>
+        <v>Eli</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L123" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Pal Agua</v>
+        <v>Lonely</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G124" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>J Balvin</v>
+        <v>Fcukers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L124" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Phoenix</v>
+        <v>Back in Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Phoenix - Single</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:24</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Marshmello</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L125" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Sideways</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G126" t="str">
-        <v>2:56</v>
+        <v>3:55</v>
       </c>
       <c r="H126" t="str">
-        <v>Ne-Yo</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L126" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Feel Your Rain</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G127" t="str">
-        <v>3:36</v>
+        <v>4:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Eli</v>
+        <v>Flea</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L127" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Lonely</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Ö</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G128" t="str">
         <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Fcukers</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L128" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Back in Love</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Back in Love - Single</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L129" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Sideways</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G130" t="str">
-        <v>3:55</v>
+        <v>4:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Charlie Puth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L130" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>wasteland</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Honora</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:22</v>
+        <v>3:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Flea</v>
+        <v>Yuna</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L131" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G132" t="str">
-        <v>2:58</v>
+        <v>2:31</v>
       </c>
       <c r="H132" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Artemas</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L132" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>Por LA</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G133" t="str">
-        <v>3:02</v>
+        <v>2:19</v>
       </c>
       <c r="H133" t="str">
-        <v>Honey Bxby</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L133" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>One Thing At A Time</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Creature of Habit</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G134" t="str">
-        <v>4:42</v>
+        <v>4:14</v>
       </c>
       <c r="H134" t="str">
-        <v>Courtney Barnett</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L134" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>wasteland</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>wasteland - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G135" t="str">
-        <v>3:05</v>
+        <v>4:18</v>
       </c>
       <c r="H135" t="str">
-        <v>Yuna</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L135" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>getting up to no good</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H136" t="str">
-        <v>Artemas</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L136" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Por LA</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>TODO Ø NADA</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:19</v>
+        <v>2:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Linea Personal</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L137" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>You Lead Me</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G138" t="str">
-        <v>4:14</v>
+        <v>3:17</v>
       </c>
       <c r="H138" t="str">
-        <v>Lauren Daigle</v>
+        <v>ERNEST</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L138" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Just A Kid</v>
+        <v>Special</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Broken View</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G139" t="str">
-        <v>4:18</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>Sam Barber</v>
+        <v>Elmiene</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L139" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Country And She Knows It</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G140" t="str">
-        <v>2:54</v>
+        <v>2:52</v>
       </c>
       <c r="H140" t="str">
-        <v>Luke Bryan</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L140" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Georgia On My Mind</v>
+        <v>STAY</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:35</v>
+        <v>3:06</v>
       </c>
       <c r="H141" t="str">
-        <v>Thomas Rhett</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L141" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Deep Blue</v>
+        <v>Unglued</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Deep Blue</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G142" t="str">
-        <v>3:17</v>
+        <v>3:54</v>
       </c>
       <c r="H142" t="str">
-        <v>ERNEST</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L142" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Special</v>
+        <v>Ritual</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>sounds for someone</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:49</v>
+        <v>3:01</v>
       </c>
       <c r="H143" t="str">
-        <v>Elmiene</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L143" t="str">
-        <v>Special - Elmiene</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Heart Attack</v>
+        <v>The Best</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>CANDY</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>2:52</v>
+        <v>3:48</v>
       </c>
       <c r="H144" t="str">
-        <v>Justine Skye</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L144" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>STAY</v>
+        <v>Smile</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>STAY - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:06</v>
+        <v>3:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Stray Kids</v>
+        <v>Two Shell</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L145" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Unglued</v>
+        <v>Duro</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Work of Heart</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:54</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Skrillex</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L146" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Ritual</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Ritual - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>2:58</v>
       </c>
       <c r="H147" t="str">
-        <v>Icona Pop</v>
+        <v>Sublime</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L147" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>The Best</v>
+        <v>Carousel</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G148" t="str">
-        <v>3:48</v>
+        <v>3:36</v>
       </c>
       <c r="H148" t="str">
-        <v>Conan Gray</v>
+        <v>Cannons</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L148" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Smile</v>
+        <v>Mercy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Smile - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:50</v>
+        <v>3:49</v>
       </c>
       <c r="H149" t="str">
-        <v>Two Shell</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L149" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Duro</v>
+        <v>Palms</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Duro - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:05</v>
+        <v>3:18</v>
       </c>
       <c r="H150" t="str">
-        <v>Skrillex</v>
+        <v>The Maine</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L150" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:58</v>
+        <v>5:28</v>
       </c>
       <c r="H151" t="str">
-        <v>Sublime</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L151" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Carousel</v>
+        <v>Danger</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Everything Glows</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:36</v>
+        <v>2:19</v>
       </c>
       <c r="H152" t="str">
-        <v>Cannons</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L152" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mercy</v>
+        <v>Icarus</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Mercy - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:49</v>
+        <v>4:25</v>
       </c>
       <c r="H153" t="str">
-        <v>PRESIDENT</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L153" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Palms</v>
+        <v>idk idk</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Palms - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:18</v>
+        <v>2:26</v>
       </c>
       <c r="H154" t="str">
-        <v>The Maine</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L154" t="str">
-        <v>Palms - The Maine</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ozzy's Song</v>
+        <v>Tonight</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>5:28</v>
+        <v>2:25</v>
       </c>
       <c r="H155" t="str">
-        <v>Black Label Society</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L155" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Danger</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Danger - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G156" t="str">
-        <v>2:19</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Nia Archives</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L156" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Icarus</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Icarus - Single</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>4:25</v>
+        <v>2:45</v>
       </c>
       <c r="H157" t="str">
-        <v>Olivia O'Brien</v>
+        <v>BIA</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L157" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>idk idk</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>idk idk - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G158" t="str">
-        <v>2:26</v>
+        <v>3:33</v>
       </c>
       <c r="H158" t="str">
-        <v>Jim Legxacy</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L158" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Tonight</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tonight - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G159" t="str">
-        <v>2:25</v>
+        <v>3:44</v>
       </c>
       <c r="H159" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L159" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Switcheroo</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>3:44</v>
+        <v>2:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Gelli Haha</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L160" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>R3verse</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>takeaways</v>
       </c>
       <c r="G161" t="str">
-        <v>2:45</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>BIA</v>
+        <v>Medium Build</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L161" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>this girl wants everything</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G162" t="str">
-        <v>3:33</v>
+        <v>2:32</v>
       </c>
       <c r="H162" t="str">
-        <v>Isaia Huron</v>
+        <v>MIKE</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L162" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>heart of gold</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:44</v>
+        <v>2:51</v>
       </c>
       <c r="H163" t="str">
-        <v>Slayyyter</v>
+        <v>kai devega</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L163" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Deep Water - EP</v>
+        <v>Skeletor</v>
       </c>
       <c r="G164" t="str">
-        <v>2:41</v>
+        <v>4:21</v>
       </c>
       <c r="H164" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L164" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>R3verse</v>
+        <v>Dream House</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>takeaways</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:31</v>
+        <v>2:54</v>
       </c>
       <c r="H165" t="str">
-        <v>Medium Build</v>
+        <v>Empress Of</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L165" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H166" t="str">
-        <v>MIKE</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L166" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>heart of gold</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>heart of gold - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H167" t="str">
-        <v>kai devega</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L167" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Breaking Down</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Skeletor</v>
+        <v>Forever Now</v>
       </c>
       <c r="G168" t="str">
-        <v>4:21</v>
+        <v>4:05</v>
       </c>
       <c r="H168" t="str">
-        <v>Chief Keef</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L168" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Dream House</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dream House - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>2:54</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Empress Of</v>
+        <v>Benny G</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L169" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Baby Blue</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:51</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Cody Simpson</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L170" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>2:37</v>
+        <v>4:19</v>
       </c>
       <c r="H171" t="str">
-        <v>MEDUZA</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L171" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Forever Now</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:05</v>
+        <v>2:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Switchfoot</v>
+        <v>WesGhost</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L172" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:46</v>
+        <v>3:17</v>
       </c>
       <c r="H173" t="str">
-        <v>Benny G</v>
+        <v>GERD</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L173" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H174" t="str">
-        <v>Eric Bellinger</v>
+        <v>Prospa</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L174" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:19</v>
+        <v>2:51</v>
       </c>
       <c r="H175" t="str">
-        <v>Anish Kumar</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L175" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>GASLIGHT</v>
+        <v>Breathe</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:10</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>WesGhost</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L176" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Truth To Be Told</v>
+        <v>xs</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:17</v>
+        <v>3:19</v>
       </c>
       <c r="H177" t="str">
-        <v>GERD</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L177" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Free Your Mind</v>
+        <v>Sail</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G178" t="str">
-        <v>3:21</v>
+        <v>4:54</v>
       </c>
       <c r="H178" t="str">
-        <v>Prospa</v>
+        <v>Future Islands</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L178" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Down To The Bone</v>
+        <v>Dreaming</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G179" t="str">
-        <v>2:51</v>
+        <v>3:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Josh Baker</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L179" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Breathe</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Breathe - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G180" t="str">
-        <v>2:48</v>
+        <v>2:39</v>
       </c>
       <c r="H180" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Armanii</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L180" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>xs</v>
+        <v>La Opinión</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>xs - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G181" t="str">
-        <v>3:19</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Ashley Cooke</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L181" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Sail</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:54</v>
+        <v>3:24</v>
       </c>
       <c r="H182" t="str">
-        <v>Future Islands</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L182" t="str">
-        <v>Sail - Future Islands</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Dreaming</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Dear Nashville</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:33</v>
+        <v>2:43</v>
       </c>
       <c r="H183" t="str">
-        <v>Ashley Monroe</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L183" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>NEW TINGZ</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:39</v>
+        <v>2:16</v>
       </c>
       <c r="H184" t="str">
-        <v>Armanii</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L184" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>La Opinión</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Mis Compas El Final</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:23</v>
+        <v>2:56</v>
       </c>
       <c r="H185" t="str">
-        <v>Joss Favela</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L185" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>qué ves en mí?</v>
+        <v>Me Neither</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G186" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H186" t="str">
-        <v>Paloma Morphy</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L186" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G187" t="str">
-        <v>2:43</v>
+        <v>2:48</v>
       </c>
       <c r="H187" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L187" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>TUTUTU</v>
+        <v>Wonder</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:16</v>
+        <v>3:48</v>
       </c>
       <c r="H188" t="str">
-        <v>ELENA ROSE</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L188" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>ICU</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:56</v>
+        <v>2:53</v>
       </c>
       <c r="H189" t="str">
-        <v>2'Live Bre</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L189" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Me Neither</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G190" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H190" t="str">
-        <v>Ty Myers</v>
+        <v>Jozzy</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L190" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Cole Palmer</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Solid Ground</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>Limoblaze</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L191" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Wonder</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Wonder - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G192" t="str">
-        <v>3:48</v>
+        <v>4:02</v>
       </c>
       <c r="H192" t="str">
-        <v>Meeks Carter</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L192" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>ICU</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>ICU - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:53</v>
+        <v>3:51</v>
       </c>
       <c r="H193" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L193" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Delicately</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:45</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>Jozzy</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L194" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Waiting Room</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Waiting Room - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:21</v>
+        <v>3:27</v>
       </c>
       <c r="H195" t="str">
-        <v>Jenevieve</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L195" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Rise</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G196" t="str">
-        <v>4:02</v>
+        <v>6:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Melissa Etheridge</v>
+        <v>José González</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L196" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Roll On Thru</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G197" t="str">
-        <v>3:51</v>
+        <v>3:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Hayden Everett</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L197" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Delicately</v>
+        <v>Daisy</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-29</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Delicately - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:20</v>
+        <v>3:02</v>
       </c>
       <c r="H198" t="str">
-        <v>Andrea Bejar</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L198" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>One Of Those Things</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-29</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G199" t="str">
-        <v>3:27</v>
+        <v>3:57</v>
       </c>
       <c r="H199" t="str">
-        <v>Lucy Clearwater</v>
+        <v>james K</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L199" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>For Every Dusk</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-29</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>6:04</v>
+        <v>2:45</v>
       </c>
       <c r="H200" t="str">
-        <v>José González</v>
+        <v>MAVICA</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L200" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>I'll Wait</v>
+        <v>Fort</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-29</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:33</v>
+        <v>2:27</v>
       </c>
       <c r="H201" t="str">
-        <v>Buzzy Lee</v>
+        <v>Lamb</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L201" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Daisy</v>
+        <v>SAME LA</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-29</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Daisy - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:02</v>
+        <v>3:44</v>
       </c>
       <c r="H202" t="str">
-        <v>Lola Blue</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L202" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Working On It</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-29</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Friend Remixes</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H203" t="str">
-        <v>james K</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L203" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-29</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Perdidos - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:45</v>
+        <v>4:03</v>
       </c>
       <c r="H204" t="str">
-        <v>MAVICA</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L204" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Fort</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-29</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Fort - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>2:27</v>
+        <v>3:26</v>
       </c>
       <c r="H205" t="str">
-        <v>Lamb</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L205" t="str">
-        <v>Fort - Lamb</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SAME LA</v>
+        <v>Simple Things</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-29</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>SAME LA - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:44</v>
+        <v>3:46</v>
       </c>
       <c r="H206" t="str">
-        <v>Tiffany Day</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L206" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Working On It</v>
+        <v>Want It Back</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D207" t="str">
         <v>2026-03-29</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Working On It - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H207" t="str">
-        <v>Arthur Hill</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L207" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>spring cleaning</v>
+        <v>Bite Down</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D208" t="str">
         <v>2026-03-29</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>4:03</v>
+        <v>3:36</v>
       </c>
       <c r="H208" t="str">
-        <v>Ethan Regan</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L208" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Just Drivin'</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D209" t="str">
         <v>2026-03-29</v>
@@ -8317,36 +8317,36 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G209" t="str">
-        <v>3:26</v>
+        <v>5:42</v>
       </c>
       <c r="H209" t="str">
-        <v>Presley Haile</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L209" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Simple Things</v>
+        <v>Demons</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D210" t="str">
         <v>2026-03-29</v>
@@ -8355,36 +8355,36 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Simple Things - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G210" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H210" t="str">
-        <v>Evening Elephants</v>
+        <v>Anella</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L210" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Want It Back</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D211" t="str">
         <v>2026-03-29</v>
@@ -8393,36 +8393,36 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Want It Back - Single</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G211" t="str">
-        <v>3:27</v>
+        <v>3:35</v>
       </c>
       <c r="H211" t="str">
-        <v>Giant Rooks</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L211" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Bite Down</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D212" t="str">
         <v>2026-03-29</v>
@@ -8431,36 +8431,36 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>Bite Down - Single</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G212" t="str">
-        <v>3:36</v>
+        <v>3:49</v>
       </c>
       <c r="H212" t="str">
-        <v>Anna Sofia</v>
+        <v>Enslaved</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L212" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B213" t="str">
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D213" t="str">
         <v>2026-03-29</v>
@@ -8469,182 +8469,30 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G213" t="str">
-        <v>5:42</v>
+        <v>4:09</v>
       </c>
       <c r="H213" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I213" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L213" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Demons</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>Ask Me How I’ve Been</v>
-      </c>
-      <c r="G214" t="str">
-        <v>2:42</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Anella</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
-      </c>
-      <c r="L214" t="str">
-        <v>Demons - Anella</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Es brennt...</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Es brennt... - Single</v>
-      </c>
-      <c r="G215" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Till Lindemann</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
-      </c>
-      <c r="L215" t="str">
-        <v>Es brennt... - Till Lindemann</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Fire Marengo</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
-      </c>
-      <c r="G216" t="str">
-        <v>3:49</v>
-      </c>
-      <c r="H216" t="str">
-        <v>Enslaved</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
-      </c>
-      <c r="L216" t="str">
-        <v>Fire Marengo - Enslaved</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Close to the Bone</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G217" t="str">
-        <v>4:09</v>
-      </c>
-      <c r="H217" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I217" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J217" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K217" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
-      </c>
-      <c r="L217" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L217"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר אמלי - אזמהניה</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-29</v>
+        <v>2d ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410260&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:56</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר אמלי - אזמהניה</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רשל רובין - יש לי כוח</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-29</v>
+        <v>2d ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410259&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רשל רובין - יש לי כוח</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עברי לידר - ביונסה</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-29</v>
+        <v>2d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410258&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>3:42</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Conan Gray</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עברי לידר - ביונסה</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ספיר סבן שלומי שבת – בליבי</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-29</v>
+        <v>2d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%a4%d7%99%d7%a8-%d7%a1%d7%91%d7%9f-%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%91%d7%9c%d7%99%d7%91%d7%99/</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>השיר “בליבי” בדואט של ספיר סבן ושלומי שבת הוא מפגש בין נוסטלגיה טלוויזיונית, זהות מוזיקלית ים־תיכונית, ורב־לשוניות רגשית. עצם החיבור ביניהם – עשור אחרי The Voice ישראל – מוסיף רובד מטא־רגשי: לא רק כשיר על געגוע, אלא גם – סגירת</v>
+        <v>2d ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2:16</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ספיר סבן שלומי שבת – בליבי</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:56</v>
+        <v>3:08</v>
       </c>
       <c r="H6" t="str">
-        <v>Charlie Puth</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:50</v>
+        <v>3:38</v>
       </c>
       <c r="H7" t="str">
-        <v>Miley Cyrus</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:42</v>
+        <v>3:01</v>
       </c>
       <c r="H8" t="str">
-        <v>Conan Gray</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:16</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>Charlie Puth</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:08</v>
+        <v>2:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Kylie Morgan</v>
+        <v>Loreen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:01</v>
+        <v>3:49</v>
       </c>
       <c r="H12" t="str">
-        <v>Angelina Mango</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:59</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>Julio Iglesias</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:59</v>
+        <v>3:50</v>
       </c>
       <c r="H14" t="str">
-        <v>Loreen</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:58</v>
+        <v>6:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Jessie Ware</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:49</v>
+        <v>4:52</v>
       </c>
       <c r="H16" t="str">
-        <v>Holly Humberstone</v>
+        <v>Eagles</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:22</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:50</v>
+        <v>3:28</v>
       </c>
       <c r="H18" t="str">
-        <v>Ella Langley</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G19" t="str">
-        <v>6:43</v>
+        <v>3:01</v>
       </c>
       <c r="H19" t="str">
-        <v>David Gilmour</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:52</v>
+        <v>4:00</v>
       </c>
       <c r="H20" t="str">
-        <v>Eagles</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:13</v>
+        <v>5:35</v>
       </c>
       <c r="H21" t="str">
-        <v>Moody Joody</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Jackson Dean</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:01</v>
+        <v>3:40</v>
       </c>
       <c r="H23" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:00</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Madison Cunningham</v>
+        <v>twocolors</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G25" t="str">
-        <v>5:35</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>mary in the junkyard</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:01</v>
+        <v>3:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Adam Sanders</v>
+        <v>Prince</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:40</v>
+        <v>5:12</v>
       </c>
       <c r="H27" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>RAYE</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H28" t="str">
-        <v>twocolors</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:42</v>
+        <v>3:18</v>
       </c>
       <c r="H29" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:56</v>
+        <v>3:33</v>
       </c>
       <c r="H30" t="str">
-        <v>Prince</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:12</v>
+        <v>5:53</v>
       </c>
       <c r="H31" t="str">
-        <v>RAYE</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:30</v>
+        <v>2:37</v>
       </c>
       <c r="H32" t="str">
-        <v>The Warning</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:18</v>
+        <v>2:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Pentatonix</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:33</v>
+        <v>2:40</v>
       </c>
       <c r="H34" t="str">
-        <v>Tenille Townes</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:53</v>
+        <v>3:30</v>
       </c>
       <c r="H35" t="str">
-        <v>Jessie Ware</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:37</v>
+        <v>4:02</v>
       </c>
       <c r="H36" t="str">
-        <v>Niall Horan</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:26</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:40</v>
+        <v>2:22</v>
       </c>
       <c r="H38" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:30</v>
+        <v>3:47</v>
       </c>
       <c r="H39" t="str">
-        <v>Jackson Dean</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:02</v>
+        <v>3:39</v>
       </c>
       <c r="H40" t="str">
-        <v>Foo Fighters</v>
+        <v>Cannons</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:40</v>
+        <v>4:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:22</v>
+        <v>4:47</v>
       </c>
       <c r="H42" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:47</v>
+        <v>2:14</v>
       </c>
       <c r="H43" t="str">
-        <v>Ella Langley</v>
+        <v>aron!</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:39</v>
+        <v>4:00</v>
       </c>
       <c r="H44" t="str">
-        <v>Cannons</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:10</v>
+        <v>3:56</v>
       </c>
       <c r="H45" t="str">
-        <v>Luke Combs</v>
+        <v>DMA'S</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:47</v>
+        <v>3:17</v>
       </c>
       <c r="H46" t="str">
-        <v>Nessa Barrett</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>aron!</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:00</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:56</v>
+        <v>3:38</v>
       </c>
       <c r="H49" t="str">
-        <v>DMA'S</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:17</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:17</v>
+        <v>2:57</v>
       </c>
       <c r="H51" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Nick Carter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:38</v>
+        <v>7:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Carly Pearce</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:11</v>
+        <v>3:06</v>
       </c>
       <c r="H54" t="str">
-        <v>OneRepublic</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:57</v>
+        <v>3:05</v>
       </c>
       <c r="H55" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>3:12</v>
       </c>
       <c r="H56" t="str">
-        <v>Armin van Buuren</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,30 +2521,30 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
-        <v>7:10</v>
+        <v>9:11</v>
       </c>
       <c r="H57" t="str">
         <v>David Gilmour</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:06</v>
+        <v>3:49</v>
       </c>
       <c r="H58" t="str">
-        <v>Grace Enger</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:05</v>
+        <v>3:28</v>
       </c>
       <c r="H59" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:12</v>
+        <v>3:31</v>
       </c>
       <c r="H60" t="str">
-        <v>Freya Ridings</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
-        <v>9:11</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>David Gilmour</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:49</v>
+        <v>2:27</v>
       </c>
       <c r="H62" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>HAUSER</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:28</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:31</v>
+        <v>2:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Martin Garrix</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H65" t="str">
-        <v>Baby Queen</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:27</v>
+        <v>2:39</v>
       </c>
       <c r="H66" t="str">
-        <v>HAUSER</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>5:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jessie J</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:50</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:51</v>
+        <v>2:42</v>
       </c>
       <c r="H69" t="str">
-        <v>Rick Astley</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:39</v>
+        <v>2:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:08</v>
+        <v>3:14</v>
       </c>
       <c r="H71" t="str">
-        <v>Jessie J</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:46</v>
+        <v>3:22</v>
       </c>
       <c r="H72" t="str">
-        <v>Bishop Briggs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:42</v>
+        <v>3:43</v>
       </c>
       <c r="H73" t="str">
-        <v>Dean Lewis</v>
+        <v>We Three</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H74" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>paris jackson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:14</v>
+        <v>2:46</v>
       </c>
       <c r="H75" t="str">
-        <v>Luke Combs</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Allison Russell</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:43</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>We Three</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:54</v>
+        <v>3:38</v>
       </c>
       <c r="H78" t="str">
-        <v>paris jackson</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:46</v>
+        <v>4:29</v>
       </c>
       <c r="H79" t="str">
-        <v>Kane Brown</v>
+        <v>Kungs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H80" t="str">
-        <v>Lainey Wilson</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Malcolm Todd</v>
+        <v>aron!</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:38</v>
+        <v>3:51</v>
       </c>
       <c r="H82" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:29</v>
+        <v>2:49</v>
       </c>
       <c r="H83" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:28</v>
+        <v>4:16</v>
       </c>
       <c r="H84" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:26</v>
+        <v>4:16</v>
       </c>
       <c r="H85" t="str">
-        <v>aron!</v>
+        <v>LANY</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:51</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:49</v>
+        <v>2:50</v>
       </c>
       <c r="H87" t="str">
-        <v>Sunday (1994)</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:16</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Owen Riegling</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:16</v>
+        <v>3:58</v>
       </c>
       <c r="H89" t="str">
-        <v>LANY</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Maverick Sabre</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:50</v>
+        <v>4:09</v>
       </c>
       <c r="H91" t="str">
-        <v>Amanda Jordan</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:57</v>
+        <v>2:08</v>
       </c>
       <c r="H92" t="str">
-        <v>Beabadoobee</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:58</v>
+        <v>2:57</v>
       </c>
       <c r="H93" t="str">
-        <v>Spacey Jane</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:25</v>
+        <v>3:13</v>
       </c>
       <c r="H94" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:09</v>
+        <v>4:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Mei Semones</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:08</v>
+        <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:57</v>
+        <v>3:34</v>
       </c>
       <c r="H97" t="str">
-        <v>Natalie Jane</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H98" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:12</v>
+        <v>4:58</v>
       </c>
       <c r="H99" t="str">
-        <v>David Gilmour</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:57</v>
+        <v>2:33</v>
       </c>
       <c r="H100" t="str">
-        <v>Far Caspian</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:34</v>
+        <v>5:01</v>
       </c>
       <c r="H101" t="str">
-        <v>Celine Dion</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,4268 +4231,4116 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G102" t="str">
-        <v>3:48</v>
+        <v>3:18</v>
       </c>
       <c r="H102" t="str">
-        <v>Harry Styles</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L102" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B103" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>3 weeks ago</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>4:58</v>
+        <v>2:47</v>
       </c>
       <c r="H103" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L103" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B104" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>3 weeks ago</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G104" t="str">
-        <v>2:33</v>
+        <v>6:17</v>
       </c>
       <c r="H104" t="str">
-        <v>Ellise</v>
+        <v>RAYE</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L104" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>MARATHON</v>
       </c>
       <c r="B105" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>3 weeks ago</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>5:01</v>
+        <v>2:49</v>
       </c>
       <c r="H105" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Becky G</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L105" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Days We Left Behind</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:18</v>
+        <v>3:00</v>
       </c>
       <c r="H106" t="str">
-        <v>Paul McCartney</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L106" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G107" t="str">
-        <v>2:47</v>
+        <v>3:34</v>
       </c>
       <c r="H107" t="str">
-        <v>Miley Cyrus</v>
+        <v>Robyn</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L107" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>FATHER</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>BULLY</v>
       </c>
       <c r="G108" t="str">
-        <v>6:17</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>RAYE</v>
+        <v>Kanye West</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L108" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>MARATHON</v>
+        <v>Lose Control</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>MARATHON - Single</v>
+        <v>ADL</v>
       </c>
       <c r="G109" t="str">
-        <v>2:49</v>
+        <v>2:39</v>
       </c>
       <c r="H109" t="str">
-        <v>Becky G</v>
+        <v>Yeat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L109" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ALL THE TIME</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Zavier</v>
       </c>
       <c r="G110" t="str">
-        <v>3:00</v>
+        <v>3:44</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L110" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Sucker For Love</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Sexistential</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G111" t="str">
-        <v>3:34</v>
+        <v>2:07</v>
       </c>
       <c r="H111" t="str">
-        <v>Robyn</v>
+        <v>Central Cee</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L111" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>FATHER</v>
+        <v>Sideways</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>BULLY</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G112" t="str">
-        <v>2:49</v>
+        <v>3:12</v>
       </c>
       <c r="H112" t="str">
-        <v>Kanye West</v>
+        <v>ZAYN</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L112" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Lose Control</v>
+        <v>Automatic</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ADL</v>
+        <v>Superbloom</v>
       </c>
       <c r="G113" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H113" t="str">
-        <v>Yeat</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L113" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Zavier</v>
+        <v>Ricochet</v>
       </c>
       <c r="G114" t="str">
-        <v>3:44</v>
+        <v>3:34</v>
       </c>
       <c r="H114" t="str">
-        <v>Fetty Wap</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L114" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WAGWAN</v>
+        <v>prom queen</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:07</v>
+        <v>2:43</v>
       </c>
       <c r="H115" t="str">
-        <v>Central Cee</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L115" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Sideways</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>KONNAKOL</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>3:26</v>
       </c>
       <c r="H116" t="str">
-        <v>ZAYN</v>
+        <v>J Balvin</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L116" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Automatic</v>
+        <v>Phoenix</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Superbloom</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:57</v>
+        <v>2:24</v>
       </c>
       <c r="H117" t="str">
-        <v>Jessie Ware</v>
+        <v>Marshmello</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L117" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Tractor Beam</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Ricochet</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:34</v>
+        <v>2:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Snail Mail</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L118" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>prom queen</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>prom queen - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:43</v>
+        <v>3:36</v>
       </c>
       <c r="H119" t="str">
-        <v>Amelia Moore</v>
+        <v>Eli</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L119" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Pal Agua</v>
+        <v>Lonely</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G120" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H120" t="str">
-        <v>J Balvin</v>
+        <v>Fcukers</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L120" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Phoenix</v>
+        <v>Back in Love</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Phoenix - Single</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:24</v>
+        <v>3:14</v>
       </c>
       <c r="H121" t="str">
-        <v>Marshmello</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L121" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Sideways</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G122" t="str">
-        <v>2:56</v>
+        <v>3:55</v>
       </c>
       <c r="H122" t="str">
-        <v>Ne-Yo</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L122" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Feel Your Rain</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G123" t="str">
-        <v>3:36</v>
+        <v>4:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>Flea</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L123" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Lonely</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ö</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G124" t="str">
         <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>Fcukers</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L124" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Back in Love</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Back in Love - Single</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L125" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sideways</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G126" t="str">
-        <v>3:55</v>
+        <v>4:42</v>
       </c>
       <c r="H126" t="str">
-        <v>Charlie Puth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L126" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>wasteland</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Honora</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:22</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Flea</v>
+        <v>Yuna</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>2:31</v>
       </c>
       <c r="H128" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Artemas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>Por LA</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G129" t="str">
-        <v>3:02</v>
+        <v>2:19</v>
       </c>
       <c r="H129" t="str">
-        <v>Honey Bxby</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L129" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>One Thing At A Time</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Creature of Habit</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G130" t="str">
-        <v>4:42</v>
+        <v>4:14</v>
       </c>
       <c r="H130" t="str">
-        <v>Courtney Barnett</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L130" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>wasteland</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>wasteland - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G131" t="str">
-        <v>3:05</v>
+        <v>4:18</v>
       </c>
       <c r="H131" t="str">
-        <v>Yuna</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L131" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>getting up to no good</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H132" t="str">
-        <v>Artemas</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L132" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Por LA</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>TODO Ø NADA</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:19</v>
+        <v>2:35</v>
       </c>
       <c r="H133" t="str">
-        <v>Linea Personal</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L133" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>You Lead Me</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G134" t="str">
-        <v>4:14</v>
+        <v>3:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Lauren Daigle</v>
+        <v>ERNEST</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L134" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Just A Kid</v>
+        <v>Special</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Broken View</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G135" t="str">
-        <v>4:18</v>
+        <v>2:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Sam Barber</v>
+        <v>Elmiene</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L135" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Country And She Knows It</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G136" t="str">
-        <v>2:54</v>
+        <v>2:52</v>
       </c>
       <c r="H136" t="str">
-        <v>Luke Bryan</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L136" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Georgia On My Mind</v>
+        <v>STAY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:35</v>
+        <v>3:06</v>
       </c>
       <c r="H137" t="str">
-        <v>Thomas Rhett</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L137" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Deep Blue</v>
+        <v>Unglued</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Deep Blue</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G138" t="str">
-        <v>3:17</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>ERNEST</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L138" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Special</v>
+        <v>Ritual</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>sounds for someone</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>3:01</v>
       </c>
       <c r="H139" t="str">
-        <v>Elmiene</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L139" t="str">
-        <v>Special - Elmiene</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Heart Attack</v>
+        <v>The Best</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>CANDY</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:52</v>
+        <v>3:48</v>
       </c>
       <c r="H140" t="str">
-        <v>Justine Skye</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L140" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>STAY</v>
+        <v>Smile</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>STAY - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:06</v>
+        <v>3:50</v>
       </c>
       <c r="H141" t="str">
-        <v>Stray Kids</v>
+        <v>Two Shell</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L141" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Unglued</v>
+        <v>Duro</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:54</v>
+        <v>3:05</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Skrillex</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L142" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ritual</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Ritual - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G143" t="str">
-        <v>3:01</v>
+        <v>2:58</v>
       </c>
       <c r="H143" t="str">
-        <v>Icona Pop</v>
+        <v>Sublime</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L143" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Best</v>
+        <v>Carousel</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G144" t="str">
-        <v>3:48</v>
+        <v>3:36</v>
       </c>
       <c r="H144" t="str">
-        <v>Conan Gray</v>
+        <v>Cannons</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L144" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Smile</v>
+        <v>Mercy</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Smile - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:50</v>
+        <v>3:49</v>
       </c>
       <c r="H145" t="str">
-        <v>Two Shell</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L145" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Duro</v>
+        <v>Palms</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Duro - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>3:18</v>
       </c>
       <c r="H146" t="str">
-        <v>Skrillex</v>
+        <v>The Maine</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L146" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G147" t="str">
-        <v>2:58</v>
+        <v>5:28</v>
       </c>
       <c r="H147" t="str">
-        <v>Sublime</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L147" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Carousel</v>
+        <v>Danger</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Everything Glows</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:36</v>
+        <v>2:19</v>
       </c>
       <c r="H148" t="str">
-        <v>Cannons</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L148" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Mercy</v>
+        <v>Icarus</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Mercy - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:49</v>
+        <v>4:25</v>
       </c>
       <c r="H149" t="str">
-        <v>PRESIDENT</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L149" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Palms</v>
+        <v>idk idk</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Palms - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:18</v>
+        <v>2:26</v>
       </c>
       <c r="H150" t="str">
-        <v>The Maine</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L150" t="str">
-        <v>Palms - The Maine</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ozzy's Song</v>
+        <v>Tonight</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:28</v>
+        <v>2:25</v>
       </c>
       <c r="H151" t="str">
-        <v>Black Label Society</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L151" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Danger</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Danger - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G152" t="str">
-        <v>2:19</v>
+        <v>3:44</v>
       </c>
       <c r="H152" t="str">
-        <v>Nia Archives</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L152" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Icarus</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Icarus - Single</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G153" t="str">
-        <v>4:25</v>
+        <v>2:45</v>
       </c>
       <c r="H153" t="str">
-        <v>Olivia O'Brien</v>
+        <v>BIA</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L153" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>idk idk</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>idk idk - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G154" t="str">
-        <v>2:26</v>
+        <v>3:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Jim Legxacy</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L154" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tonight</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Tonight - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G155" t="str">
-        <v>2:25</v>
+        <v>3:44</v>
       </c>
       <c r="H155" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L155" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Switcheroo</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>2:41</v>
       </c>
       <c r="H156" t="str">
-        <v>Gelli Haha</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L156" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>R3verse</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>takeaways</v>
       </c>
       <c r="G157" t="str">
-        <v>2:45</v>
+        <v>3:31</v>
       </c>
       <c r="H157" t="str">
-        <v>BIA</v>
+        <v>Medium Build</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L157" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>this girl wants everything</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G158" t="str">
-        <v>3:33</v>
+        <v>2:32</v>
       </c>
       <c r="H158" t="str">
-        <v>Isaia Huron</v>
+        <v>MIKE</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L158" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>heart of gold</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:44</v>
+        <v>2:51</v>
       </c>
       <c r="H159" t="str">
-        <v>Slayyyter</v>
+        <v>kai devega</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L159" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Deep Water - EP</v>
+        <v>Skeletor</v>
       </c>
       <c r="G160" t="str">
-        <v>2:41</v>
+        <v>4:21</v>
       </c>
       <c r="H160" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L160" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>R3verse</v>
+        <v>Dream House</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>takeaways</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:31</v>
+        <v>2:54</v>
       </c>
       <c r="H161" t="str">
-        <v>Medium Build</v>
+        <v>Empress Of</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L161" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H162" t="str">
-        <v>MIKE</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L162" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>heart of gold</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>heart of gold - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H163" t="str">
-        <v>kai devega</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L163" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Breaking Down</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Skeletor</v>
+        <v>Forever Now</v>
       </c>
       <c r="G164" t="str">
-        <v>4:21</v>
+        <v>4:05</v>
       </c>
       <c r="H164" t="str">
-        <v>Chief Keef</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L164" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Dream House</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream House - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>3:46</v>
       </c>
       <c r="H165" t="str">
-        <v>Empress Of</v>
+        <v>Benny G</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L165" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Baby Blue</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:51</v>
+        <v>3:03</v>
       </c>
       <c r="H166" t="str">
-        <v>Cody Simpson</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L166" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>2:37</v>
+        <v>4:19</v>
       </c>
       <c r="H167" t="str">
-        <v>MEDUZA</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Forever Now</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:05</v>
+        <v>2:10</v>
       </c>
       <c r="H168" t="str">
-        <v>Switchfoot</v>
+        <v>WesGhost</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L168" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:46</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Benny G</v>
+        <v>GERD</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L169" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H170" t="str">
-        <v>Eric Bellinger</v>
+        <v>Prospa</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L170" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:19</v>
+        <v>2:51</v>
       </c>
       <c r="H171" t="str">
-        <v>Anish Kumar</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L171" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>GASLIGHT</v>
+        <v>Breathe</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:10</v>
+        <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>WesGhost</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L172" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Truth To Be Told</v>
+        <v>xs</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:17</v>
+        <v>3:19</v>
       </c>
       <c r="H173" t="str">
-        <v>GERD</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L173" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Free Your Mind</v>
+        <v>Sail</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G174" t="str">
-        <v>3:21</v>
+        <v>4:54</v>
       </c>
       <c r="H174" t="str">
-        <v>Prospa</v>
+        <v>Future Islands</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L174" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Down To The Bone</v>
+        <v>Dreaming</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G175" t="str">
-        <v>2:51</v>
+        <v>3:33</v>
       </c>
       <c r="H175" t="str">
-        <v>Josh Baker</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L175" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Breathe</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Breathe - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>2:39</v>
       </c>
       <c r="H176" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Armanii</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L176" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>xs</v>
+        <v>La Opinión</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>xs - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G177" t="str">
-        <v>3:19</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>Ashley Cooke</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L177" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Sail</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:54</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>Future Islands</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L178" t="str">
-        <v>Sail - Future Islands</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Dreaming</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Dear Nashville</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:33</v>
+        <v>2:43</v>
       </c>
       <c r="H179" t="str">
-        <v>Ashley Monroe</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L179" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>NEW TINGZ</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:39</v>
+        <v>2:16</v>
       </c>
       <c r="H180" t="str">
-        <v>Armanii</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L180" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>La Opinión</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Mis Compas El Final</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>2:56</v>
       </c>
       <c r="H181" t="str">
-        <v>Joss Favela</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L181" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>qué ves en mí?</v>
+        <v>Me Neither</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G182" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Paloma Morphy</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L182" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G183" t="str">
-        <v>2:43</v>
+        <v>2:48</v>
       </c>
       <c r="H183" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L183" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>TUTUTU</v>
+        <v>Wonder</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:16</v>
+        <v>3:48</v>
       </c>
       <c r="H184" t="str">
-        <v>ELENA ROSE</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L184" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>ICU</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:56</v>
+        <v>2:53</v>
       </c>
       <c r="H185" t="str">
-        <v>2'Live Bre</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Me Neither</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G186" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H186" t="str">
-        <v>Ty Myers</v>
+        <v>Jozzy</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L186" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cole Palmer</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Solid Ground</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H187" t="str">
-        <v>Limoblaze</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L187" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Wonder</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Wonder - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G188" t="str">
-        <v>3:48</v>
+        <v>4:02</v>
       </c>
       <c r="H188" t="str">
-        <v>Meeks Carter</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L188" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ICU</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>ICU - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:53</v>
+        <v>3:51</v>
       </c>
       <c r="H189" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L189" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Delicately</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:45</v>
+        <v>3:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Jozzy</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Waiting Room</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Waiting Room - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>3:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Jenevieve</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L191" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Rise</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G192" t="str">
-        <v>4:02</v>
+        <v>6:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Melissa Etheridge</v>
+        <v>José González</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L192" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Roll On Thru</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G193" t="str">
-        <v>3:51</v>
+        <v>3:33</v>
       </c>
       <c r="H193" t="str">
-        <v>Hayden Everett</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L193" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Delicately</v>
+        <v>Daisy</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Delicately - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>3:02</v>
       </c>
       <c r="H194" t="str">
-        <v>Andrea Bejar</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L194" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>One Of Those Things</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G195" t="str">
-        <v>3:27</v>
+        <v>3:57</v>
       </c>
       <c r="H195" t="str">
-        <v>Lucy Clearwater</v>
+        <v>james K</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L195" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>For Every Dusk</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>6:04</v>
+        <v>2:45</v>
       </c>
       <c r="H196" t="str">
-        <v>José González</v>
+        <v>MAVICA</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L196" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I'll Wait</v>
+        <v>Fort</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:33</v>
+        <v>2:27</v>
       </c>
       <c r="H197" t="str">
-        <v>Buzzy Lee</v>
+        <v>Lamb</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L197" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Daisy</v>
+        <v>SAME LA</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Daisy - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:02</v>
+        <v>3:44</v>
       </c>
       <c r="H198" t="str">
-        <v>Lola Blue</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L198" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Working On It</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Friend Remixes</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H199" t="str">
-        <v>james K</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L199" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Perdidos - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:45</v>
+        <v>4:03</v>
       </c>
       <c r="H200" t="str">
-        <v>MAVICA</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L200" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Fort</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Fort - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:27</v>
+        <v>3:26</v>
       </c>
       <c r="H201" t="str">
-        <v>Lamb</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L201" t="str">
-        <v>Fort - Lamb</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SAME LA</v>
+        <v>Simple Things</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>SAME LA - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:44</v>
+        <v>3:46</v>
       </c>
       <c r="H202" t="str">
-        <v>Tiffany Day</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L202" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Working On It</v>
+        <v>Want It Back</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Working On It - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H203" t="str">
-        <v>Arthur Hill</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L203" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>spring cleaning</v>
+        <v>Bite Down</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>4:03</v>
+        <v>3:36</v>
       </c>
       <c r="H204" t="str">
-        <v>Ethan Regan</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L204" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Just Drivin'</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E205" t="str">
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G205" t="str">
-        <v>3:26</v>
+        <v>5:42</v>
       </c>
       <c r="H205" t="str">
-        <v>Presley Haile</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L205" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Simple Things</v>
+        <v>Demons</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E206" t="str">
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Simple Things - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G206" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H206" t="str">
-        <v>Evening Elephants</v>
+        <v>Anella</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L206" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Want It Back</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E207" t="str">
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Want It Back - Single</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:27</v>
+        <v>3:35</v>
       </c>
       <c r="H207" t="str">
-        <v>Giant Rooks</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L207" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Bite Down</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D208" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E208" t="str">
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Bite Down - Single</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>3:36</v>
+        <v>3:49</v>
       </c>
       <c r="H208" t="str">
-        <v>Anna Sofia</v>
+        <v>Enslaved</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L208" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D209" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E209" t="str">
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G209" t="str">
-        <v>5:42</v>
+        <v>4:09</v>
       </c>
       <c r="H209" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Demons</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Ask Me How I’ve Been</v>
-      </c>
-      <c r="G210" t="str">
-        <v>2:42</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Anella</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Demons - Anella</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Es brennt...</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Es brennt... - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H211" t="str">
-        <v>Till Lindemann</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Es brennt... - Till Lindemann</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Fire Marengo</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
-      </c>
-      <c r="G212" t="str">
-        <v>3:49</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Enslaved</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
-      </c>
-      <c r="L212" t="str">
-        <v>Fire Marengo - Enslaved</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Close to the Bone</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G213" t="str">
-        <v>4:09</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
-      </c>
-      <c r="L213" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L211"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>מינקובסקי – מכלוף</v>
       </c>
       <c r="B2" t="str">
-        <v>2d ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a0%d7%a7%d7%95%d7%91%d7%a1%d7%a7%d7%99-%d7%9e%d7%9b%d7%9c%d7%95%d7%a3/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-30</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2d ago</v>
+        <v>“מינקובסקי” שכתב מינקובסקי בביצוע מכלוף – הוא טקסט מורכב הרבה יותר ממה שנראה במבט ראשון. יש כאן שילוב של ראפ, פופ, הומור עצמי, זהות עדתית ומטא־אמירה על הצלחה ואותנטיות. השיר נפתח בשאלה דיבורית: “מה אתה מנסה להגיד / שאתה?! אתה</v>
       </c>
       <c r="G2" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>מינקובסקי – מכלוף</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>סאבלימינל - ימים טובים באים</v>
       </c>
       <c r="B3" t="str">
-        <v>2d ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24459&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-30</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2d ago</v>
+        <v>08:26</v>
       </c>
       <c r="G3" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Miley Cyrus</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>סאבלימינל - ימים טובים באים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B4" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-30</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:42</v>
+        <v>3:56</v>
       </c>
       <c r="H4" t="str">
-        <v>Conan Gray</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B5" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-30</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:16</v>
+        <v>2:50</v>
       </c>
       <c r="H5" t="str">
-        <v>Charlie Puth</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-30</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:08</v>
+        <v>3:42</v>
       </c>
       <c r="H6" t="str">
-        <v>Kylie Morgan</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-30</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:38</v>
+        <v>2:16</v>
       </c>
       <c r="H7" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-30</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:01</v>
+        <v>3:08</v>
       </c>
       <c r="H8" t="str">
-        <v>Angelina Mango</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-30</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v>3:38</v>
       </c>
       <c r="H9" t="str">
-        <v>Julio Iglesias</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-30</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:59</v>
+        <v>3:01</v>
       </c>
       <c r="H10" t="str">
-        <v>Loreen</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B11" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-30</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:58</v>
+        <v>3:59</v>
       </c>
       <c r="H11" t="str">
-        <v>Jessie Ware</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-30</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:49</v>
+        <v>2:59</v>
       </c>
       <c r="H12" t="str">
-        <v>Holly Humberstone</v>
+        <v>Loreen</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B13" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-30</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:22</v>
+        <v>2:58</v>
       </c>
       <c r="H13" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B14" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-30</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:50</v>
+        <v>3:49</v>
       </c>
       <c r="H14" t="str">
-        <v>Ella Langley</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B15" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-30</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>6:43</v>
+        <v>3:22</v>
       </c>
       <c r="H15" t="str">
-        <v>David Gilmour</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B16" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-30</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:52</v>
+        <v>3:50</v>
       </c>
       <c r="H16" t="str">
-        <v>Eagles</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B17" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-30</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:13</v>
+        <v>6:43</v>
       </c>
       <c r="H17" t="str">
-        <v>Moody Joody</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-30</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:28</v>
+        <v>4:52</v>
       </c>
       <c r="H18" t="str">
-        <v>Jackson Dean</v>
+        <v>Eagles</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-30</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:01</v>
+        <v>3:13</v>
       </c>
       <c r="H19" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-30</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:00</v>
+        <v>3:28</v>
       </c>
       <c r="H20" t="str">
-        <v>Madison Cunningham</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-30</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:35</v>
+        <v>3:01</v>
       </c>
       <c r="H21" t="str">
-        <v>mary in the junkyard</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B22" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-30</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:01</v>
+        <v>4:00</v>
       </c>
       <c r="H22" t="str">
-        <v>Adam Sanders</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B23" t="str">
-        <v>8d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-30</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:40</v>
+        <v>5:35</v>
       </c>
       <c r="H23" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-30</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H24" t="str">
-        <v>twocolors</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-30</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:42</v>
+        <v>3:40</v>
       </c>
       <c r="H25" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-30</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:56</v>
+        <v>2:25</v>
       </c>
       <c r="H26" t="str">
-        <v>Prince</v>
+        <v>twocolors</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B27" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-30</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:12</v>
+        <v>3:42</v>
       </c>
       <c r="H27" t="str">
-        <v>RAYE</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B28" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-30</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:30</v>
+        <v>3:56</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>Prince</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-30</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:18</v>
+        <v>5:12</v>
       </c>
       <c r="H29" t="str">
-        <v>Pentatonix</v>
+        <v>RAYE</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:33</v>
+        <v>3:30</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>The Warning</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:53</v>
+        <v>3:18</v>
       </c>
       <c r="H31" t="str">
-        <v>Jessie Ware</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:37</v>
+        <v>3:33</v>
       </c>
       <c r="H32" t="str">
-        <v>Niall Horan</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B33" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:26</v>
+        <v>5:53</v>
       </c>
       <c r="H33" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B34" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-30</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:40</v>
+        <v>2:37</v>
       </c>
       <c r="H34" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B35" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-30</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:30</v>
+        <v>2:26</v>
       </c>
       <c r="H35" t="str">
-        <v>Jackson Dean</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-30</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:02</v>
+        <v>2:40</v>
       </c>
       <c r="H36" t="str">
-        <v>Foo Fighters</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B37" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-30</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:40</v>
+        <v>3:30</v>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-30</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:22</v>
+        <v>4:02</v>
       </c>
       <c r="H38" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B39" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-30</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H39" t="str">
-        <v>Ella Langley</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-30</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:39</v>
+        <v>2:22</v>
       </c>
       <c r="H40" t="str">
-        <v>Cannons</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-30</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:10</v>
+        <v>3:47</v>
       </c>
       <c r="H41" t="str">
-        <v>Luke Combs</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B42" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-30</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:47</v>
+        <v>3:39</v>
       </c>
       <c r="H42" t="str">
-        <v>Nessa Barrett</v>
+        <v>Cannons</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-30</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:14</v>
+        <v>4:10</v>
       </c>
       <c r="H43" t="str">
-        <v>aron!</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-30</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:00</v>
+        <v>4:47</v>
       </c>
       <c r="H44" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-30</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:56</v>
+        <v>2:14</v>
       </c>
       <c r="H45" t="str">
-        <v>DMA'S</v>
+        <v>aron!</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-30</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:17</v>
+        <v>4:00</v>
       </c>
       <c r="H46" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-30</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:17</v>
+        <v>3:56</v>
       </c>
       <c r="H47" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>DMA'S</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H48" t="str">
-        <v>Nick Carter</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:38</v>
+        <v>3:17</v>
       </c>
       <c r="H49" t="str">
-        <v>Carly Pearce</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B50" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-30</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>3:31</v>
       </c>
       <c r="H50" t="str">
-        <v>OneRepublic</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-30</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H51" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-30</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:47</v>
+        <v>4:11</v>
       </c>
       <c r="H52" t="str">
-        <v>Armin van Buuren</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-30</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>7:10</v>
+        <v>2:57</v>
       </c>
       <c r="H53" t="str">
-        <v>David Gilmour</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:06</v>
+        <v>3:47</v>
       </c>
       <c r="H54" t="str">
-        <v>Grace Enger</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-30</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:05</v>
+        <v>7:10</v>
       </c>
       <c r="H55" t="str">
-        <v>Tucker Wetmore</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-30</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:12</v>
+        <v>3:06</v>
       </c>
       <c r="H56" t="str">
-        <v>Freya Ridings</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-30</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>9:11</v>
+        <v>3:05</v>
       </c>
       <c r="H57" t="str">
-        <v>David Gilmour</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-30</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:49</v>
+        <v>3:12</v>
       </c>
       <c r="H58" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-30</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:28</v>
+        <v>9:11</v>
       </c>
       <c r="H59" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-30</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:31</v>
+        <v>3:49</v>
       </c>
       <c r="H60" t="str">
-        <v>Martin Garrix</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-30</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:11</v>
+        <v>3:28</v>
       </c>
       <c r="H61" t="str">
-        <v>Baby Queen</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-30</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:27</v>
+        <v>3:31</v>
       </c>
       <c r="H62" t="str">
-        <v>HAUSER</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-30</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:34</v>
+        <v>3:11</v>
       </c>
       <c r="H63" t="str">
-        <v>Holly Humberstone</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-30</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:50</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>HAUSER</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-30</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:51</v>
+        <v>3:34</v>
       </c>
       <c r="H65" t="str">
-        <v>Rick Astley</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-30</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H66" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-30</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:08</v>
+        <v>3:51</v>
       </c>
       <c r="H67" t="str">
-        <v>Jessie J</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-30</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>2:39</v>
       </c>
       <c r="H68" t="str">
-        <v>Bishop Briggs</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-30</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:42</v>
+        <v>5:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie J</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-30</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:31</v>
+        <v>3:46</v>
       </c>
       <c r="H70" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-30</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:14</v>
+        <v>2:42</v>
       </c>
       <c r="H71" t="str">
-        <v>Luke Combs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-30</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:22</v>
+        <v>2:31</v>
       </c>
       <c r="H72" t="str">
-        <v>Allison Russell</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-30</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:43</v>
+        <v>3:14</v>
       </c>
       <c r="H73" t="str">
-        <v>We Three</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-30</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:54</v>
+        <v>3:22</v>
       </c>
       <c r="H74" t="str">
-        <v>paris jackson</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-30</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:46</v>
+        <v>3:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Kane Brown</v>
+        <v>We Three</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-30</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:37</v>
+        <v>2:54</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>paris jackson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-30</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H77" t="str">
-        <v>Malcolm Todd</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-30</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:38</v>
+        <v>3:37</v>
       </c>
       <c r="H78" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-30</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:29</v>
+        <v>2:57</v>
       </c>
       <c r="H79" t="str">
-        <v>Kungs</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-30</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:28</v>
+        <v>3:38</v>
       </c>
       <c r="H80" t="str">
-        <v>Sunday (1994)</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-30</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>4:29</v>
       </c>
       <c r="H81" t="str">
-        <v>aron!</v>
+        <v>Kungs</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-30</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:51</v>
+        <v>4:28</v>
       </c>
       <c r="H82" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-30</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:49</v>
+        <v>3:26</v>
       </c>
       <c r="H83" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-30</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:16</v>
+        <v>3:51</v>
       </c>
       <c r="H84" t="str">
-        <v>Owen Riegling</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-30</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:16</v>
+        <v>2:49</v>
       </c>
       <c r="H85" t="str">
-        <v>LANY</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-30</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H86" t="str">
-        <v>Maverick Sabre</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-30</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:50</v>
+        <v>4:16</v>
       </c>
       <c r="H87" t="str">
-        <v>Amanda Jordan</v>
+        <v>LANY</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-30</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>3:25</v>
       </c>
       <c r="H88" t="str">
-        <v>Beabadoobee</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-30</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:58</v>
+        <v>2:50</v>
       </c>
       <c r="H89" t="str">
-        <v>Spacey Jane</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-30</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:25</v>
+        <v>3:57</v>
       </c>
       <c r="H90" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-30</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:09</v>
+        <v>3:58</v>
       </c>
       <c r="H91" t="str">
-        <v>Mei Semones</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-30</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:08</v>
+        <v>3:25</v>
       </c>
       <c r="H92" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-30</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:57</v>
+        <v>4:09</v>
       </c>
       <c r="H93" t="str">
-        <v>Natalie Jane</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-30</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:13</v>
+        <v>2:08</v>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-30</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:12</v>
+        <v>2:57</v>
       </c>
       <c r="H95" t="str">
-        <v>David Gilmour</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-30</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:57</v>
+        <v>3:13</v>
       </c>
       <c r="H96" t="str">
-        <v>Far Caspian</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-30</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:34</v>
+        <v>4:12</v>
       </c>
       <c r="H97" t="str">
-        <v>Celine Dion</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-30</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:48</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>Harry Styles</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:58</v>
+        <v>3:34</v>
       </c>
       <c r="H99" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-30</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:33</v>
+        <v>3:48</v>
       </c>
       <c r="H100" t="str">
-        <v>Ellise</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-30</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:01</v>
+        <v>4:58</v>
       </c>
       <c r="H101" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Days We Left Behind</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-30</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:18</v>
+        <v>2:33</v>
       </c>
       <c r="H102" t="str">
-        <v>Paul McCartney</v>
+        <v>Ellise</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>2:47</v>
+        <v>5:01</v>
       </c>
       <c r="H103" t="str">
-        <v>Miley Cyrus</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>6:17</v>
+        <v>3:18</v>
       </c>
       <c r="H104" t="str">
-        <v>RAYE</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>MARATHON</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>MARATHON - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:49</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Becky G</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L105" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ALL THE TIME</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G106" t="str">
-        <v>3:00</v>
+        <v>6:17</v>
       </c>
       <c r="H106" t="str">
-        <v>John Summit</v>
+        <v>RAYE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L106" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Sucker For Love</v>
+        <v>MARATHON</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Sexistential</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H107" t="str">
-        <v>Robyn</v>
+        <v>Becky G</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L107" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>FATHER</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>BULLY</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Kanye West</v>
+        <v>John Summit</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L108" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Lose Control</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>ADL</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>2:39</v>
+        <v>3:34</v>
       </c>
       <c r="H109" t="str">
-        <v>Yeat</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>FATHER</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Zavier</v>
+        <v>BULLY</v>
       </c>
       <c r="G110" t="str">
-        <v>3:44</v>
+        <v>2:49</v>
       </c>
       <c r="H110" t="str">
-        <v>Fetty Wap</v>
+        <v>Kanye West</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L110" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WAGWAN</v>
+        <v>Lose Control</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>ADL</v>
       </c>
       <c r="G111" t="str">
-        <v>2:07</v>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>Central Cee</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L111" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Sideways</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>KONNAKOL</v>
+        <v>Zavier</v>
       </c>
       <c r="G112" t="str">
-        <v>3:12</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>ZAYN</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L112" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Automatic</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Superbloom</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G113" t="str">
-        <v>2:57</v>
+        <v>2:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Jessie Ware</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L113" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Tractor Beam</v>
+        <v>Sideways</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Ricochet</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G114" t="str">
-        <v>3:34</v>
+        <v>3:12</v>
       </c>
       <c r="H114" t="str">
-        <v>Snail Mail</v>
+        <v>ZAYN</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L114" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>prom queen</v>
+        <v>Automatic</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>prom queen - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G115" t="str">
-        <v>2:43</v>
+        <v>2:57</v>
       </c>
       <c r="H115" t="str">
-        <v>Amelia Moore</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L115" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Pal Agua</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G116" t="str">
-        <v>3:26</v>
+        <v>3:34</v>
       </c>
       <c r="H116" t="str">
-        <v>J Balvin</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L116" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Phoenix</v>
+        <v>prom queen</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Phoenix - Single</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:24</v>
+        <v>2:43</v>
       </c>
       <c r="H117" t="str">
-        <v>Marshmello</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L117" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H118" t="str">
-        <v>Ne-Yo</v>
+        <v>J Balvin</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L118" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Feel Your Rain</v>
+        <v>Phoenix</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:36</v>
+        <v>2:24</v>
       </c>
       <c r="H119" t="str">
-        <v>Eli</v>
+        <v>Marshmello</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L119" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lonely</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ö</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:58</v>
+        <v>2:56</v>
       </c>
       <c r="H120" t="str">
-        <v>Fcukers</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L120" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Back in Love</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Back in Love - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:14</v>
+        <v>3:36</v>
       </c>
       <c r="H121" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Eli</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L121" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Sideways</v>
+        <v>Lonely</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Ö</v>
       </c>
       <c r="G122" t="str">
-        <v>3:55</v>
+        <v>2:58</v>
       </c>
       <c r="H122" t="str">
-        <v>Charlie Puth</v>
+        <v>Fcukers</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L122" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>Back in Love</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Honora</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:22</v>
+        <v>3:14</v>
       </c>
       <c r="H123" t="str">
-        <v>Flea</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L123" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Sideways</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G124" t="str">
-        <v>2:58</v>
+        <v>3:55</v>
       </c>
       <c r="H124" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L124" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>4:22</v>
       </c>
       <c r="H125" t="str">
-        <v>Honey Bxby</v>
+        <v>Flea</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L125" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>One Thing At A Time</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Creature of Habit</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:42</v>
+        <v>2:58</v>
       </c>
       <c r="H126" t="str">
-        <v>Courtney Barnett</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L126" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>wasteland</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>wasteland - Single</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>3:02</v>
       </c>
       <c r="H127" t="str">
-        <v>Yuna</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L127" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>getting up to no good</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G128" t="str">
-        <v>2:31</v>
+        <v>4:42</v>
       </c>
       <c r="H128" t="str">
-        <v>Artemas</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L128" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Por LA</v>
+        <v>wasteland</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>TODO Ø NADA</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:19</v>
+        <v>3:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Linea Personal</v>
+        <v>Yuna</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L129" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>You Lead Me</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G130" t="str">
-        <v>4:14</v>
+        <v>2:31</v>
       </c>
       <c r="H130" t="str">
-        <v>Lauren Daigle</v>
+        <v>Artemas</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L130" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Just A Kid</v>
+        <v>Por LA</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Broken View</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G131" t="str">
-        <v>4:18</v>
+        <v>2:19</v>
       </c>
       <c r="H131" t="str">
-        <v>Sam Barber</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L131" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Country And She Knows It</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G132" t="str">
-        <v>2:54</v>
+        <v>4:14</v>
       </c>
       <c r="H132" t="str">
-        <v>Luke Bryan</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L132" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G133" t="str">
-        <v>2:35</v>
+        <v>4:18</v>
       </c>
       <c r="H133" t="str">
-        <v>Thomas Rhett</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L133" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Deep Blue</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Deep Blue</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:17</v>
+        <v>2:54</v>
       </c>
       <c r="H134" t="str">
-        <v>ERNEST</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L134" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Special</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>sounds for someone</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:49</v>
+        <v>2:35</v>
       </c>
       <c r="H135" t="str">
-        <v>Elmiene</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L135" t="str">
-        <v>Special - Elmiene</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Heart Attack</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>CANDY</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G136" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>Justine Skye</v>
+        <v>ERNEST</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L136" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>STAY</v>
+        <v>Special</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>STAY - Single</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G137" t="str">
-        <v>3:06</v>
+        <v>2:49</v>
       </c>
       <c r="H137" t="str">
-        <v>Stray Kids</v>
+        <v>Elmiene</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L137" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Unglued</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Work of Heart</v>
+        <v>CANDY</v>
       </c>
       <c r="G138" t="str">
-        <v>3:54</v>
+        <v>2:52</v>
       </c>
       <c r="H138" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L138" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ritual</v>
+        <v>STAY</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Ritual - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H139" t="str">
-        <v>Icona Pop</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L139" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>The Best</v>
+        <v>Unglued</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G140" t="str">
-        <v>3:48</v>
+        <v>3:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Conan Gray</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L140" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Smile</v>
+        <v>Ritual</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Smile - Single</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:50</v>
+        <v>3:01</v>
       </c>
       <c r="H141" t="str">
-        <v>Two Shell</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L141" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Duro</v>
+        <v>The Best</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Duro - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G142" t="str">
-        <v>3:05</v>
+        <v>3:48</v>
       </c>
       <c r="H142" t="str">
-        <v>Skrillex</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L142" t="str">
-        <v>Duro - Skrillex</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Smile</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:58</v>
+        <v>3:50</v>
       </c>
       <c r="H143" t="str">
-        <v>Sublime</v>
+        <v>Two Shell</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L143" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Carousel</v>
+        <v>Duro</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Everything Glows</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:36</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Cannons</v>
+        <v>Skrillex</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L144" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Mercy</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Mercy - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G145" t="str">
-        <v>3:49</v>
+        <v>2:58</v>
       </c>
       <c r="H145" t="str">
-        <v>PRESIDENT</v>
+        <v>Sublime</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L145" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Palms</v>
+        <v>Carousel</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Palms - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G146" t="str">
-        <v>3:18</v>
+        <v>3:36</v>
       </c>
       <c r="H146" t="str">
-        <v>The Maine</v>
+        <v>Cannons</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L146" t="str">
-        <v>Palms - The Maine</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Ozzy's Song</v>
+        <v>Mercy</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>5:28</v>
+        <v>3:49</v>
       </c>
       <c r="H147" t="str">
-        <v>Black Label Society</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L147" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Danger</v>
+        <v>Palms</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Danger - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:19</v>
+        <v>3:18</v>
       </c>
       <c r="H148" t="str">
-        <v>Nia Archives</v>
+        <v>The Maine</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L148" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Icarus</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Icarus - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G149" t="str">
-        <v>4:25</v>
+        <v>5:28</v>
       </c>
       <c r="H149" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L149" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>idk idk</v>
+        <v>Danger</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>idk idk - Single</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:26</v>
+        <v>2:19</v>
       </c>
       <c r="H150" t="str">
-        <v>Jim Legxacy</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L150" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Tonight</v>
+        <v>Icarus</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Tonight - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:25</v>
+        <v>4:25</v>
       </c>
       <c r="H151" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L151" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>idk idk</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Switcheroo</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:44</v>
+        <v>2:26</v>
       </c>
       <c r="H152" t="str">
-        <v>Gelli Haha</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L152" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>Tonight</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:45</v>
+        <v>2:25</v>
       </c>
       <c r="H153" t="str">
-        <v>BIA</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L153" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>this girl wants everything</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G154" t="str">
-        <v>3:33</v>
+        <v>3:44</v>
       </c>
       <c r="H154" t="str">
-        <v>Isaia Huron</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L154" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G155" t="str">
-        <v>3:44</v>
+        <v>2:45</v>
       </c>
       <c r="H155" t="str">
-        <v>Slayyyter</v>
+        <v>BIA</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L155" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Kingdom of Fear</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Deep Water - EP</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G156" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H156" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L156" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>R3verse</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>takeaways</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G157" t="str">
-        <v>3:31</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>Medium Build</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L157" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>2:32</v>
+        <v>2:41</v>
       </c>
       <c r="H158" t="str">
-        <v>MIKE</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L158" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>heart of gold</v>
+        <v>R3verse</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>heart of gold - Single</v>
+        <v>takeaways</v>
       </c>
       <c r="G159" t="str">
-        <v>2:51</v>
+        <v>3:31</v>
       </c>
       <c r="H159" t="str">
-        <v>kai devega</v>
+        <v>Medium Build</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L159" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Breaking Down</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Skeletor</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G160" t="str">
-        <v>4:21</v>
+        <v>2:32</v>
       </c>
       <c r="H160" t="str">
-        <v>Chief Keef</v>
+        <v>MIKE</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L160" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Dream House</v>
+        <v>heart of gold</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Dream House - Single</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:54</v>
+        <v>2:51</v>
       </c>
       <c r="H161" t="str">
-        <v>Empress Of</v>
+        <v>kai devega</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L161" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Baby Blue</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G162" t="str">
-        <v>2:51</v>
+        <v>4:21</v>
       </c>
       <c r="H162" t="str">
-        <v>Cody Simpson</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L162" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Dream House</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:37</v>
+        <v>2:54</v>
       </c>
       <c r="H163" t="str">
-        <v>MEDUZA</v>
+        <v>Empress Of</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L163" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Forever Now</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:05</v>
+        <v>2:51</v>
       </c>
       <c r="H164" t="str">
-        <v>Switchfoot</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L164" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:46</v>
+        <v>2:37</v>
       </c>
       <c r="H165" t="str">
-        <v>Benny G</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L165" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G166" t="str">
-        <v>3:03</v>
+        <v>4:05</v>
       </c>
       <c r="H166" t="str">
-        <v>Eric Bellinger</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L166" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>4:19</v>
+        <v>3:46</v>
       </c>
       <c r="H167" t="str">
-        <v>Anish Kumar</v>
+        <v>Benny G</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L167" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>GASLIGHT</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:10</v>
+        <v>3:03</v>
       </c>
       <c r="H168" t="str">
-        <v>WesGhost</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L168" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Truth To Be Told</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>3:17</v>
+        <v>4:19</v>
       </c>
       <c r="H169" t="str">
-        <v>GERD</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L169" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Free Your Mind</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:21</v>
+        <v>2:10</v>
       </c>
       <c r="H170" t="str">
-        <v>Prospa</v>
+        <v>WesGhost</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L170" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Down To The Bone</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H171" t="str">
-        <v>Josh Baker</v>
+        <v>GERD</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L171" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Breathe</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Breathe - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H172" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Prospa</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L172" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>xs</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>xs - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:19</v>
+        <v>2:51</v>
       </c>
       <c r="H173" t="str">
-        <v>Ashley Cooke</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L173" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Sail</v>
+        <v>Breathe</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:54</v>
+        <v>2:48</v>
       </c>
       <c r="H174" t="str">
-        <v>Future Islands</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L174" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Dreaming</v>
+        <v>xs</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Dear Nashville</v>
+        <v>xs - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:33</v>
+        <v>3:19</v>
       </c>
       <c r="H175" t="str">
-        <v>Ashley Monroe</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L175" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>NEW TINGZ</v>
+        <v>Sail</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G176" t="str">
-        <v>2:39</v>
+        <v>4:54</v>
       </c>
       <c r="H176" t="str">
-        <v>Armanii</v>
+        <v>Future Islands</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L176" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>La Opinión</v>
+        <v>Dreaming</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Mis Compas El Final</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>3:33</v>
       </c>
       <c r="H177" t="str">
-        <v>Joss Favela</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L177" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>qué ves en mí?</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>2:39</v>
       </c>
       <c r="H178" t="str">
-        <v>Paloma Morphy</v>
+        <v>Armanii</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L178" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>La Opinión</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G179" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L179" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>TUTUTU</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>TUTUTU - Single</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:16</v>
+        <v>3:24</v>
       </c>
       <c r="H180" t="str">
-        <v>ELENA ROSE</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L180" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:56</v>
+        <v>2:43</v>
       </c>
       <c r="H181" t="str">
-        <v>2'Live Bre</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L181" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Me Neither</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Heavy On The Soul</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:32</v>
+        <v>2:16</v>
       </c>
       <c r="H182" t="str">
-        <v>Ty Myers</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L182" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cole Palmer</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Solid Ground</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:48</v>
+        <v>2:56</v>
       </c>
       <c r="H183" t="str">
-        <v>Limoblaze</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L183" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Wonder</v>
+        <v>Me Neither</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Wonder - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G184" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H184" t="str">
-        <v>Meeks Carter</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L184" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>ICU</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>ICU - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G185" t="str">
-        <v>2:53</v>
+        <v>2:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L185" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Wonder</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:45</v>
+        <v>3:48</v>
       </c>
       <c r="H186" t="str">
-        <v>Jozzy</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L186" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Waiting Room</v>
+        <v>ICU</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Waiting Room - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:21</v>
+        <v>2:53</v>
       </c>
       <c r="H187" t="str">
-        <v>Jenevieve</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L187" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Rise</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G188" t="str">
-        <v>4:02</v>
+        <v>2:45</v>
       </c>
       <c r="H188" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Jozzy</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L188" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Roll On Thru</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:51</v>
+        <v>3:21</v>
       </c>
       <c r="H189" t="str">
-        <v>Hayden Everett</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L189" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Delicately</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Delicately - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G190" t="str">
-        <v>3:20</v>
+        <v>4:02</v>
       </c>
       <c r="H190" t="str">
-        <v>Andrea Bejar</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L190" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>One Of Those Things</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:27</v>
+        <v>3:51</v>
       </c>
       <c r="H191" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L191" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>For Every Dusk</v>
+        <v>Delicately</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>6:04</v>
+        <v>3:20</v>
       </c>
       <c r="H192" t="str">
-        <v>José González</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L192" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I'll Wait</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:33</v>
+        <v>3:27</v>
       </c>
       <c r="H193" t="str">
-        <v>Buzzy Lee</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L193" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Daisy</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Daisy - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G194" t="str">
-        <v>3:02</v>
+        <v>6:04</v>
       </c>
       <c r="H194" t="str">
-        <v>Lola Blue</v>
+        <v>José González</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L194" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Friend Remixes</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G195" t="str">
-        <v>3:57</v>
+        <v>3:33</v>
       </c>
       <c r="H195" t="str">
-        <v>james K</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L195" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Daisy</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Perdidos - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:45</v>
+        <v>3:02</v>
       </c>
       <c r="H196" t="str">
-        <v>MAVICA</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L196" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Fort</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-30</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Fort - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G197" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H197" t="str">
-        <v>Lamb</v>
+        <v>james K</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L197" t="str">
-        <v>Fort - Lamb</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SAME LA</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-30</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>SAME LA - Single</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:44</v>
+        <v>2:45</v>
       </c>
       <c r="H198" t="str">
-        <v>Tiffany Day</v>
+        <v>MAVICA</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L198" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Working On It</v>
+        <v>Fort</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-30</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Working On It - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:06</v>
+        <v>2:27</v>
       </c>
       <c r="H199" t="str">
-        <v>Arthur Hill</v>
+        <v>Lamb</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L199" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>spring cleaning</v>
+        <v>SAME LA</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-30</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>spring cleaning - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:03</v>
+        <v>3:44</v>
       </c>
       <c r="H200" t="str">
-        <v>Ethan Regan</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L200" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Just Drivin'</v>
+        <v>Working On It</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-30</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H201" t="str">
-        <v>Presley Haile</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L201" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Simple Things</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-30</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Simple Things - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:46</v>
+        <v>4:03</v>
       </c>
       <c r="H202" t="str">
-        <v>Evening Elephants</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L202" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Want It Back</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-30</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Want It Back - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:27</v>
+        <v>3:26</v>
       </c>
       <c r="H203" t="str">
-        <v>Giant Rooks</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L203" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Bite Down</v>
+        <v>Simple Things</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-30</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Bite Down - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:36</v>
+        <v>3:46</v>
       </c>
       <c r="H204" t="str">
-        <v>Anna Sofia</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L204" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Want It Back</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-30</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>5:42</v>
+        <v>3:27</v>
       </c>
       <c r="H205" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L205" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Demons</v>
+        <v>Bite Down</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-30</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>2:42</v>
+        <v>3:36</v>
       </c>
       <c r="H206" t="str">
-        <v>Anella</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L206" t="str">
-        <v>Demons - Anella</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Es brennt...</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D207" t="str">
         <v>2026-03-30</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G207" t="str">
-        <v>3:35</v>
+        <v>5:42</v>
       </c>
       <c r="H207" t="str">
-        <v>Till Lindemann</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L207" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Fire Marengo</v>
+        <v>Demons</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D208" t="str">
         <v>2026-03-30</v>
@@ -8279,68 +8279,144 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G208" t="str">
-        <v>3:49</v>
+        <v>2:42</v>
       </c>
       <c r="H208" t="str">
-        <v>Enslaved</v>
+        <v>Anella</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L208" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
+        <v>Es brennt...</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Es brennt... - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Till Lindemann</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Es brennt... - Till Lindemann</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Fire Marengo</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>3:49</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Enslaved</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Fire Marengo - Enslaved</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
         <v>Close to the Bone</v>
       </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
-      <c r="D209" t="str">
-        <v>2026-03-30</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
+      <c r="D211" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G209" t="str">
+      <c r="G211" t="str">
         <v>4:09</v>
       </c>
-      <c r="H209" t="str">
+      <c r="H211" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K209" t="str">
+      <c r="K211" t="str">
         <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
-      <c r="L209" t="str">
+      <c r="L211" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L211"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L210"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מינקובסקי – מכלוף</v>
+        <v>הראל סקעת – אמונה שבורה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a0%d7%a7%d7%95%d7%91%d7%a1%d7%a7%d7%99-%d7%9e%d7%9b%d7%9c%d7%95%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%9e%d7%95%d7%a0%d7%94-%d7%a9%d7%91%d7%95%d7%a8%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“מינקובסקי” שכתב מינקובסקי בביצוע מכלוף – הוא טקסט מורכב הרבה יותר ממה שנראה במבט ראשון. יש כאן שילוב של ראפ, פופ, הומור עצמי, זהות עדתית ומטא־אמירה על הצלחה ואותנטיות. השיר נפתח בשאלה דיבורית: “מה אתה מנסה להגיד / שאתה?! אתה</v>
+        <v>הראל סקעת שר בלדה שמצליחה לגעת בנושא עמוק – משבר אמונה דרך הגשה עדינה, כמעט מתפללת. כבר מהשורה – “באמונה שבורה באתי נקי עד אליך” נוצר מתח. מצד אחד: רצון להיות “נקי”, כן, פתוח. מצד שני: אמונה שנשברה- משהו בסיסי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מינקובסקי – מכלוף</v>
+        <v>הראל סקעת – אמונה שבורה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>סאבלימינל - ימים טובים באים</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-30</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24459&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-30</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>08:26</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>3:56</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>סאבלימינל - ימים טובים באים</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B4" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-30</v>
@@ -530,10 +530,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:56</v>
+        <v>2:50</v>
       </c>
       <c r="H4" t="str">
-        <v>Charlie Puth</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-30</v>
@@ -568,10 +568,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:50</v>
+        <v>3:42</v>
       </c>
       <c r="H5" t="str">
-        <v>Miley Cyrus</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B6" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-30</v>
@@ -606,10 +606,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:42</v>
+        <v>2:16</v>
       </c>
       <c r="H6" t="str">
-        <v>Conan Gray</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-30</v>
@@ -644,10 +644,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:16</v>
+        <v>3:08</v>
       </c>
       <c r="H7" t="str">
-        <v>Charlie Puth</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-30</v>
@@ -682,10 +682,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:08</v>
+        <v>3:38</v>
       </c>
       <c r="H8" t="str">
-        <v>Kylie Morgan</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-30</v>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:38</v>
+        <v>3:01</v>
       </c>
       <c r="H9" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-30</v>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:01</v>
+        <v>3:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Angelina Mango</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-30</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H11" t="str">
-        <v>Julio Iglesias</v>
+        <v>Loreen</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-30</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H12" t="str">
-        <v>Loreen</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-30</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:58</v>
+        <v>3:49</v>
       </c>
       <c r="H13" t="str">
-        <v>Jessie Ware</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-30</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:49</v>
+        <v>3:22</v>
       </c>
       <c r="H14" t="str">
-        <v>Holly Humberstone</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B15" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-30</v>
@@ -948,10 +948,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H15" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B16" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-30</v>
@@ -986,10 +986,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:50</v>
+        <v>6:43</v>
       </c>
       <c r="H16" t="str">
-        <v>Ella Langley</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-30</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>6:43</v>
+        <v>4:52</v>
       </c>
       <c r="H17" t="str">
-        <v>David Gilmour</v>
+        <v>Eagles</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-30</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:52</v>
+        <v>3:13</v>
       </c>
       <c r="H18" t="str">
-        <v>Eagles</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-30</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:13</v>
+        <v>3:28</v>
       </c>
       <c r="H19" t="str">
-        <v>Moody Joody</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-30</v>
@@ -1138,10 +1138,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H20" t="str">
-        <v>Jackson Dean</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-30</v>
@@ -1176,10 +1176,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:01</v>
+        <v>4:00</v>
       </c>
       <c r="H21" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-30</v>
@@ -1214,10 +1214,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:00</v>
+        <v>5:35</v>
       </c>
       <c r="H22" t="str">
-        <v>Madison Cunningham</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-30</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:35</v>
+        <v>3:01</v>
       </c>
       <c r="H23" t="str">
-        <v>mary in the junkyard</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-30</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:01</v>
+        <v>3:40</v>
       </c>
       <c r="H24" t="str">
-        <v>Adam Sanders</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-30</v>
@@ -1328,10 +1328,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:40</v>
+        <v>2:25</v>
       </c>
       <c r="H25" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>twocolors</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-30</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:25</v>
+        <v>3:42</v>
       </c>
       <c r="H26" t="str">
-        <v>twocolors</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-30</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:42</v>
+        <v>3:56</v>
       </c>
       <c r="H27" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Prince</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-30</v>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:56</v>
+        <v>5:12</v>
       </c>
       <c r="H28" t="str">
-        <v>Prince</v>
+        <v>RAYE</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-30</v>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:12</v>
+        <v>3:30</v>
       </c>
       <c r="H29" t="str">
-        <v>RAYE</v>
+        <v>The Warning</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:30</v>
+        <v>3:18</v>
       </c>
       <c r="H30" t="str">
-        <v>The Warning</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:18</v>
+        <v>3:33</v>
       </c>
       <c r="H31" t="str">
-        <v>Pentatonix</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:33</v>
+        <v>5:53</v>
       </c>
       <c r="H32" t="str">
-        <v>Tenille Townes</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>5:53</v>
+        <v>2:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Jessie Ware</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B34" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-30</v>
@@ -1670,10 +1670,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H34" t="str">
-        <v>Niall Horan</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-30</v>
@@ -1708,10 +1708,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:26</v>
+        <v>2:40</v>
       </c>
       <c r="H35" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B36" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-30</v>
@@ -1746,10 +1746,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:40</v>
+        <v>3:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-30</v>
@@ -1784,10 +1784,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:30</v>
+        <v>4:02</v>
       </c>
       <c r="H37" t="str">
-        <v>Jackson Dean</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-30</v>
@@ -1822,10 +1822,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:02</v>
+        <v>3:40</v>
       </c>
       <c r="H38" t="str">
-        <v>Foo Fighters</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B39" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-30</v>
@@ -1860,10 +1860,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:40</v>
+        <v>2:22</v>
       </c>
       <c r="H39" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-30</v>
@@ -1898,10 +1898,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:22</v>
+        <v>3:47</v>
       </c>
       <c r="H40" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B41" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-30</v>
@@ -1936,10 +1936,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:47</v>
+        <v>3:39</v>
       </c>
       <c r="H41" t="str">
-        <v>Ella Langley</v>
+        <v>Cannons</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B42" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-30</v>
@@ -1974,10 +1974,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:39</v>
+        <v>4:10</v>
       </c>
       <c r="H42" t="str">
-        <v>Cannons</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B43" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-30</v>
@@ -2012,10 +2012,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:10</v>
+        <v>4:47</v>
       </c>
       <c r="H43" t="str">
-        <v>Luke Combs</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B44" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-30</v>
@@ -2050,10 +2050,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:47</v>
+        <v>2:14</v>
       </c>
       <c r="H44" t="str">
-        <v>Nessa Barrett</v>
+        <v>aron!</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B45" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-30</v>
@@ -2088,10 +2088,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H45" t="str">
-        <v>aron!</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-30</v>
@@ -2126,10 +2126,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:00</v>
+        <v>3:56</v>
       </c>
       <c r="H46" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>DMA'S</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-30</v>
@@ -2164,10 +2164,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:56</v>
+        <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>DMA'S</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:17</v>
       </c>
       <c r="H48" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H49" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-30</v>
@@ -2278,10 +2278,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H50" t="str">
-        <v>Nick Carter</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B51" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-30</v>
@@ -2316,10 +2316,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:38</v>
+        <v>4:11</v>
       </c>
       <c r="H51" t="str">
-        <v>Carly Pearce</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-30</v>
@@ -2354,10 +2354,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:11</v>
+        <v>2:57</v>
       </c>
       <c r="H52" t="str">
-        <v>OneRepublic</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B53" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-30</v>
@@ -2392,10 +2392,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:57</v>
+        <v>3:47</v>
       </c>
       <c r="H53" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:47</v>
+        <v>7:10</v>
       </c>
       <c r="H54" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-30</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>7:10</v>
+        <v>3:06</v>
       </c>
       <c r="H55" t="str">
-        <v>David Gilmour</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-30</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:06</v>
+        <v>3:05</v>
       </c>
       <c r="H56" t="str">
-        <v>Grace Enger</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-30</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H57" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-30</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:12</v>
+        <v>9:11</v>
       </c>
       <c r="H58" t="str">
-        <v>Freya Ridings</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-30</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H59" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-30</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:49</v>
+        <v>3:28</v>
       </c>
       <c r="H60" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-30</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H61" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-30</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H62" t="str">
-        <v>Martin Garrix</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-30</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:11</v>
+        <v>2:27</v>
       </c>
       <c r="H63" t="str">
-        <v>Baby Queen</v>
+        <v>HAUSER</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-30</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H64" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-30</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:34</v>
+        <v>2:50</v>
       </c>
       <c r="H65" t="str">
-        <v>Holly Humberstone</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-30</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H66" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-30</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H67" t="str">
-        <v>Rick Astley</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-30</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:39</v>
+        <v>5:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Jessie J</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-30</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:08</v>
+        <v>3:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Jessie J</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-30</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H70" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-30</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:42</v>
+        <v>2:31</v>
       </c>
       <c r="H71" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-30</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:31</v>
+        <v>3:14</v>
       </c>
       <c r="H72" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-30</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H73" t="str">
-        <v>Luke Combs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-30</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H74" t="str">
-        <v>Allison Russell</v>
+        <v>We Three</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-30</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H75" t="str">
-        <v>We Three</v>
+        <v>paris jackson</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-30</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H76" t="str">
-        <v>paris jackson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-30</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:46</v>
+        <v>3:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-30</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H78" t="str">
-        <v>Lainey Wilson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-30</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H79" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-30</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:38</v>
+        <v>4:29</v>
       </c>
       <c r="H80" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Kungs</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-30</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:29</v>
+        <v>4:28</v>
       </c>
       <c r="H81" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-30</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:28</v>
+        <v>3:26</v>
       </c>
       <c r="H82" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-30</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H83" t="str">
-        <v>aron!</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-30</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H84" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-30</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-30</v>
@@ -3649,7 +3649,7 @@
         <v>4:16</v>
       </c>
       <c r="H86" t="str">
-        <v>Owen Riegling</v>
+        <v>LANY</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-30</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H87" t="str">
-        <v>LANY</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-30</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H88" t="str">
-        <v>Maverick Sabre</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-30</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H89" t="str">
-        <v>Amanda Jordan</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-30</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="H90" t="str">
-        <v>Beabadoobee</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-30</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H91" t="str">
-        <v>Spacey Jane</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-30</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H92" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-30</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-30</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H94" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-30</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H95" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-30</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H96" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-30</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-30</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H98" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H99" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-30</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H100" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-30</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H101" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B102" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-30</v>
@@ -4254,10 +4254,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H102" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B103" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>3 weeks ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G103" t="str">
-        <v>5:01</v>
+        <v>3:18</v>
       </c>
       <c r="H103" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L103" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Days We Left Behind</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:18</v>
+        <v>2:47</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L104" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>6:17</v>
       </c>
       <c r="H105" t="str">
-        <v>Miley Cyrus</v>
+        <v>RAYE</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>MARATHON</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>6:17</v>
+        <v>2:49</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>Becky G</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L106" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>MARATHON</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>MARATHON - Single</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>Becky G</v>
+        <v>John Summit</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L107" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ALL THE TIME</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H108" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L108" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Sucker For Love</v>
+        <v>FATHER</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>BULLY</v>
       </c>
       <c r="G109" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>Kanye West</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L109" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>FATHER</v>
+        <v>Lose Control</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>BULLY</v>
+        <v>ADL</v>
       </c>
       <c r="G110" t="str">
-        <v>2:49</v>
+        <v>2:39</v>
       </c>
       <c r="H110" t="str">
-        <v>Kanye West</v>
+        <v>Yeat</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L110" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lose Control</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ADL</v>
+        <v>Zavier</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L111" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Zavier</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>2:07</v>
       </c>
       <c r="H112" t="str">
-        <v>Fetty Wap</v>
+        <v>Central Cee</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WAGWAN</v>
+        <v>Sideways</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G113" t="str">
-        <v>2:07</v>
+        <v>3:12</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>ZAYN</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L113" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sideways</v>
+        <v>Automatic</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>KONNAKOL</v>
+        <v>Superbloom</v>
       </c>
       <c r="G114" t="str">
-        <v>3:12</v>
+        <v>2:57</v>
       </c>
       <c r="H114" t="str">
-        <v>ZAYN</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L114" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Automatic</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Superbloom</v>
+        <v>Ricochet</v>
       </c>
       <c r="G115" t="str">
-        <v>2:57</v>
+        <v>3:34</v>
       </c>
       <c r="H115" t="str">
-        <v>Jessie Ware</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L115" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tractor Beam</v>
+        <v>prom queen</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ricochet</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:34</v>
+        <v>2:43</v>
       </c>
       <c r="H116" t="str">
-        <v>Snail Mail</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L116" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>prom queen</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>prom queen - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:43</v>
+        <v>3:26</v>
       </c>
       <c r="H117" t="str">
-        <v>Amelia Moore</v>
+        <v>J Balvin</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L117" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Pal Agua</v>
+        <v>Phoenix</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:26</v>
+        <v>2:24</v>
       </c>
       <c r="H118" t="str">
-        <v>J Balvin</v>
+        <v>Marshmello</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L118" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Phoenix</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Phoenix - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:24</v>
+        <v>2:56</v>
       </c>
       <c r="H119" t="str">
-        <v>Marshmello</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L119" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:56</v>
+        <v>3:36</v>
       </c>
       <c r="H120" t="str">
-        <v>Ne-Yo</v>
+        <v>Eli</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L120" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Feel Your Rain</v>
+        <v>Lonely</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G121" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H121" t="str">
-        <v>Eli</v>
+        <v>Fcukers</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L121" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Lonely</v>
+        <v>Back in Love</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Ö</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:58</v>
+        <v>3:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Fcukers</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L122" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Back in Love</v>
+        <v>Sideways</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Back in Love - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G123" t="str">
-        <v>3:14</v>
+        <v>3:55</v>
       </c>
       <c r="H123" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L123" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Sideways</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Honora</v>
       </c>
       <c r="G124" t="str">
-        <v>3:55</v>
+        <v>4:22</v>
       </c>
       <c r="H124" t="str">
-        <v>Charlie Puth</v>
+        <v>Flea</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L124" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Honora</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:22</v>
+        <v>2:58</v>
       </c>
       <c r="H125" t="str">
-        <v>Flea</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L125" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:58</v>
+        <v>3:02</v>
       </c>
       <c r="H126" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L126" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G127" t="str">
-        <v>3:02</v>
+        <v>4:42</v>
       </c>
       <c r="H127" t="str">
-        <v>Honey Bxby</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L127" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>One Thing At A Time</v>
+        <v>wasteland</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Creature of Habit</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:42</v>
+        <v>3:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Courtney Barnett</v>
+        <v>Yuna</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L128" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>wasteland</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>wasteland - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G129" t="str">
-        <v>3:05</v>
+        <v>2:31</v>
       </c>
       <c r="H129" t="str">
-        <v>Yuna</v>
+        <v>Artemas</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L129" t="str">
-        <v>wasteland - Yuna</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Por LA</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>getting up to no good</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G130" t="str">
-        <v>2:31</v>
+        <v>2:19</v>
       </c>
       <c r="H130" t="str">
-        <v>Artemas</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L130" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Por LA</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>TODO Ø NADA</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G131" t="str">
-        <v>2:19</v>
+        <v>4:14</v>
       </c>
       <c r="H131" t="str">
-        <v>Linea Personal</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L131" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>You Lead Me</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Broken View</v>
       </c>
       <c r="G132" t="str">
-        <v>4:14</v>
+        <v>4:18</v>
       </c>
       <c r="H132" t="str">
-        <v>Lauren Daigle</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L132" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Just A Kid</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Broken View</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:18</v>
+        <v>2:54</v>
       </c>
       <c r="H133" t="str">
-        <v>Sam Barber</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L133" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Country And She Knows It</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:54</v>
+        <v>2:35</v>
       </c>
       <c r="H134" t="str">
-        <v>Luke Bryan</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L134" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G135" t="str">
-        <v>2:35</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Thomas Rhett</v>
+        <v>ERNEST</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L135" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Deep Blue</v>
+        <v>Special</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Deep Blue</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G136" t="str">
-        <v>3:17</v>
+        <v>2:49</v>
       </c>
       <c r="H136" t="str">
-        <v>ERNEST</v>
+        <v>Elmiene</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L136" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Special</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>sounds for someone</v>
+        <v>CANDY</v>
       </c>
       <c r="G137" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H137" t="str">
-        <v>Elmiene</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L137" t="str">
-        <v>Special - Elmiene</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Heart Attack</v>
+        <v>STAY</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>CANDY</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:52</v>
+        <v>3:06</v>
       </c>
       <c r="H138" t="str">
-        <v>Justine Skye</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L138" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>STAY</v>
+        <v>Unglued</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>STAY - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G139" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H139" t="str">
-        <v>Stray Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L139" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Unglued</v>
+        <v>Ritual</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Work of Heart</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:54</v>
+        <v>3:01</v>
       </c>
       <c r="H140" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L140" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Ritual</v>
+        <v>The Best</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Ritual - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G141" t="str">
-        <v>3:01</v>
+        <v>3:48</v>
       </c>
       <c r="H141" t="str">
-        <v>Icona Pop</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L141" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>The Best</v>
+        <v>Smile</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:48</v>
+        <v>3:50</v>
       </c>
       <c r="H142" t="str">
-        <v>Conan Gray</v>
+        <v>Two Shell</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L142" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Smile</v>
+        <v>Duro</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Smile - Single</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H143" t="str">
-        <v>Two Shell</v>
+        <v>Skrillex</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L143" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Duro</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Duro - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>2:58</v>
       </c>
       <c r="H144" t="str">
-        <v>Skrillex</v>
+        <v>Sublime</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L144" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Carousel</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G145" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H145" t="str">
-        <v>Sublime</v>
+        <v>Cannons</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L145" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Carousel</v>
+        <v>Mercy</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Everything Glows</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:36</v>
+        <v>3:49</v>
       </c>
       <c r="H146" t="str">
-        <v>Cannons</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L146" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Mercy</v>
+        <v>Palms</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Mercy - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:49</v>
+        <v>3:18</v>
       </c>
       <c r="H147" t="str">
-        <v>PRESIDENT</v>
+        <v>The Maine</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L147" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Palms</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Palms - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G148" t="str">
-        <v>3:18</v>
+        <v>5:28</v>
       </c>
       <c r="H148" t="str">
-        <v>The Maine</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L148" t="str">
-        <v>Palms - The Maine</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Ozzy's Song</v>
+        <v>Danger</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>5:28</v>
+        <v>2:19</v>
       </c>
       <c r="H149" t="str">
-        <v>Black Label Society</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L149" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Danger</v>
+        <v>Icarus</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Danger - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:19</v>
+        <v>4:25</v>
       </c>
       <c r="H150" t="str">
-        <v>Nia Archives</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L150" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Icarus</v>
+        <v>idk idk</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Icarus - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>4:25</v>
+        <v>2:26</v>
       </c>
       <c r="H151" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L151" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>idk idk</v>
+        <v>Tonight</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>idk idk - Single</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:26</v>
+        <v>2:25</v>
       </c>
       <c r="H152" t="str">
-        <v>Jim Legxacy</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L152" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tonight</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Tonight - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G153" t="str">
-        <v>2:25</v>
+        <v>3:44</v>
       </c>
       <c r="H153" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L153" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Switcheroo</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G154" t="str">
-        <v>3:44</v>
+        <v>2:45</v>
       </c>
       <c r="H154" t="str">
-        <v>Gelli Haha</v>
+        <v>BIA</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L154" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G155" t="str">
-        <v>2:45</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>BIA</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L155" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>this girl wants everything</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G156" t="str">
-        <v>3:33</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Isaia Huron</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L156" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>2:41</v>
       </c>
       <c r="H157" t="str">
-        <v>Slayyyter</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L157" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Kingdom of Fear</v>
+        <v>R3verse</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Deep Water - EP</v>
+        <v>takeaways</v>
       </c>
       <c r="G158" t="str">
-        <v>2:41</v>
+        <v>3:31</v>
       </c>
       <c r="H158" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Medium Build</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L158" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>R3verse</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>takeaways</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G159" t="str">
-        <v>3:31</v>
+        <v>2:32</v>
       </c>
       <c r="H159" t="str">
-        <v>Medium Build</v>
+        <v>MIKE</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L159" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>heart of gold</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H160" t="str">
-        <v>MIKE</v>
+        <v>kai devega</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L160" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>heart of gold</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>heart of gold - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G161" t="str">
-        <v>2:51</v>
+        <v>4:21</v>
       </c>
       <c r="H161" t="str">
-        <v>kai devega</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L161" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Breaking Down</v>
+        <v>Dream House</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Skeletor</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:21</v>
+        <v>2:54</v>
       </c>
       <c r="H162" t="str">
-        <v>Chief Keef</v>
+        <v>Empress Of</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L162" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Dream House</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Dream House - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:54</v>
+        <v>2:51</v>
       </c>
       <c r="H163" t="str">
-        <v>Empress Of</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L163" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Baby Blue</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H164" t="str">
-        <v>Cody Simpson</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L164" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G165" t="str">
-        <v>2:37</v>
+        <v>4:05</v>
       </c>
       <c r="H165" t="str">
-        <v>MEDUZA</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L165" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Forever Now</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>4:05</v>
+        <v>3:46</v>
       </c>
       <c r="H166" t="str">
-        <v>Switchfoot</v>
+        <v>Benny G</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L166" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:46</v>
+        <v>3:03</v>
       </c>
       <c r="H167" t="str">
-        <v>Benny G</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L167" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>3:03</v>
+        <v>4:19</v>
       </c>
       <c r="H168" t="str">
-        <v>Eric Bellinger</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L168" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:19</v>
+        <v>2:10</v>
       </c>
       <c r="H169" t="str">
-        <v>Anish Kumar</v>
+        <v>WesGhost</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L169" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>GASLIGHT</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:10</v>
+        <v>3:17</v>
       </c>
       <c r="H170" t="str">
-        <v>WesGhost</v>
+        <v>GERD</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L170" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Truth To Be Told</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H171" t="str">
-        <v>GERD</v>
+        <v>Prospa</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L171" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Free Your Mind</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>Prospa</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L172" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Down To The Bone</v>
+        <v>Breathe</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:51</v>
+        <v>2:48</v>
       </c>
       <c r="H173" t="str">
-        <v>Josh Baker</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L173" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Breathe</v>
+        <v>xs</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Breathe - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H174" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L174" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>xs</v>
+        <v>Sail</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>xs - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G175" t="str">
-        <v>3:19</v>
+        <v>4:54</v>
       </c>
       <c r="H175" t="str">
-        <v>Ashley Cooke</v>
+        <v>Future Islands</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L175" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Sail</v>
+        <v>Dreaming</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G176" t="str">
-        <v>4:54</v>
+        <v>3:33</v>
       </c>
       <c r="H176" t="str">
-        <v>Future Islands</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L176" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Dreaming</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Dear Nashville</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G177" t="str">
-        <v>3:33</v>
+        <v>2:39</v>
       </c>
       <c r="H177" t="str">
-        <v>Ashley Monroe</v>
+        <v>Armanii</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L177" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>NEW TINGZ</v>
+        <v>La Opinión</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G178" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H178" t="str">
-        <v>Armanii</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L178" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>La Opinión</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Mis Compas El Final</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:23</v>
+        <v>3:24</v>
       </c>
       <c r="H179" t="str">
-        <v>Joss Favela</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L179" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>qué ves en mí?</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:24</v>
+        <v>2:43</v>
       </c>
       <c r="H180" t="str">
-        <v>Paloma Morphy</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L180" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:43</v>
+        <v>2:16</v>
       </c>
       <c r="H181" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L181" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>TUTUTU</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>TUTUTU - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:16</v>
+        <v>2:56</v>
       </c>
       <c r="H182" t="str">
-        <v>ELENA ROSE</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L182" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>Me Neither</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G183" t="str">
-        <v>2:56</v>
+        <v>3:32</v>
       </c>
       <c r="H183" t="str">
-        <v>2'Live Bre</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L183" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Me Neither</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G184" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Ty Myers</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L184" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Cole Palmer</v>
+        <v>Wonder</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Solid Ground</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:48</v>
+        <v>3:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Limoblaze</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L185" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Wonder</v>
+        <v>ICU</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Wonder - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:48</v>
+        <v>2:53</v>
       </c>
       <c r="H186" t="str">
-        <v>Meeks Carter</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L186" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ICU</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>ICU - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G187" t="str">
-        <v>2:53</v>
+        <v>2:45</v>
       </c>
       <c r="H187" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Jozzy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L187" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Waiting Room</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Waiting Room - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:45</v>
+        <v>3:21</v>
       </c>
       <c r="H188" t="str">
-        <v>Jozzy</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
       </c>
       <c r="L188" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Waiting Room - Jenevieve</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Waiting Room</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Waiting Room - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G189" t="str">
-        <v>3:21</v>
+        <v>4:02</v>
       </c>
       <c r="H189" t="str">
-        <v>Jenevieve</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L189" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Rise</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:02</v>
+        <v>3:51</v>
       </c>
       <c r="H190" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L190" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Roll On Thru</v>
+        <v>Delicately</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:51</v>
+        <v>3:20</v>
       </c>
       <c r="H191" t="str">
-        <v>Hayden Everett</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L191" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Delicately</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Delicately - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H192" t="str">
-        <v>Andrea Bejar</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L192" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>One Of Those Things</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G193" t="str">
-        <v>3:27</v>
+        <v>6:04</v>
       </c>
       <c r="H193" t="str">
-        <v>Lucy Clearwater</v>
+        <v>José González</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L193" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>For Every Dusk</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G194" t="str">
-        <v>6:04</v>
+        <v>3:33</v>
       </c>
       <c r="H194" t="str">
-        <v>José González</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L194" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>I'll Wait</v>
+        <v>Daisy</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:33</v>
+        <v>3:02</v>
       </c>
       <c r="H195" t="str">
-        <v>Buzzy Lee</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L195" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Daisy</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Daisy - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G196" t="str">
-        <v>3:02</v>
+        <v>3:57</v>
       </c>
       <c r="H196" t="str">
-        <v>Lola Blue</v>
+        <v>james K</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L196" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-30</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Friend Remixes</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:57</v>
+        <v>2:45</v>
       </c>
       <c r="H197" t="str">
-        <v>james K</v>
+        <v>MAVICA</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L197" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Fort</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-30</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Perdidos - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:45</v>
+        <v>2:27</v>
       </c>
       <c r="H198" t="str">
-        <v>MAVICA</v>
+        <v>Lamb</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L198" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Fort</v>
+        <v>SAME LA</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-30</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Fort - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:27</v>
+        <v>3:44</v>
       </c>
       <c r="H199" t="str">
-        <v>Lamb</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L199" t="str">
-        <v>Fort - Lamb</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SAME LA</v>
+        <v>Working On It</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-30</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>SAME LA - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:44</v>
+        <v>3:06</v>
       </c>
       <c r="H200" t="str">
-        <v>Tiffany Day</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L200" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Working On It</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-30</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Working On It - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:06</v>
+        <v>4:03</v>
       </c>
       <c r="H201" t="str">
-        <v>Arthur Hill</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L201" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>spring cleaning</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-30</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H202" t="str">
-        <v>Ethan Regan</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L202" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Just Drivin'</v>
+        <v>Simple Things</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-30</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H203" t="str">
-        <v>Presley Haile</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L203" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Simple Things</v>
+        <v>Want It Back</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-30</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Simple Things - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:46</v>
+        <v>3:27</v>
       </c>
       <c r="H204" t="str">
-        <v>Evening Elephants</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L204" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Want It Back</v>
+        <v>Bite Down</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-30</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Want It Back - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:27</v>
+        <v>3:36</v>
       </c>
       <c r="H205" t="str">
-        <v>Giant Rooks</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L205" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Bite Down</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-30</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Bite Down - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G206" t="str">
-        <v>3:36</v>
+        <v>5:42</v>
       </c>
       <c r="H206" t="str">
-        <v>Anna Sofia</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L206" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Demons</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D207" t="str">
         <v>2026-03-30</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G207" t="str">
-        <v>5:42</v>
+        <v>2:42</v>
       </c>
       <c r="H207" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Anella</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L207" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Demons</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D208" t="str">
         <v>2026-03-30</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>2:42</v>
+        <v>3:35</v>
       </c>
       <c r="H208" t="str">
-        <v>Anella</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L208" t="str">
-        <v>Demons - Anella</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Es brennt...</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D209" t="str">
         <v>2026-03-30</v>
@@ -8317,36 +8317,36 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G209" t="str">
-        <v>3:35</v>
+        <v>3:49</v>
       </c>
       <c r="H209" t="str">
-        <v>Till Lindemann</v>
+        <v>Enslaved</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L209" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Fire Marengo</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D210" t="str">
         <v>2026-03-30</v>
@@ -8355,68 +8355,30 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G210" t="str">
-        <v>3:49</v>
+        <v>4:09</v>
       </c>
       <c r="H210" t="str">
-        <v>Enslaved</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L210" t="str">
-        <v>Fire Marengo - Enslaved</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Close to the Bone</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-03-30</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G211" t="str">
-        <v>4:09</v>
-      </c>
-      <c r="H211" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
-      </c>
-      <c r="L211" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L211"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:L237"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל סקעת – אמונה שבורה</v>
+        <v>שי וינר - יבוא שלום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%9e%d7%95%d7%a0%d7%94-%d7%a9%d7%91%d7%95%d7%a8%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410287&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הראל סקעת שר בלדה שמצליחה לגעת בנושא עמוק – משבר אמונה דרך הגשה עדינה, כמעט מתפללת. כבר מהשורה – “באמונה שבורה באתי נקי עד אליך” נוצר מתח. מצד אחד: רצון להיות “נקי”, כן, פתוח. מצד שני: אמונה שנשברה- משהו בסיסי</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל סקעת – אמונה שבורה</v>
+        <v>שי וינר - יבוא שלום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>שחר גזנלי - 2 כוסות יין</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410286&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-30</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>שחר גזנלי - 2 כוסות יין</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>קול החברים - מחרוזת רוקדת בלילות 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410285&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-30</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Miley Cyrus</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>קול החברים - מחרוזת רוקדת בלילות 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>עמית סמוכי - ראויה לאהבה</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410284&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-30</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:42</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Conan Gray</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>עמית סמוכי - ראויה לאהבה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>עופר בדיחי - בצל עצי התאנה</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410283&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-30</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>2:16</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>עופר בדיחי - בצל עצי התאנה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>סטפן לגר - מינימום</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410282&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-30</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:08</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Kylie Morgan</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>סטפן לגר - מינימום</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>נוי אביטל - ההצגה חייבת להימשך</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410281&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-30</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>נוי אביטל - ההצגה חייבת להימשך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>מנשה סביליה - מחרוזת אם קצת עצוב 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410280&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-30</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Angelina Mango</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>מנשה סביליה - מחרוזת אם קצת עצוב 2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>מינקובסקי - מכלוף</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410279&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-30</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:59</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Julio Iglesias</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>מינקובסקי - מכלוף</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>מאור אברהם - כל הלילה</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410278&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-30</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>2:59</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Loreen</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>מאור אברהם - כל הלילה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>מאור אברהם - הלב הזה שלך</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410277&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-30</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>2:58</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>Jessie Ware</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>מאור אברהם - הלב הזה שלך</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>יוסף נטיב - אנשים כאלה</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410276&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-30</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>Holly Humberstone</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>יוסף נטיב - אנשים כאלה</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>יוסי שטרית - חורף אחד בלעדייך</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410275&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-30</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>יוסי שטרית - חורף אחד בלעדייך</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>האחים אהרון - השם ישמרך</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410274&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-30</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Ella Langley</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>האחים אהרון - השם ישמרך</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>בני אלבז - עם פלדה</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410273&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-30</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>6:43</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>David Gilmour</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>בני אלבז - עם פלדה</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>אריאל רביבו - גאולה</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410272&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-30</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>4:52</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>Eagles</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>אריאל רביבו - גאולה</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>אריאל לוי - מחרוזת שמח בני 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410271&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-30</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>Moody Joody</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>אריאל לוי - מחרוזת שמח בני 2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>תמר אופיר - בדמייך חיי</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410270&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-30</v>
@@ -1097,16 +1097,16 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>3:28</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>Jackson Dean</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>תמר אופיר - בדמייך חיי</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>ליאל נחתום - שערי שמים פתח</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410269&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-30</v>
@@ -1135,16 +1135,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>ליאל נחתום - שערי שמים פתח</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>הראל סקעת - אמונה שבורה</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410268&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-30</v>
@@ -1173,16 +1173,16 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>4:00</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>Madison Cunningham</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>הראל סקעת - אמונה שבורה</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>החצר האחורית של ג'וני - לבד</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410267&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-30</v>
@@ -1211,16 +1211,16 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>5:35</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>mary in the junkyard</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>החצר האחורית של ג'וני - לבד</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>הודיה בנישו - בינתיים</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410266&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-30</v>
@@ -1249,16 +1249,16 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>Adam Sanders</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>הודיה בנישו - בינתיים</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>אליהו חייט - אני קורא לך</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410265&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-30</v>
@@ -1287,16 +1287,16 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>3:40</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>SIENNA SPIRO</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>אליהו חייט - אני קורא לך</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>אור סלמן - הלב הטוב ינצח</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410264&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-30</v>
@@ -1325,16 +1325,16 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>2:25</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>twocolors</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>אור סלמן - הלב הטוב ינצח</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>אהרון ירימי &amp; ששי יעיש - אביר ישראל 2026</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410263&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-30</v>
@@ -1363,16 +1363,16 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>3:42</v>
+        <v/>
       </c>
       <c r="H26" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>אהרון ירימי &amp; ששי יעיש - אביר ישראל 2026</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>אביר יעקב - עד מתי נעצור</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410262&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-30</v>
@@ -1401,16 +1401,16 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H27" t="str">
-        <v>Prince</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>אביר יעקב - עד מתי נעצור</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-30</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:12</v>
+        <v>3:56</v>
       </c>
       <c r="H28" t="str">
-        <v>RAYE</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-30</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:30</v>
+        <v>2:50</v>
       </c>
       <c r="H29" t="str">
-        <v>The Warning</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:18</v>
+        <v>3:42</v>
       </c>
       <c r="H30" t="str">
-        <v>Pentatonix</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:33</v>
+        <v>2:16</v>
       </c>
       <c r="H31" t="str">
-        <v>Tenille Townes</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:53</v>
+        <v>3:08</v>
       </c>
       <c r="H32" t="str">
-        <v>Jessie Ware</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:37</v>
+        <v>3:38</v>
       </c>
       <c r="H33" t="str">
-        <v>Niall Horan</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-30</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:26</v>
+        <v>3:01</v>
       </c>
       <c r="H34" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-30</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:40</v>
+        <v>3:59</v>
       </c>
       <c r="H35" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-30</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:30</v>
+        <v>2:59</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>Loreen</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B37" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-30</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:02</v>
+        <v>2:58</v>
       </c>
       <c r="H37" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-30</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:40</v>
+        <v>3:49</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-30</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:22</v>
+        <v>3:22</v>
       </c>
       <c r="H39" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-30</v>
@@ -1895,10 +1895,10 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:47</v>
+        <v>3:50</v>
       </c>
       <c r="H40" t="str">
         <v>Ella Langley</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-30</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:39</v>
+        <v>6:43</v>
       </c>
       <c r="H41" t="str">
-        <v>Cannons</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-30</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:10</v>
+        <v>4:52</v>
       </c>
       <c r="H42" t="str">
-        <v>Luke Combs</v>
+        <v>Eagles</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-30</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:47</v>
+        <v>3:13</v>
       </c>
       <c r="H43" t="str">
-        <v>Nessa Barrett</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-30</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:14</v>
+        <v>3:28</v>
       </c>
       <c r="H44" t="str">
-        <v>aron!</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-30</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:00</v>
+        <v>3:01</v>
       </c>
       <c r="H45" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-30</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:56</v>
+        <v>4:00</v>
       </c>
       <c r="H46" t="str">
-        <v>DMA'S</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-30</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:17</v>
+        <v>5:35</v>
       </c>
       <c r="H47" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:17</v>
+        <v>3:01</v>
       </c>
       <c r="H48" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:31</v>
+        <v>3:40</v>
       </c>
       <c r="H49" t="str">
-        <v>Nick Carter</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-30</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:38</v>
+        <v>2:25</v>
       </c>
       <c r="H50" t="str">
-        <v>Carly Pearce</v>
+        <v>twocolors</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-30</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:11</v>
+        <v>3:42</v>
       </c>
       <c r="H51" t="str">
-        <v>OneRepublic</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-30</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:57</v>
+        <v>3:56</v>
       </c>
       <c r="H52" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Prince</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-30</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H53" t="str">
-        <v>Armin van Buuren</v>
+        <v>RAYE</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>7:10</v>
+        <v>3:30</v>
       </c>
       <c r="H54" t="str">
-        <v>David Gilmour</v>
+        <v>The Warning</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-30</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H55" t="str">
-        <v>Grace Enger</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-30</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:05</v>
+        <v>3:33</v>
       </c>
       <c r="H56" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-30</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:12</v>
+        <v>5:53</v>
       </c>
       <c r="H57" t="str">
-        <v>Freya Ridings</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-30</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>9:11</v>
+        <v>2:37</v>
       </c>
       <c r="H58" t="str">
-        <v>David Gilmour</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-30</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:49</v>
+        <v>2:26</v>
       </c>
       <c r="H59" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-30</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:28</v>
+        <v>2:40</v>
       </c>
       <c r="H60" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-30</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:31</v>
+        <v>3:30</v>
       </c>
       <c r="H61" t="str">
-        <v>Martin Garrix</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-30</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:11</v>
+        <v>4:02</v>
       </c>
       <c r="H62" t="str">
-        <v>Baby Queen</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-30</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:40</v>
       </c>
       <c r="H63" t="str">
-        <v>HAUSER</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-30</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:34</v>
+        <v>2:22</v>
       </c>
       <c r="H64" t="str">
-        <v>Holly Humberstone</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-30</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H65" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-30</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:51</v>
+        <v>3:39</v>
       </c>
       <c r="H66" t="str">
-        <v>Rick Astley</v>
+        <v>Cannons</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-30</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:39</v>
+        <v>4:10</v>
       </c>
       <c r="H67" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-30</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:08</v>
+        <v>4:47</v>
       </c>
       <c r="H68" t="str">
-        <v>Jessie J</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-30</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:46</v>
+        <v>2:14</v>
       </c>
       <c r="H69" t="str">
-        <v>Bishop Briggs</v>
+        <v>aron!</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-30</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:42</v>
+        <v>4:00</v>
       </c>
       <c r="H70" t="str">
-        <v>Dean Lewis</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-30</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:31</v>
+        <v>3:56</v>
       </c>
       <c r="H71" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>DMA'S</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-30</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H72" t="str">
-        <v>Luke Combs</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-30</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:22</v>
+        <v>3:17</v>
       </c>
       <c r="H73" t="str">
-        <v>Allison Russell</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-30</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:43</v>
+        <v>3:31</v>
       </c>
       <c r="H74" t="str">
-        <v>We Three</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-30</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:54</v>
+        <v>3:38</v>
       </c>
       <c r="H75" t="str">
-        <v>paris jackson</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-30</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:46</v>
+        <v>4:11</v>
       </c>
       <c r="H76" t="str">
-        <v>Kane Brown</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-30</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-30</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:57</v>
+        <v>3:47</v>
       </c>
       <c r="H78" t="str">
-        <v>Malcolm Todd</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-30</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:38</v>
+        <v>7:10</v>
       </c>
       <c r="H79" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-30</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:29</v>
+        <v>3:06</v>
       </c>
       <c r="H80" t="str">
-        <v>Kungs</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-30</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:28</v>
+        <v>3:05</v>
       </c>
       <c r="H81" t="str">
-        <v>Sunday (1994)</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-30</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:26</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>aron!</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-30</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:51</v>
+        <v>9:11</v>
       </c>
       <c r="H83" t="str">
-        <v>Colinstoughmusic</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-30</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:49</v>
+        <v>3:49</v>
       </c>
       <c r="H84" t="str">
-        <v>Sunday (1994)</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-30</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:16</v>
+        <v>3:28</v>
       </c>
       <c r="H85" t="str">
-        <v>Owen Riegling</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-30</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H86" t="str">
-        <v>LANY</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-30</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:25</v>
+        <v>3:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Maverick Sabre</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-30</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:50</v>
+        <v>2:27</v>
       </c>
       <c r="H88" t="str">
-        <v>Amanda Jordan</v>
+        <v>HAUSER</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-30</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H89" t="str">
-        <v>Beabadoobee</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-30</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:58</v>
+        <v>2:50</v>
       </c>
       <c r="H90" t="str">
-        <v>Spacey Jane</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-30</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:25</v>
+        <v>3:51</v>
       </c>
       <c r="H91" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-30</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:09</v>
+        <v>2:39</v>
       </c>
       <c r="H92" t="str">
-        <v>Mei Semones</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-30</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:08</v>
+        <v>5:08</v>
       </c>
       <c r="H93" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-30</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:57</v>
+        <v>3:46</v>
       </c>
       <c r="H94" t="str">
-        <v>Natalie Jane</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-30</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-30</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:12</v>
+        <v>2:31</v>
       </c>
       <c r="H96" t="str">
-        <v>David Gilmour</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-30</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>3:14</v>
       </c>
       <c r="H97" t="str">
-        <v>Far Caspian</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-30</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:34</v>
+        <v>3:22</v>
       </c>
       <c r="H98" t="str">
-        <v>Celine Dion</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:48</v>
+        <v>3:43</v>
       </c>
       <c r="H99" t="str">
-        <v>Harry Styles</v>
+        <v>We Three</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-30</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:58</v>
+        <v>2:54</v>
       </c>
       <c r="H100" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>paris jackson</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-30</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:33</v>
+        <v>2:46</v>
       </c>
       <c r="H101" t="str">
-        <v>Ellise</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-30</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>5:01</v>
+        <v>3:37</v>
       </c>
       <c r="H102" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Days We Left Behind</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:18</v>
+        <v>2:57</v>
       </c>
       <c r="H103" t="str">
-        <v>Paul McCartney</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:47</v>
+        <v>3:38</v>
       </c>
       <c r="H104" t="str">
-        <v>Miley Cyrus</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>6:17</v>
+        <v>4:29</v>
       </c>
       <c r="H105" t="str">
-        <v>RAYE</v>
+        <v>Kungs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>MARATHON</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>MARATHON - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:49</v>
+        <v>4:28</v>
       </c>
       <c r="H106" t="str">
-        <v>Becky G</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ALL THE TIME</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>3:26</v>
       </c>
       <c r="H107" t="str">
-        <v>John Summit</v>
+        <v>aron!</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Sucker For Love</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sexistential</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:34</v>
+        <v>3:51</v>
       </c>
       <c r="H108" t="str">
-        <v>Robyn</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>FATHER</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>BULLY</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
         <v>2:49</v>
       </c>
       <c r="H109" t="str">
-        <v>Kanye West</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Lose Control</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>ADL</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:39</v>
+        <v>4:16</v>
       </c>
       <c r="H110" t="str">
-        <v>Yeat</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Zavier</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>4:16</v>
       </c>
       <c r="H111" t="str">
-        <v>Fetty Wap</v>
+        <v>LANY</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WAGWAN</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>2:07</v>
+        <v>3:25</v>
       </c>
       <c r="H112" t="str">
-        <v>Central Cee</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Sideways</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>KONNAKOL</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>3:12</v>
+        <v>2:50</v>
       </c>
       <c r="H113" t="str">
-        <v>ZAYN</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Automatic</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Superbloom</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>2:57</v>
+        <v>3:57</v>
       </c>
       <c r="H114" t="str">
-        <v>Jessie Ware</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tractor Beam</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ricochet</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:34</v>
+        <v>3:58</v>
       </c>
       <c r="H115" t="str">
-        <v>Snail Mail</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>prom queen</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>prom queen - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G116" t="str">
-        <v>2:43</v>
+        <v>3:25</v>
       </c>
       <c r="H116" t="str">
-        <v>Amelia Moore</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pal Agua</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Pal Agua - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G117" t="str">
-        <v>3:26</v>
+        <v>4:09</v>
       </c>
       <c r="H117" t="str">
-        <v>J Balvin</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v/>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Phoenix</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Phoenix - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G118" t="str">
-        <v>2:24</v>
+        <v>2:08</v>
       </c>
       <c r="H118" t="str">
-        <v>Marshmello</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v/>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v/>
       </c>
       <c r="L118" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G119" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H119" t="str">
-        <v>Ne-Yo</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v/>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v/>
       </c>
       <c r="L119" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Feel Your Rain</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G120" t="str">
-        <v>3:36</v>
+        <v>3:13</v>
       </c>
       <c r="H120" t="str">
-        <v>Eli</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v/>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v/>
       </c>
       <c r="L120" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Lonely</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B121" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Ö</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>4:12</v>
       </c>
       <c r="H121" t="str">
-        <v>Fcukers</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v/>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v/>
       </c>
       <c r="L121" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Back in Love</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B122" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Back in Love - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G122" t="str">
-        <v>3:14</v>
+        <v>3:57</v>
       </c>
       <c r="H122" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v/>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v/>
       </c>
       <c r="L122" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sideways</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B123" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Whatever's Clever!</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G123" t="str">
-        <v>3:55</v>
+        <v>3:34</v>
       </c>
       <c r="H123" t="str">
-        <v>Charlie Puth</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v/>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v/>
       </c>
       <c r="L123" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B124" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Honora</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G124" t="str">
-        <v>4:22</v>
+        <v>3:48</v>
       </c>
       <c r="H124" t="str">
-        <v>Flea</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v/>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v/>
       </c>
       <c r="L124" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B125" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G125" t="str">
-        <v>2:58</v>
+        <v>4:58</v>
       </c>
       <c r="H125" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v/>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v/>
       </c>
       <c r="L125" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B126" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G126" t="str">
-        <v>3:02</v>
+        <v>2:33</v>
       </c>
       <c r="H126" t="str">
-        <v>Honey Bxby</v>
+        <v>Ellise</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v/>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v/>
       </c>
       <c r="L126" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>One Thing At A Time</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Creature of Habit</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G127" t="str">
-        <v>4:42</v>
+        <v>5:01</v>
       </c>
       <c r="H127" t="str">
-        <v>Courtney Barnett</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v/>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v/>
       </c>
       <c r="L127" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>wasteland</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>wasteland - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G128" t="str">
-        <v>3:05</v>
+        <v>1:37</v>
       </c>
       <c r="H128" t="str">
-        <v>Yuna</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L128" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Back Home</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>getting up to no good</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G129" t="str">
-        <v>2:31</v>
+        <v>1:36</v>
       </c>
       <c r="H129" t="str">
-        <v>Artemas</v>
+        <v>MIKE</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L129" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Por LA</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>TODO Ø NADA</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G130" t="str">
-        <v>2:19</v>
+        <v>3:18</v>
       </c>
       <c r="H130" t="str">
-        <v>Linea Personal</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L130" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>You Lead Me</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:14</v>
+        <v>2:47</v>
       </c>
       <c r="H131" t="str">
-        <v>Lauren Daigle</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L131" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Just A Kid</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Broken View</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G132" t="str">
-        <v>4:18</v>
+        <v>6:17</v>
       </c>
       <c r="H132" t="str">
-        <v>Sam Barber</v>
+        <v>RAYE</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L132" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Country And She Knows It</v>
+        <v>MARATHON</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H133" t="str">
-        <v>Luke Bryan</v>
+        <v>Becky G</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L133" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Georgia On My Mind</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:35</v>
+        <v>3:00</v>
       </c>
       <c r="H134" t="str">
-        <v>Thomas Rhett</v>
+        <v>John Summit</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L134" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Deep Blue</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Deep Blue</v>
+        <v>Sexistential</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>3:34</v>
       </c>
       <c r="H135" t="str">
-        <v>ERNEST</v>
+        <v>Robyn</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L135" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Special</v>
+        <v>FATHER</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>sounds for someone</v>
+        <v>BULLY</v>
       </c>
       <c r="G136" t="str">
         <v>2:49</v>
       </c>
       <c r="H136" t="str">
-        <v>Elmiene</v>
+        <v>Kanye West</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L136" t="str">
-        <v>Special - Elmiene</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Heart Attack</v>
+        <v>Lose Control</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>CANDY</v>
+        <v>ADL</v>
       </c>
       <c r="G137" t="str">
-        <v>2:52</v>
+        <v>2:39</v>
       </c>
       <c r="H137" t="str">
-        <v>Justine Skye</v>
+        <v>Yeat</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L137" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>STAY</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>STAY - Single</v>
+        <v>Zavier</v>
       </c>
       <c r="G138" t="str">
-        <v>3:06</v>
+        <v>3:44</v>
       </c>
       <c r="H138" t="str">
-        <v>Stray Kids</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L138" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Unglued</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Work of Heart</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G139" t="str">
-        <v>3:54</v>
+        <v>2:07</v>
       </c>
       <c r="H139" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Central Cee</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L139" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Ritual</v>
+        <v>Sideways</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Ritual - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G140" t="str">
-        <v>3:01</v>
+        <v>3:12</v>
       </c>
       <c r="H140" t="str">
-        <v>Icona Pop</v>
+        <v>ZAYN</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L140" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>The Best</v>
+        <v>Automatic</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Superbloom</v>
       </c>
       <c r="G141" t="str">
-        <v>3:48</v>
+        <v>2:57</v>
       </c>
       <c r="H141" t="str">
-        <v>Conan Gray</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L141" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Smile</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Smile - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G142" t="str">
-        <v>3:50</v>
+        <v>3:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Two Shell</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L142" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Duro</v>
+        <v>prom queen</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Duro - Single</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:05</v>
+        <v>2:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Skrillex</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L143" t="str">
-        <v>Duro - Skrillex</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H144" t="str">
-        <v>Sublime</v>
+        <v>J Balvin</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L144" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Carousel</v>
+        <v>Phoenix</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Everything Glows</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:36</v>
+        <v>2:24</v>
       </c>
       <c r="H145" t="str">
-        <v>Cannons</v>
+        <v>Marshmello</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L145" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Mercy</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Mercy - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:49</v>
+        <v>2:56</v>
       </c>
       <c r="H146" t="str">
-        <v>PRESIDENT</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L146" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Palms</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Palms - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:18</v>
+        <v>3:36</v>
       </c>
       <c r="H147" t="str">
-        <v>The Maine</v>
+        <v>Eli</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L147" t="str">
-        <v>Palms - The Maine</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Ozzy's Song</v>
+        <v>Lonely</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Ö</v>
       </c>
       <c r="G148" t="str">
-        <v>5:28</v>
+        <v>2:58</v>
       </c>
       <c r="H148" t="str">
-        <v>Black Label Society</v>
+        <v>Fcukers</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L148" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Danger</v>
+        <v>Back in Love</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Danger - Single</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:19</v>
+        <v>3:14</v>
       </c>
       <c r="H149" t="str">
-        <v>Nia Archives</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L149" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Icarus</v>
+        <v>Sideways</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Icarus - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G150" t="str">
-        <v>4:25</v>
+        <v>3:55</v>
       </c>
       <c r="H150" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L150" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>idk idk</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>idk idk - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G151" t="str">
-        <v>2:26</v>
+        <v>4:22</v>
       </c>
       <c r="H151" t="str">
-        <v>Jim Legxacy</v>
+        <v>Flea</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L151" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tonight</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Tonight - Single</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:25</v>
+        <v>2:58</v>
       </c>
       <c r="H152" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L152" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Switcheroo</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:44</v>
+        <v>3:02</v>
       </c>
       <c r="H153" t="str">
-        <v>Gelli Haha</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L153" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G154" t="str">
-        <v>2:45</v>
+        <v>4:42</v>
       </c>
       <c r="H154" t="str">
-        <v>BIA</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L154" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>this girl wants everything</v>
+        <v>wasteland</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>3:05</v>
       </c>
       <c r="H155" t="str">
-        <v>Isaia Huron</v>
+        <v>Yuna</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L155" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>2:31</v>
       </c>
       <c r="H156" t="str">
-        <v>Slayyyter</v>
+        <v>Artemas</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L156" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Por LA</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Deep Water - EP</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G157" t="str">
-        <v>2:41</v>
+        <v>2:19</v>
       </c>
       <c r="H157" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L157" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>R3verse</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>takeaways</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G158" t="str">
-        <v>3:31</v>
+        <v>4:14</v>
       </c>
       <c r="H158" t="str">
-        <v>Medium Build</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L158" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Broken View</v>
       </c>
       <c r="G159" t="str">
-        <v>2:32</v>
+        <v>4:18</v>
       </c>
       <c r="H159" t="str">
-        <v>MIKE</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L159" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>heart of gold</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>heart of gold - Single</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H160" t="str">
-        <v>kai devega</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L160" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Breaking Down</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Skeletor</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:21</v>
+        <v>2:35</v>
       </c>
       <c r="H161" t="str">
-        <v>Chief Keef</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L161" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dream House</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Dream House - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G162" t="str">
-        <v>2:54</v>
+        <v>3:17</v>
       </c>
       <c r="H162" t="str">
-        <v>Empress Of</v>
+        <v>ERNEST</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L162" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Baby Blue</v>
+        <v>Special</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G163" t="str">
-        <v>2:51</v>
+        <v>2:49</v>
       </c>
       <c r="H163" t="str">
-        <v>Cody Simpson</v>
+        <v>Elmiene</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L163" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G164" t="str">
-        <v>2:37</v>
+        <v>2:52</v>
       </c>
       <c r="H164" t="str">
-        <v>MEDUZA</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L164" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>STAY</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Forever Now</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:05</v>
+        <v>3:06</v>
       </c>
       <c r="H165" t="str">
-        <v>Switchfoot</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L165" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Unglued</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G166" t="str">
-        <v>3:46</v>
+        <v>3:54</v>
       </c>
       <c r="H166" t="str">
-        <v>Benny G</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L166" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Ritual</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:03</v>
+        <v>3:01</v>
       </c>
       <c r="H167" t="str">
-        <v>Eric Bellinger</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L167" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>The Best</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G168" t="str">
-        <v>4:19</v>
+        <v>3:48</v>
       </c>
       <c r="H168" t="str">
-        <v>Anish Kumar</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L168" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>GASLIGHT</v>
+        <v>Smile</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H169" t="str">
-        <v>WesGhost</v>
+        <v>Two Shell</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L169" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Truth To Be Told</v>
+        <v>Duro</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:17</v>
+        <v>3:05</v>
       </c>
       <c r="H170" t="str">
-        <v>GERD</v>
+        <v>Skrillex</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L170" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Free Your Mind</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G171" t="str">
-        <v>3:21</v>
+        <v>2:58</v>
       </c>
       <c r="H171" t="str">
-        <v>Prospa</v>
+        <v>Sublime</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L171" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Down To The Bone</v>
+        <v>Carousel</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G172" t="str">
-        <v>2:51</v>
+        <v>3:36</v>
       </c>
       <c r="H172" t="str">
-        <v>Josh Baker</v>
+        <v>Cannons</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L172" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Breathe</v>
+        <v>Mercy</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Breathe - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:48</v>
+        <v>3:49</v>
       </c>
       <c r="H173" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L173" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>xs</v>
+        <v>Palms</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>xs - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:19</v>
+        <v>3:18</v>
       </c>
       <c r="H174" t="str">
-        <v>Ashley Cooke</v>
+        <v>The Maine</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L174" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Sail</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G175" t="str">
-        <v>4:54</v>
+        <v>5:28</v>
       </c>
       <c r="H175" t="str">
-        <v>Future Islands</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L175" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Dreaming</v>
+        <v>Danger</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Dear Nashville</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:33</v>
+        <v>2:19</v>
       </c>
       <c r="H176" t="str">
-        <v>Ashley Monroe</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L176" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>NEW TINGZ</v>
+        <v>Icarus</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:39</v>
+        <v>4:25</v>
       </c>
       <c r="H177" t="str">
-        <v>Armanii</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L177" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>La Opinión</v>
+        <v>idk idk</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Mis Compas El Final</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:23</v>
+        <v>2:26</v>
       </c>
       <c r="H178" t="str">
-        <v>Joss Favela</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L178" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>qué ves en mí?</v>
+        <v>Tonight</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H179" t="str">
-        <v>Paloma Morphy</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L179" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G180" t="str">
-        <v>2:43</v>
+        <v>3:44</v>
       </c>
       <c r="H180" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L180" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>TUTUTU</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>TUTUTU - Single</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>2:16</v>
+        <v>2:45</v>
       </c>
       <c r="H181" t="str">
-        <v>ELENA ROSE</v>
+        <v>BIA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L181" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G182" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H182" t="str">
-        <v>2'Live Bre</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L182" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Me Neither</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Heavy On The Soul</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G183" t="str">
-        <v>3:32</v>
+        <v>3:44</v>
       </c>
       <c r="H183" t="str">
-        <v>Ty Myers</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L183" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Cole Palmer</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Solid Ground</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>2:41</v>
       </c>
       <c r="H184" t="str">
-        <v>Limoblaze</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L184" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Wonder</v>
+        <v>R3verse</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Wonder - Single</v>
+        <v>takeaways</v>
       </c>
       <c r="G185" t="str">
-        <v>3:48</v>
+        <v>3:31</v>
       </c>
       <c r="H185" t="str">
-        <v>Meeks Carter</v>
+        <v>Medium Build</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L185" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>ICU</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>ICU - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G186" t="str">
-        <v>2:53</v>
+        <v>2:32</v>
       </c>
       <c r="H186" t="str">
-        <v>Joseph O'Brien</v>
+        <v>MIKE</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L186" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>heart of gold</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:45</v>
+        <v>2:51</v>
       </c>
       <c r="H187" t="str">
-        <v>Jozzy</v>
+        <v>kai devega</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L187" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Waiting Room</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Waiting Room - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G188" t="str">
-        <v>3:21</v>
+        <v>4:21</v>
       </c>
       <c r="H188" t="str">
-        <v>Jenevieve</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L188" t="str">
-        <v>Waiting Room - Jenevieve</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Dream House</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Rise</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:02</v>
+        <v>2:54</v>
       </c>
       <c r="H189" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Empress Of</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L189" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Roll On Thru</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:51</v>
+        <v>2:51</v>
       </c>
       <c r="H190" t="str">
-        <v>Hayden Everett</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L190" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Delicately</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Delicately - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:20</v>
+        <v>2:37</v>
       </c>
       <c r="H191" t="str">
-        <v>Andrea Bejar</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L191" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>One Of Those Things</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G192" t="str">
-        <v>3:27</v>
+        <v>4:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L192" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>For Every Dusk</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>6:04</v>
+        <v>3:46</v>
       </c>
       <c r="H193" t="str">
-        <v>José González</v>
+        <v>Benny G</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L193" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>I'll Wait</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:33</v>
+        <v>3:03</v>
       </c>
       <c r="H194" t="str">
-        <v>Buzzy Lee</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L194" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Daisy</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Daisy - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G195" t="str">
-        <v>3:02</v>
+        <v>4:19</v>
       </c>
       <c r="H195" t="str">
-        <v>Lola Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L195" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Friend Remixes</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:57</v>
+        <v>2:10</v>
       </c>
       <c r="H196" t="str">
-        <v>james K</v>
+        <v>WesGhost</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L196" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-30</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Perdidos - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:45</v>
+        <v>3:17</v>
       </c>
       <c r="H197" t="str">
-        <v>MAVICA</v>
+        <v>GERD</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L197" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Fort</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-30</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Fort - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:27</v>
+        <v>3:21</v>
       </c>
       <c r="H198" t="str">
-        <v>Lamb</v>
+        <v>Prospa</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L198" t="str">
-        <v>Fort - Lamb</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SAME LA</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-30</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>SAME LA - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:44</v>
+        <v>2:51</v>
       </c>
       <c r="H199" t="str">
-        <v>Tiffany Day</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L199" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Working On It</v>
+        <v>Breathe</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-30</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Working On It - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H200" t="str">
-        <v>Arthur Hill</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L200" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>spring cleaning</v>
+        <v>xs</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-30</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>spring cleaning - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H201" t="str">
-        <v>Ethan Regan</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L201" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Just Drivin'</v>
+        <v>Sail</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-30</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G202" t="str">
-        <v>3:26</v>
+        <v>4:54</v>
       </c>
       <c r="H202" t="str">
-        <v>Presley Haile</v>
+        <v>Future Islands</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L202" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Simple Things</v>
+        <v>Dreaming</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-30</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Simple Things - Single</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G203" t="str">
-        <v>3:46</v>
+        <v>3:33</v>
       </c>
       <c r="H203" t="str">
-        <v>Evening Elephants</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L203" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Want It Back</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-30</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Want It Back - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G204" t="str">
-        <v>3:27</v>
+        <v>2:39</v>
       </c>
       <c r="H204" t="str">
-        <v>Giant Rooks</v>
+        <v>Armanii</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L204" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Bite Down</v>
+        <v>La Opinión</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D205" t="str">
         <v>2026-03-30</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Bite Down - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G205" t="str">
-        <v>3:36</v>
+        <v>3:23</v>
       </c>
       <c r="H205" t="str">
-        <v>Anna Sofia</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L205" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D206" t="str">
         <v>2026-03-30</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>5:42</v>
+        <v>3:24</v>
       </c>
       <c r="H206" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L206" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Demons</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D207" t="str">
         <v>2026-03-30</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>2:42</v>
+        <v>2:43</v>
       </c>
       <c r="H207" t="str">
-        <v>Anella</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L207" t="str">
-        <v>Demons - Anella</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Es brennt...</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D208" t="str">
         <v>2026-03-30</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Es brennt... - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>3:35</v>
+        <v>2:16</v>
       </c>
       <c r="H208" t="str">
-        <v>Till Lindemann</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L208" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Fire Marengo</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D209" t="str">
         <v>2026-03-30</v>
@@ -8317,68 +8317,1094 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G209" t="str">
-        <v>3:49</v>
+        <v>2:56</v>
       </c>
       <c r="H209" t="str">
-        <v>Enslaved</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L209" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
+        <v>Me Neither</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Heavy On The Soul</v>
+      </c>
+      <c r="G210" t="str">
+        <v>3:32</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Ty Myers</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Me Neither - Ty Myers</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Cole Palmer</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Solid Ground</v>
+      </c>
+      <c r="G211" t="str">
+        <v>2:48</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Limoblaze</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Cole Palmer - Limoblaze</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Wonder</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Wonder - Single</v>
+      </c>
+      <c r="G212" t="str">
+        <v>3:48</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Meeks Carter</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Wonder - Meeks Carter</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>ICU</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>ICU - Single</v>
+      </c>
+      <c r="G213" t="str">
+        <v>2:53</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Joseph O'Brien</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
+      </c>
+      <c r="L213" t="str">
+        <v>ICU - Joseph O'Brien</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Supermans Weakness (feat. Chris Brown)</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>Soundtrack 2 Get Her Back</v>
+      </c>
+      <c r="G214" t="str">
+        <v>2:45</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Jozzy</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Waiting Room</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/waiting-room/1884548258</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>Waiting Room - Single</v>
+      </c>
+      <c r="G215" t="str">
+        <v>3:21</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Jenevieve</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/waiting-room/1884548243</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Waiting Room - Jenevieve</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>The Other Side Of Blue</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>Rise</v>
+      </c>
+      <c r="G216" t="str">
+        <v>4:02</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Melissa Etheridge</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+      </c>
+      <c r="L216" t="str">
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Roll On Thru</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+      </c>
+      <c r="D217" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v>Roll On Thru - Single</v>
+      </c>
+      <c r="G217" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H217" t="str">
+        <v>Hayden Everett</v>
+      </c>
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+      </c>
+      <c r="K217" t="str">
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Roll On Thru - Hayden Everett</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Delicately</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v>Delicately - Single</v>
+      </c>
+      <c r="G218" t="str">
+        <v>3:20</v>
+      </c>
+      <c r="H218" t="str">
+        <v>Andrea Bejar</v>
+      </c>
+      <c r="I218" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+      </c>
+      <c r="K218" t="str">
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Delicately - Andrea Bejar</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>One Of Those Things</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" t="str">
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+      </c>
+      <c r="D219" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v>One Of Those Things - Single</v>
+      </c>
+      <c r="G219" t="str">
+        <v>3:27</v>
+      </c>
+      <c r="H219" t="str">
+        <v>Lucy Clearwater</v>
+      </c>
+      <c r="I219" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+      </c>
+      <c r="K219" t="str">
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+      </c>
+      <c r="L219" t="str">
+        <v>One Of Those Things - Lucy Clearwater</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>For Every Dusk</v>
+      </c>
+      <c r="B220" t="str">
+        <v/>
+      </c>
+      <c r="C220" t="str">
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+      </c>
+      <c r="D220" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v>Against The Dying Of The Light</v>
+      </c>
+      <c r="G220" t="str">
+        <v>6:04</v>
+      </c>
+      <c r="H220" t="str">
+        <v>José González</v>
+      </c>
+      <c r="I220" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J220" t="str">
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+      </c>
+      <c r="K220" t="str">
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+      </c>
+      <c r="L220" t="str">
+        <v>For Every Dusk - José González</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>I'll Wait</v>
+      </c>
+      <c r="B221" t="str">
+        <v/>
+      </c>
+      <c r="C221" t="str">
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+      </c>
+      <c r="D221" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v>Shoulder to Shoulder</v>
+      </c>
+      <c r="G221" t="str">
+        <v>3:33</v>
+      </c>
+      <c r="H221" t="str">
+        <v>Buzzy Lee</v>
+      </c>
+      <c r="I221" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J221" t="str">
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+      </c>
+      <c r="K221" t="str">
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+      </c>
+      <c r="L221" t="str">
+        <v>I'll Wait - Buzzy Lee</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Daisy</v>
+      </c>
+      <c r="B222" t="str">
+        <v/>
+      </c>
+      <c r="C222" t="str">
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+      </c>
+      <c r="D222" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E222" t="str">
+        <v/>
+      </c>
+      <c r="F222" t="str">
+        <v>Daisy - Single</v>
+      </c>
+      <c r="G222" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H222" t="str">
+        <v>Lola Blue</v>
+      </c>
+      <c r="I222" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J222" t="str">
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+      </c>
+      <c r="K222" t="str">
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+      </c>
+      <c r="L222" t="str">
+        <v>Daisy - Lola Blue</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Play (Objekt Remix)</v>
+      </c>
+      <c r="B223" t="str">
+        <v/>
+      </c>
+      <c r="C223" t="str">
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+      </c>
+      <c r="D223" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E223" t="str">
+        <v/>
+      </c>
+      <c r="F223" t="str">
+        <v>Friend Remixes</v>
+      </c>
+      <c r="G223" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H223" t="str">
+        <v>james K</v>
+      </c>
+      <c r="I223" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J223" t="str">
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+      </c>
+      <c r="K223" t="str">
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+      </c>
+      <c r="L223" t="str">
+        <v>Play (Objekt Remix) - james K</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>Volverás (feat. Uma)</v>
+      </c>
+      <c r="B224" t="str">
+        <v/>
+      </c>
+      <c r="C224" t="str">
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+      </c>
+      <c r="D224" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E224" t="str">
+        <v/>
+      </c>
+      <c r="F224" t="str">
+        <v>Perdidos - Single</v>
+      </c>
+      <c r="G224" t="str">
+        <v>2:45</v>
+      </c>
+      <c r="H224" t="str">
+        <v>MAVICA</v>
+      </c>
+      <c r="I224" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J224" t="str">
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+      </c>
+      <c r="K224" t="str">
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+      </c>
+      <c r="L224" t="str">
+        <v>Volverás (feat. Uma) - MAVICA</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Fort</v>
+      </c>
+      <c r="B225" t="str">
+        <v/>
+      </c>
+      <c r="C225" t="str">
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
+      </c>
+      <c r="D225" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E225" t="str">
+        <v/>
+      </c>
+      <c r="F225" t="str">
+        <v>Fort - Single</v>
+      </c>
+      <c r="G225" t="str">
+        <v>2:27</v>
+      </c>
+      <c r="H225" t="str">
+        <v>Lamb</v>
+      </c>
+      <c r="I225" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J225" t="str">
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+      </c>
+      <c r="K225" t="str">
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
+      </c>
+      <c r="L225" t="str">
+        <v>Fort - Lamb</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>SAME LA</v>
+      </c>
+      <c r="B226" t="str">
+        <v/>
+      </c>
+      <c r="C226" t="str">
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+      </c>
+      <c r="D226" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E226" t="str">
+        <v/>
+      </c>
+      <c r="F226" t="str">
+        <v>SAME LA - Single</v>
+      </c>
+      <c r="G226" t="str">
+        <v>3:44</v>
+      </c>
+      <c r="H226" t="str">
+        <v>Tiffany Day</v>
+      </c>
+      <c r="I226" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J226" t="str">
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+      </c>
+      <c r="K226" t="str">
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+      </c>
+      <c r="L226" t="str">
+        <v>SAME LA - Tiffany Day</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Working On It</v>
+      </c>
+      <c r="B227" t="str">
+        <v/>
+      </c>
+      <c r="C227" t="str">
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+      </c>
+      <c r="D227" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E227" t="str">
+        <v/>
+      </c>
+      <c r="F227" t="str">
+        <v>Working On It - Single</v>
+      </c>
+      <c r="G227" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H227" t="str">
+        <v>Arthur Hill</v>
+      </c>
+      <c r="I227" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J227" t="str">
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+      </c>
+      <c r="K227" t="str">
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+      </c>
+      <c r="L227" t="str">
+        <v>Working On It - Arthur Hill</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>spring cleaning</v>
+      </c>
+      <c r="B228" t="str">
+        <v/>
+      </c>
+      <c r="C228" t="str">
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+      </c>
+      <c r="D228" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E228" t="str">
+        <v/>
+      </c>
+      <c r="F228" t="str">
+        <v>spring cleaning - Single</v>
+      </c>
+      <c r="G228" t="str">
+        <v>4:03</v>
+      </c>
+      <c r="H228" t="str">
+        <v>Ethan Regan</v>
+      </c>
+      <c r="I228" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J228" t="str">
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+      </c>
+      <c r="K228" t="str">
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+      </c>
+      <c r="L228" t="str">
+        <v>spring cleaning - Ethan Regan</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Just Drivin'</v>
+      </c>
+      <c r="B229" t="str">
+        <v/>
+      </c>
+      <c r="C229" t="str">
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+      </c>
+      <c r="D229" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E229" t="str">
+        <v/>
+      </c>
+      <c r="F229" t="str">
+        <v>Just Drivin' - Single</v>
+      </c>
+      <c r="G229" t="str">
+        <v>3:26</v>
+      </c>
+      <c r="H229" t="str">
+        <v>Presley Haile</v>
+      </c>
+      <c r="I229" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J229" t="str">
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+      </c>
+      <c r="K229" t="str">
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+      </c>
+      <c r="L229" t="str">
+        <v>Just Drivin' - Presley Haile</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Simple Things</v>
+      </c>
+      <c r="B230" t="str">
+        <v/>
+      </c>
+      <c r="C230" t="str">
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+      </c>
+      <c r="D230" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" t="str">
+        <v>Simple Things - Single</v>
+      </c>
+      <c r="G230" t="str">
+        <v>3:46</v>
+      </c>
+      <c r="H230" t="str">
+        <v>Evening Elephants</v>
+      </c>
+      <c r="I230" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J230" t="str">
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+      </c>
+      <c r="K230" t="str">
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+      </c>
+      <c r="L230" t="str">
+        <v>Simple Things - Evening Elephants</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Want It Back</v>
+      </c>
+      <c r="B231" t="str">
+        <v/>
+      </c>
+      <c r="C231" t="str">
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+      </c>
+      <c r="D231" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E231" t="str">
+        <v/>
+      </c>
+      <c r="F231" t="str">
+        <v>Want It Back - Single</v>
+      </c>
+      <c r="G231" t="str">
+        <v>3:27</v>
+      </c>
+      <c r="H231" t="str">
+        <v>Giant Rooks</v>
+      </c>
+      <c r="I231" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J231" t="str">
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+      </c>
+      <c r="K231" t="str">
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+      </c>
+      <c r="L231" t="str">
+        <v>Want It Back - Giant Rooks</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Bite Down</v>
+      </c>
+      <c r="B232" t="str">
+        <v/>
+      </c>
+      <c r="C232" t="str">
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+      </c>
+      <c r="D232" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E232" t="str">
+        <v/>
+      </c>
+      <c r="F232" t="str">
+        <v>Bite Down - Single</v>
+      </c>
+      <c r="G232" t="str">
+        <v>3:36</v>
+      </c>
+      <c r="H232" t="str">
+        <v>Anna Sofia</v>
+      </c>
+      <c r="I232" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J232" t="str">
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+      </c>
+      <c r="K232" t="str">
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+      </c>
+      <c r="L232" t="str">
+        <v>Bite Down - Anna Sofia</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Ulvgjeld &amp; Blodsodel</v>
+      </c>
+      <c r="B233" t="str">
+        <v/>
+      </c>
+      <c r="C233" t="str">
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+      </c>
+      <c r="D233" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E233" t="str">
+        <v/>
+      </c>
+      <c r="F233" t="str">
+        <v>Grand Serpent Rising</v>
+      </c>
+      <c r="G233" t="str">
+        <v>5:42</v>
+      </c>
+      <c r="H233" t="str">
+        <v>Dimmu Borgir</v>
+      </c>
+      <c r="I233" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J233" t="str">
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+      </c>
+      <c r="K233" t="str">
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+      </c>
+      <c r="L233" t="str">
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>Demons</v>
+      </c>
+      <c r="B234" t="str">
+        <v/>
+      </c>
+      <c r="C234" t="str">
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
+      </c>
+      <c r="D234" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E234" t="str">
+        <v/>
+      </c>
+      <c r="F234" t="str">
+        <v>Ask Me How I’ve Been</v>
+      </c>
+      <c r="G234" t="str">
+        <v>2:42</v>
+      </c>
+      <c r="H234" t="str">
+        <v>Anella</v>
+      </c>
+      <c r="I234" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J234" t="str">
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+      </c>
+      <c r="K234" t="str">
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
+      </c>
+      <c r="L234" t="str">
+        <v>Demons - Anella</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>Es brennt...</v>
+      </c>
+      <c r="B235" t="str">
+        <v/>
+      </c>
+      <c r="C235" t="str">
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+      </c>
+      <c r="D235" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E235" t="str">
+        <v/>
+      </c>
+      <c r="F235" t="str">
+        <v>Es brennt... - Single</v>
+      </c>
+      <c r="G235" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H235" t="str">
+        <v>Till Lindemann</v>
+      </c>
+      <c r="I235" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J235" t="str">
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+      </c>
+      <c r="K235" t="str">
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+      </c>
+      <c r="L235" t="str">
+        <v>Es brennt... - Till Lindemann</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Fire Marengo</v>
+      </c>
+      <c r="B236" t="str">
+        <v/>
+      </c>
+      <c r="C236" t="str">
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+      </c>
+      <c r="D236" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E236" t="str">
+        <v/>
+      </c>
+      <c r="F236" t="str">
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+      </c>
+      <c r="G236" t="str">
+        <v>3:49</v>
+      </c>
+      <c r="H236" t="str">
+        <v>Enslaved</v>
+      </c>
+      <c r="I236" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J236" t="str">
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+      </c>
+      <c r="K236" t="str">
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+      </c>
+      <c r="L236" t="str">
+        <v>Fire Marengo - Enslaved</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
         <v>Close to the Bone</v>
       </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
+      <c r="B237" t="str">
+        <v/>
+      </c>
+      <c r="C237" t="str">
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
-      <c r="D210" t="str">
-        <v>2026-03-30</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
+      <c r="D237" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E237" t="str">
+        <v/>
+      </c>
+      <c r="F237" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G210" t="str">
+      <c r="G237" t="str">
         <v>4:09</v>
       </c>
-      <c r="H210" t="str">
+      <c r="H237" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
+      <c r="I237" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J237" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K210" t="str">
+      <c r="K237" t="str">
         <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
-      <c r="L210" t="str">
+      <c r="L237" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L237"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>החצר האחורית של ג'וני לבד</v>
+        <v>החצר האחורית של ג'וני – לבד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>החצר האחורית של ג'וני לבד</v>
+        <v>החצר האחורית של ג'וני – לבד</v>
       </c>
     </row>
     <row r="3">
@@ -1351,7 +1351,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:42</v>

--- a/data/global/2026-03-week05/titles.xlsx
+++ b/data/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L211"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>החצר האחורית של ג'וני – לבד</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-31</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%97%d7%a6%d7%a8-%d7%94%d7%90%d7%97%d7%95%d7%a8%d7%99%d7%aa-%d7%a9%d7%9c-%d7%92%d7%95%d7%a0%d7%99-%d7%9c%d7%91%d7%93/</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר לבד של יונתן כהן (מהפרויקט “החצר האחורית של ג’וני”) הוא שיר חשוף, כמעט כמו מונולוג אישי—שנע בין סיפור חיים, וידוי נפשי וביקורת חברתית, עטוף בסאונד ים־תיכוני עם נגיעות היפ־הופ. השורה: “עברתי את מסע החיים הרבה לפני משבר 40” היא</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:56</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>החצר האחורית של ג'וני – לבד</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -492,10 +492,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:56</v>
+        <v>2:50</v>
       </c>
       <c r="H3" t="str">
-        <v>Charlie Puth</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -530,10 +530,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:50</v>
+        <v>3:42</v>
       </c>
       <c r="H4" t="str">
-        <v>Miley Cyrus</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-31</v>
@@ -568,10 +568,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:42</v>
+        <v>2:16</v>
       </c>
       <c r="H5" t="str">
-        <v>Conan Gray</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-31</v>
@@ -606,10 +606,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:16</v>
+        <v>3:08</v>
       </c>
       <c r="H6" t="str">
-        <v>Charlie Puth</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-31</v>
@@ -644,10 +644,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:08</v>
+        <v>3:38</v>
       </c>
       <c r="H7" t="str">
-        <v>Kylie Morgan</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-31</v>
@@ -682,10 +682,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:38</v>
+        <v>3:01</v>
       </c>
       <c r="H8" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-31</v>
@@ -720,10 +720,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:01</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>Angelina Mango</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-31</v>
@@ -758,10 +758,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Julio Iglesias</v>
+        <v>Loreen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-31</v>
@@ -796,10 +796,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Loreen</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-31</v>
@@ -834,10 +834,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:58</v>
+        <v>3:49</v>
       </c>
       <c r="H12" t="str">
-        <v>Jessie Ware</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-31</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>Holly Humberstone</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-31</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H14" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-31</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:50</v>
+        <v>6:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Ella Langley</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-31</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>6:43</v>
+        <v>4:52</v>
       </c>
       <c r="H16" t="str">
-        <v>David Gilmour</v>
+        <v>Eagles</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-31</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:52</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>Eagles</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-31</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:13</v>
+        <v>3:28</v>
       </c>
       <c r="H18" t="str">
-        <v>Moody Joody</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-31</v>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Jackson Dean</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-31</v>
@@ -1138,10 +1138,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:01</v>
+        <v>4:00</v>
       </c>
       <c r="H20" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-31</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:00</v>
+        <v>5:35</v>
       </c>
       <c r="H21" t="str">
-        <v>Madison Cunningham</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-31</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:35</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>mary in the junkyard</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-31</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:01</v>
+        <v>3:40</v>
       </c>
       <c r="H23" t="str">
-        <v>Adam Sanders</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-31</v>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:40</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>twocolors</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-31</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:25</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>twocolors</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B26" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-31</v>
@@ -1366,10 +1366,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:42</v>
+        <v>3:56</v>
       </c>
       <c r="H26" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Prince</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-31</v>
@@ -1404,10 +1404,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:56</v>
+        <v>5:12</v>
       </c>
       <c r="H27" t="str">
-        <v>Prince</v>
+        <v>RAYE</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B28" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-31</v>
@@ -1442,10 +1442,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:12</v>
+        <v>3:30</v>
       </c>
       <c r="H28" t="str">
-        <v>RAYE</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-31</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:30</v>
+        <v>3:18</v>
       </c>
       <c r="H29" t="str">
-        <v>The Warning</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-31</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:18</v>
+        <v>3:33</v>
       </c>
       <c r="H30" t="str">
-        <v>Pentatonix</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-31</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:33</v>
+        <v>5:53</v>
       </c>
       <c r="H31" t="str">
-        <v>Tenille Townes</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B32" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-31</v>
@@ -1594,10 +1594,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:53</v>
+        <v>2:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Jessie Ware</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B33" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-31</v>
@@ -1632,10 +1632,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Niall Horan</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-31</v>
@@ -1670,10 +1670,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:26</v>
+        <v>2:40</v>
       </c>
       <c r="H34" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B35" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-31</v>
@@ -1708,10 +1708,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:40</v>
+        <v>3:30</v>
       </c>
       <c r="H35" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-31</v>
@@ -1746,10 +1746,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:30</v>
+        <v>4:02</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-31</v>
@@ -1784,10 +1784,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:02</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>Foo Fighters</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-31</v>
@@ -1822,10 +1822,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:40</v>
+        <v>2:22</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-31</v>
@@ -1860,10 +1860,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:22</v>
+        <v>3:47</v>
       </c>
       <c r="H39" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-31</v>
@@ -1898,10 +1898,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:47</v>
+        <v>3:39</v>
       </c>
       <c r="H40" t="str">
-        <v>Ella Langley</v>
+        <v>Cannons</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B41" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-31</v>
@@ -1936,10 +1936,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:39</v>
+        <v>4:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Cannons</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B42" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-31</v>
@@ -1974,10 +1974,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:10</v>
+        <v>4:47</v>
       </c>
       <c r="H42" t="str">
-        <v>Luke Combs</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B43" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-31</v>
@@ -2012,10 +2012,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:47</v>
+        <v>2:14</v>
       </c>
       <c r="H43" t="str">
-        <v>Nessa Barrett</v>
+        <v>aron!</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B44" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-31</v>
@@ -2050,10 +2050,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H44" t="str">
-        <v>aron!</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B45" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-31</v>
@@ -2088,10 +2088,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:00</v>
+        <v>3:56</v>
       </c>
       <c r="H45" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>DMA'S</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-31</v>
@@ -2126,10 +2126,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:56</v>
+        <v>3:17</v>
       </c>
       <c r="H46" t="str">
-        <v>DMA'S</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-31</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-31</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-31</v>
@@ -2240,10 +2240,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Nick Carter</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-31</v>
@@ -2278,10 +2278,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:38</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Carly Pearce</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-31</v>
@@ -2316,10 +2316,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:11</v>
+        <v>2:57</v>
       </c>
       <c r="H51" t="str">
-        <v>OneRepublic</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-31</v>
@@ -2354,10 +2354,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:57</v>
+        <v>3:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-31</v>
@@ -2392,10 +2392,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:47</v>
+        <v>7:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-31</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>7:10</v>
+        <v>3:06</v>
       </c>
       <c r="H54" t="str">
-        <v>David Gilmour</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-31</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:06</v>
+        <v>3:05</v>
       </c>
       <c r="H55" t="str">
-        <v>Grace Enger</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-31</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H56" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-31</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:12</v>
+        <v>9:11</v>
       </c>
       <c r="H57" t="str">
-        <v>Freya Ridings</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-31</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H58" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-31</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:49</v>
+        <v>3:28</v>
       </c>
       <c r="H59" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-31</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H60" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-31</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>Martin Garrix</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-31</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:11</v>
+        <v>2:27</v>
       </c>
       <c r="H62" t="str">
-        <v>Baby Queen</v>
+        <v>HAUSER</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-31</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-31</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:34</v>
+        <v>2:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Holly Humberstone</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-31</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H65" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-31</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H66" t="str">
-        <v>Rick Astley</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-31</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:39</v>
+        <v>5:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Jessie J</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-31</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:08</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Jessie J</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-31</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H69" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-31</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:42</v>
+        <v>2:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-31</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:31</v>
+        <v>3:14</v>
       </c>
       <c r="H71" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-31</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H72" t="str">
-        <v>Luke Combs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-31</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H73" t="str">
-        <v>Allison Russell</v>
+        <v>We Three</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-31</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H74" t="str">
-        <v>We Three</v>
+        <v>paris jackson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-31</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H75" t="str">
-        <v>paris jackson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-31</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:46</v>
+        <v>3:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-31</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-31</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H78" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-31</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:38</v>
+        <v>4:29</v>
       </c>
       <c r="H79" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Kungs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-31</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:29</v>
+        <v>4:28</v>
       </c>
       <c r="H80" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-31</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:28</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-31</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H82" t="str">
-        <v>aron!</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-31</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H83" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-31</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H84" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-31</v>
@@ -3611,7 +3611,7 @@
         <v>4:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Owen Riegling</v>
+        <v>LANY</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-31</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>LANY</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-31</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H87" t="str">
-        <v>Maverick Sabre</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-31</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Amanda Jordan</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-31</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="H89" t="str">
-        <v>Beabadoobee</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-31</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Spacey Jane</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-31</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H91" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-31</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H92" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-31</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H93" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-31</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H94" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-31</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-31</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-31</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H97" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-31</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H98" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-31</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H99" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-31</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H100" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-31</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H101" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-31</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G102" t="str">
-        <v>5:01</v>
+        <v>1:37</v>
       </c>
       <c r="H102" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L102" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Home on the Range</v>
+        <v>Back Home</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-31</v>
@@ -4292,33 +4292,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G103" t="str">
-        <v>1:37</v>
+        <v>1:36</v>
       </c>
       <c r="H103" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L103" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Back Home</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-31</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>1:36</v>
+        <v>3:18</v>
       </c>
       <c r="H104" t="str">
-        <v>MIKE</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Days We Left Behind</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-31</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:18</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Paul McCartney</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L105" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-31</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G106" t="str">
-        <v>2:47</v>
+        <v>6:17</v>
       </c>
       <c r="H106" t="str">
-        <v>Miley Cyrus</v>
+        <v>RAYE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L106" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>MARATHON</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-31</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>6:17</v>
+        <v>2:49</v>
       </c>
       <c r="H107" t="str">
-        <v>RAYE</v>
+        <v>Becky G</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L107" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>MARATHON</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-31</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>MARATHON - Single</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Becky G</v>
+        <v>John Summit</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L108" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ALL THE TIME</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-31</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sucker For Love</v>
+        <v>FATHER</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-31</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Sexistential</v>
+        <v>BULLY</v>
       </c>
       <c r="G110" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H110" t="str">
-        <v>Robyn</v>
+        <v>Kanye West</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L110" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>FATHER</v>
+        <v>Lose Control</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-31</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>BULLY</v>
+        <v>ADL</v>
       </c>
       <c r="G111" t="str">
-        <v>2:49</v>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>Kanye West</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L111" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Lose Control</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-31</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ADL</v>
+        <v>Zavier</v>
       </c>
       <c r="G112" t="str">
-        <v>2:39</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Yeat</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L112" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-31</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Zavier</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G113" t="str">
-        <v>3:44</v>
+        <v>2:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Fetty Wap</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L113" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WAGWAN</v>
+        <v>Sideways</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-31</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G114" t="str">
-        <v>2:07</v>
+        <v>3:12</v>
       </c>
       <c r="H114" t="str">
-        <v>Central Cee</v>
+        <v>ZAYN</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L114" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Sideways</v>
+        <v>Automatic</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-31</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>KONNAKOL</v>
+        <v>Superbloom</v>
       </c>
       <c r="G115" t="str">
-        <v>3:12</v>
+        <v>2:57</v>
       </c>
       <c r="H115" t="str">
-        <v>ZAYN</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L115" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Automatic</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-31</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Superbloom</v>
+        <v>Ricochet</v>
       </c>
       <c r="G116" t="str">
-        <v>2:57</v>
+        <v>3:34</v>
       </c>
       <c r="H116" t="str">
-        <v>Jessie Ware</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L116" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Tractor Beam</v>
+        <v>prom queen</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-31</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ricochet</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:34</v>
+        <v>2:43</v>
       </c>
       <c r="H117" t="str">
-        <v>Snail Mail</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L117" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>prom queen</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-31</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>prom queen - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:43</v>
+        <v>3:26</v>
       </c>
       <c r="H118" t="str">
-        <v>Amelia Moore</v>
+        <v>J Balvin</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L118" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Pal Agua</v>
+        <v>Phoenix</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-31</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:26</v>
+        <v>2:24</v>
       </c>
       <c r="H119" t="str">
-        <v>J Balvin</v>
+        <v>Marshmello</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L119" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Phoenix</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-31</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Phoenix - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:24</v>
+        <v>2:56</v>
       </c>
       <c r="H120" t="str">
-        <v>Marshmello</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L120" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-31</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:56</v>
+        <v>3:36</v>
       </c>
       <c r="H121" t="str">
-        <v>Ne-Yo</v>
+        <v>Eli</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <